--- a/hall/resources/sample/ResearchSkills.xlsx
+++ b/hall/resources/sample/ResearchSkills.xlsx
@@ -135,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2076" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2076" uniqueCount="404">
   <si>
     <t>id</t>
   </si>
@@ -278,67 +278,67 @@
     <t>解锁800000下注额</t>
   </si>
   <si>
-    <t>1,0_-500</t>
+    <t>1,0_-5000</t>
   </si>
   <si>
     <t>中奖率提升1%</t>
   </si>
   <si>
-    <t>1,0_-1000</t>
+    <t>1,0_-10000</t>
   </si>
   <si>
     <t>中奖率提升2%</t>
   </si>
   <si>
-    <t>1,0_-1500</t>
+    <t>1,0_-15000</t>
   </si>
   <si>
     <t>中奖率提升3%</t>
   </si>
   <si>
-    <t>1,0_-2000</t>
+    <t>1,0_-20000</t>
   </si>
   <si>
     <t>中奖率提升4%</t>
   </si>
   <si>
-    <t>1,0_-2500</t>
+    <t>1,0_-25000</t>
   </si>
   <si>
     <t>中奖率提升5%</t>
   </si>
   <si>
-    <t>1,0_-3000</t>
+    <t>1,0_-30000</t>
   </si>
   <si>
     <t>中奖率提升6%</t>
   </si>
   <si>
-    <t>1,0_-3500</t>
+    <t>1,0_-35000</t>
   </si>
   <si>
     <t>中奖率提升7%</t>
   </si>
   <si>
-    <t>1,0_-4000</t>
+    <t>1,0_-40000</t>
   </si>
   <si>
     <t>中奖率提升8%</t>
   </si>
   <si>
-    <t>1,0_-4500</t>
+    <t>1,0_-45000</t>
   </si>
   <si>
     <t>中奖率提升9%</t>
   </si>
   <si>
-    <t>1,0_-5000</t>
+    <t>1,0_-50000</t>
   </si>
   <si>
     <t>中奖率提升10%</t>
   </si>
   <si>
-    <t>1,3_10</t>
+    <t>1,3_100</t>
   </si>
   <si>
     <t>常规模式5-10倍中奖概率提升1%</t>
@@ -392,7 +392,7 @@
     <t>常规模式5-10倍中奖概率提升9%</t>
   </si>
   <si>
-    <t>1,3_19</t>
+    <t>1,3_20000</t>
   </si>
   <si>
     <t>常规模式5-10倍中奖概率提升10%</t>
@@ -458,31 +458,61 @@
     <t>常规模式10-20倍中奖概率提升10%</t>
   </si>
   <si>
+    <t>2,100</t>
+  </si>
+  <si>
     <t>中樱桃符号概率提升1%</t>
   </si>
   <si>
+    <t>2,500</t>
+  </si>
+  <si>
     <t>中樱桃符号概率提升2%</t>
   </si>
   <si>
+    <t>2,1000</t>
+  </si>
+  <si>
     <t>中樱桃符号概率提升3%</t>
   </si>
   <si>
+    <t>2,1500</t>
+  </si>
+  <si>
     <t>中樱桃符号概率提升4%</t>
   </si>
   <si>
+    <t>2,2000</t>
+  </si>
+  <si>
     <t>中樱桃符号概率提升5%</t>
   </si>
   <si>
+    <t>2,2500</t>
+  </si>
+  <si>
     <t>中樱桃符号概率提升6%</t>
   </si>
   <si>
+    <t>2,3000</t>
+  </si>
+  <si>
     <t>中樱桃符号概率提升7%</t>
   </si>
   <si>
+    <t>2,3500</t>
+  </si>
+  <si>
     <t>中樱桃符号概率提升8%</t>
   </si>
   <si>
+    <t>2,4000</t>
+  </si>
+  <si>
     <t>中樱桃符号概率提升9%</t>
+  </si>
+  <si>
+    <t>2,5000</t>
   </si>
   <si>
     <t>中樱桃符号概率提升10%</t>
@@ -1964,7 +1994,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1979,6 +2009,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2307,7 +2340,7 @@
     <col min="13" max="13" width="15.875" style="1" customWidth="1"/>
     <col min="14" max="14" width="24.875" style="1" customWidth="1"/>
     <col min="15" max="15" width="22" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="16" max="16383" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -2498,7 +2531,7 @@
         <v>29</v>
       </c>
       <c r="H7" s="2">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>30</v>
@@ -2556,7 +2589,7 @@
         <v>33</v>
       </c>
       <c r="H9" s="2">
-        <v>16000</v>
+        <v>12000</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>34</v>
@@ -2585,7 +2618,7 @@
         <v>35</v>
       </c>
       <c r="H10" s="2">
-        <v>32000</v>
+        <v>16000</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>36</v>
@@ -2614,7 +2647,7 @@
         <v>37</v>
       </c>
       <c r="H11" s="2">
-        <v>64000</v>
+        <v>20000</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>38</v>
@@ -3747,11 +3780,11 @@
         <v>27</v>
       </c>
       <c r="H50" s="2"/>
-      <c r="L50" s="1" t="s">
-        <v>45</v>
+      <c r="L50" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -3777,11 +3810,11 @@
         <v>29</v>
       </c>
       <c r="H51" s="2"/>
-      <c r="L51" s="1" t="s">
-        <v>45</v>
+      <c r="L51" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -3807,11 +3840,11 @@
         <v>31</v>
       </c>
       <c r="H52" s="2"/>
-      <c r="L52" s="1" t="s">
-        <v>45</v>
+      <c r="L52" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -3837,11 +3870,11 @@
         <v>33</v>
       </c>
       <c r="H53" s="2"/>
-      <c r="L53" s="1" t="s">
-        <v>45</v>
+      <c r="L53" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -3867,11 +3900,11 @@
         <v>35</v>
       </c>
       <c r="H54" s="2"/>
-      <c r="L54" s="1" t="s">
-        <v>45</v>
+      <c r="L54" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -3897,11 +3930,11 @@
         <v>37</v>
       </c>
       <c r="H55" s="2"/>
-      <c r="L55" s="1" t="s">
-        <v>45</v>
+      <c r="L55" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -3927,11 +3960,11 @@
         <v>39</v>
       </c>
       <c r="H56" s="2"/>
-      <c r="L56" s="1" t="s">
-        <v>45</v>
+      <c r="L56" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -3957,11 +3990,11 @@
         <v>41</v>
       </c>
       <c r="H57" s="2"/>
-      <c r="L57" s="1" t="s">
-        <v>45</v>
+      <c r="L57" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -3987,11 +4020,11 @@
         <v>43</v>
       </c>
       <c r="H58" s="2"/>
-      <c r="L58" s="1" t="s">
-        <v>45</v>
+      <c r="L58" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -4017,11 +4050,11 @@
         <v>45</v>
       </c>
       <c r="H59" s="2"/>
-      <c r="L59" s="1" t="s">
-        <v>45</v>
+      <c r="L59" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -4072,10 +4105,10 @@
       </c>
       <c r="H61" s="2"/>
       <c r="L61" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -4102,10 +4135,10 @@
       </c>
       <c r="H62" s="2"/>
       <c r="L62" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -4132,10 +4165,10 @@
       </c>
       <c r="H63" s="2"/>
       <c r="L63" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -4162,10 +4195,10 @@
       </c>
       <c r="H64" s="2"/>
       <c r="L64" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -4192,10 +4225,10 @@
       </c>
       <c r="H65" s="2"/>
       <c r="L65" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -4222,10 +4255,10 @@
       </c>
       <c r="H66" s="2"/>
       <c r="L66" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -4252,10 +4285,10 @@
       </c>
       <c r="H67" s="2"/>
       <c r="L67" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -4282,10 +4315,10 @@
       </c>
       <c r="H68" s="2"/>
       <c r="L68" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -4312,10 +4345,10 @@
       </c>
       <c r="H69" s="2"/>
       <c r="L69" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -4342,10 +4375,10 @@
       </c>
       <c r="H70" s="2"/>
       <c r="L70" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -4362,7 +4395,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F71" s="1">
         <v>10340001</v>
@@ -4370,7 +4403,9 @@
       <c r="G71" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H71" s="2"/>
+      <c r="H71" s="2">
+        <v>1000</v>
+      </c>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="1">
@@ -4386,7 +4421,7 @@
         <v>1</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F72" s="1">
         <v>10340001</v>
@@ -4415,7 +4450,7 @@
         <v>2</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F73" s="1">
         <v>10340001</v>
@@ -4424,7 +4459,7 @@
         <v>29</v>
       </c>
       <c r="H73" s="2">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>30</v>
@@ -4444,7 +4479,7 @@
         <v>3</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F74" s="1">
         <v>10340001</v>
@@ -4473,7 +4508,7 @@
         <v>4</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F75" s="1">
         <v>10340001</v>
@@ -4482,7 +4517,7 @@
         <v>33</v>
       </c>
       <c r="H75" s="2">
-        <v>16000</v>
+        <v>12000</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>34</v>
@@ -4502,7 +4537,7 @@
         <v>5</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F76" s="1">
         <v>10340001</v>
@@ -4511,7 +4546,7 @@
         <v>35</v>
       </c>
       <c r="H76" s="2">
-        <v>32000</v>
+        <v>16000</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>36</v>
@@ -4531,7 +4566,7 @@
         <v>6</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F77" s="1">
         <v>10340001</v>
@@ -4540,7 +4575,7 @@
         <v>37</v>
       </c>
       <c r="H77" s="2">
-        <v>64000</v>
+        <v>20000</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>38</v>
@@ -4560,7 +4595,7 @@
         <v>7</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F78" s="1">
         <v>10340001</v>
@@ -4589,7 +4624,7 @@
         <v>8</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F79" s="1">
         <v>10340001</v>
@@ -4618,7 +4653,7 @@
         <v>9</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F80" s="1">
         <v>10340001</v>
@@ -4647,7 +4682,7 @@
         <v>10</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F81" s="1">
         <v>10340001</v>
@@ -4676,7 +4711,7 @@
         <v>0</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F82" s="1">
         <v>10340002</v>
@@ -4700,7 +4735,7 @@
         <v>1</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F83" s="1">
         <v>10340002</v>
@@ -4730,7 +4765,7 @@
         <v>2</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F84" s="1">
         <v>10340002</v>
@@ -4760,7 +4795,7 @@
         <v>3</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F85" s="1">
         <v>10340002</v>
@@ -4790,7 +4825,7 @@
         <v>4</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F86" s="1">
         <v>10340002</v>
@@ -4820,7 +4855,7 @@
         <v>5</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F87" s="1">
         <v>10340002</v>
@@ -4850,7 +4885,7 @@
         <v>6</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F88" s="1">
         <v>10340002</v>
@@ -4880,7 +4915,7 @@
         <v>7</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F89" s="1">
         <v>10340002</v>
@@ -4910,7 +4945,7 @@
         <v>8</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F90" s="1">
         <v>10340002</v>
@@ -4940,7 +4975,7 @@
         <v>9</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F91" s="1">
         <v>10340002</v>
@@ -4970,7 +5005,7 @@
         <v>10</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F92" s="1">
         <v>10340002</v>
@@ -5000,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F93" s="1">
         <v>10340003</v>
@@ -5024,7 +5059,7 @@
         <v>1</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F94" s="1">
         <v>10340003</v>
@@ -5034,7 +5069,7 @@
       </c>
       <c r="H94" s="2"/>
       <c r="J94" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K94" s="1" t="s">
         <v>68</v>
@@ -5054,7 +5089,7 @@
         <v>2</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F95" s="1">
         <v>10340003</v>
@@ -5064,7 +5099,7 @@
       </c>
       <c r="H95" s="2"/>
       <c r="J95" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K95" s="1" t="s">
         <v>70</v>
@@ -5084,7 +5119,7 @@
         <v>3</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F96" s="1">
         <v>10340003</v>
@@ -5094,7 +5129,7 @@
       </c>
       <c r="H96" s="2"/>
       <c r="J96" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K96" s="1" t="s">
         <v>72</v>
@@ -5114,7 +5149,7 @@
         <v>4</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F97" s="1">
         <v>10340003</v>
@@ -5124,7 +5159,7 @@
       </c>
       <c r="H97" s="2"/>
       <c r="J97" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K97" s="1" t="s">
         <v>74</v>
@@ -5144,7 +5179,7 @@
         <v>5</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F98" s="1">
         <v>10340003</v>
@@ -5154,7 +5189,7 @@
       </c>
       <c r="H98" s="2"/>
       <c r="J98" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K98" s="1" t="s">
         <v>76</v>
@@ -5174,7 +5209,7 @@
         <v>6</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F99" s="1">
         <v>10340003</v>
@@ -5184,7 +5219,7 @@
       </c>
       <c r="H99" s="2"/>
       <c r="J99" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K99" s="1" t="s">
         <v>78</v>
@@ -5204,7 +5239,7 @@
         <v>7</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F100" s="1">
         <v>10340003</v>
@@ -5214,7 +5249,7 @@
       </c>
       <c r="H100" s="2"/>
       <c r="J100" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K100" s="1" t="s">
         <v>80</v>
@@ -5234,7 +5269,7 @@
         <v>8</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F101" s="1">
         <v>10340003</v>
@@ -5244,7 +5279,7 @@
       </c>
       <c r="H101" s="2"/>
       <c r="J101" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K101" s="1" t="s">
         <v>82</v>
@@ -5264,7 +5299,7 @@
         <v>9</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F102" s="1">
         <v>10340003</v>
@@ -5274,7 +5309,7 @@
       </c>
       <c r="H102" s="2"/>
       <c r="J102" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K102" s="1" t="s">
         <v>84</v>
@@ -5294,7 +5329,7 @@
         <v>10</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F103" s="1">
         <v>10340003</v>
@@ -5304,7 +5339,7 @@
       </c>
       <c r="H103" s="2"/>
       <c r="J103" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K103" s="1" t="s">
         <v>86</v>
@@ -5324,7 +5359,7 @@
         <v>0</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F104" s="1">
         <v>10340004</v>
@@ -5348,7 +5383,7 @@
         <v>1</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F105" s="1">
         <v>10340004</v>
@@ -5358,10 +5393,10 @@
       </c>
       <c r="H105" s="2"/>
       <c r="J105" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -5378,7 +5413,7 @@
         <v>2</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F106" s="1">
         <v>10340004</v>
@@ -5388,10 +5423,10 @@
       </c>
       <c r="H106" s="2"/>
       <c r="J106" s="1" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -5408,7 +5443,7 @@
         <v>3</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F107" s="1">
         <v>10340004</v>
@@ -5418,10 +5453,10 @@
       </c>
       <c r="H107" s="2"/>
       <c r="J107" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -5438,7 +5473,7 @@
         <v>4</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F108" s="1">
         <v>10340004</v>
@@ -5448,10 +5483,10 @@
       </c>
       <c r="H108" s="2"/>
       <c r="J108" s="1" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -5468,7 +5503,7 @@
         <v>5</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F109" s="1">
         <v>10340004</v>
@@ -5478,10 +5513,10 @@
       </c>
       <c r="H109" s="2"/>
       <c r="J109" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -5498,7 +5533,7 @@
         <v>6</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F110" s="1">
         <v>10340004</v>
@@ -5508,10 +5543,10 @@
       </c>
       <c r="H110" s="2"/>
       <c r="J110" s="1" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -5528,7 +5563,7 @@
         <v>7</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F111" s="1">
         <v>10340004</v>
@@ -5538,10 +5573,10 @@
       </c>
       <c r="H111" s="2"/>
       <c r="J111" s="1" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -5558,7 +5593,7 @@
         <v>8</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F112" s="1">
         <v>10340004</v>
@@ -5568,10 +5603,10 @@
       </c>
       <c r="H112" s="2"/>
       <c r="J112" s="1" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -5588,7 +5623,7 @@
         <v>9</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F113" s="1">
         <v>10340004</v>
@@ -5598,10 +5633,10 @@
       </c>
       <c r="H113" s="2"/>
       <c r="J113" s="1" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -5618,7 +5653,7 @@
         <v>10</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F114" s="1">
         <v>10340004</v>
@@ -5628,10 +5663,10 @@
       </c>
       <c r="H114" s="2"/>
       <c r="J114" s="1" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -5648,7 +5683,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F115" s="1">
         <v>10340005</v>
@@ -5672,7 +5707,7 @@
         <v>1</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F116" s="1">
         <v>10340005</v>
@@ -5682,10 +5717,10 @@
       </c>
       <c r="H116" s="2"/>
       <c r="J116" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -5702,7 +5737,7 @@
         <v>2</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F117" s="1">
         <v>10340005</v>
@@ -5712,10 +5747,10 @@
       </c>
       <c r="H117" s="2"/>
       <c r="J117" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -5732,7 +5767,7 @@
         <v>3</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F118" s="1">
         <v>10340005</v>
@@ -5742,10 +5777,10 @@
       </c>
       <c r="H118" s="2"/>
       <c r="J118" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -5762,7 +5797,7 @@
         <v>4</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F119" s="1">
         <v>10340005</v>
@@ -5772,10 +5807,10 @@
       </c>
       <c r="H119" s="2"/>
       <c r="J119" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -5792,7 +5827,7 @@
         <v>5</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F120" s="1">
         <v>10340005</v>
@@ -5802,10 +5837,10 @@
       </c>
       <c r="H120" s="2"/>
       <c r="J120" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
     </row>
     <row r="121" spans="1:13">
@@ -5822,7 +5857,7 @@
         <v>6</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F121" s="1">
         <v>10340005</v>
@@ -5832,10 +5867,10 @@
       </c>
       <c r="H121" s="2"/>
       <c r="J121" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="122" spans="1:13">
@@ -5852,7 +5887,7 @@
         <v>7</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F122" s="1">
         <v>10340005</v>
@@ -5862,10 +5897,10 @@
       </c>
       <c r="H122" s="2"/>
       <c r="J122" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
     </row>
     <row r="123" spans="1:13">
@@ -5882,7 +5917,7 @@
         <v>8</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F123" s="1">
         <v>10340005</v>
@@ -5892,10 +5927,10 @@
       </c>
       <c r="H123" s="2"/>
       <c r="J123" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="124" spans="1:13">
@@ -5912,7 +5947,7 @@
         <v>9</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F124" s="1">
         <v>10340005</v>
@@ -5922,10 +5957,10 @@
       </c>
       <c r="H124" s="2"/>
       <c r="J124" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
     </row>
     <row r="125" spans="1:13">
@@ -5942,7 +5977,7 @@
         <v>10</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F125" s="1">
         <v>10340005</v>
@@ -5952,10 +5987,10 @@
       </c>
       <c r="H125" s="2"/>
       <c r="J125" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="126" spans="1:13">
@@ -5972,7 +6007,7 @@
         <v>0</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F126" s="1">
         <v>10340006</v>
@@ -5996,7 +6031,7 @@
         <v>1</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F127" s="1">
         <v>10340006</v>
@@ -6009,7 +6044,7 @@
         <v>45</v>
       </c>
       <c r="M127" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="128" spans="1:13">
@@ -6026,7 +6061,7 @@
         <v>2</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F128" s="1">
         <v>10340006</v>
@@ -6039,7 +6074,7 @@
         <v>45</v>
       </c>
       <c r="M128" s="1" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
     </row>
     <row r="129" spans="1:15">
@@ -6056,7 +6091,7 @@
         <v>3</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F129" s="1">
         <v>10340006</v>
@@ -6069,7 +6104,7 @@
         <v>45</v>
       </c>
       <c r="M129" s="1" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
     </row>
     <row r="130" spans="1:15">
@@ -6086,7 +6121,7 @@
         <v>4</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F130" s="1">
         <v>10340006</v>
@@ -6099,7 +6134,7 @@
         <v>45</v>
       </c>
       <c r="M130" s="1" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
     </row>
     <row r="131" spans="1:15">
@@ -6116,7 +6151,7 @@
         <v>5</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F131" s="1">
         <v>10340006</v>
@@ -6129,7 +6164,7 @@
         <v>45</v>
       </c>
       <c r="M131" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="132" spans="1:15">
@@ -6146,7 +6181,7 @@
         <v>6</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F132" s="1">
         <v>10340006</v>
@@ -6159,7 +6194,7 @@
         <v>45</v>
       </c>
       <c r="M132" s="1" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
     </row>
     <row r="133" spans="1:15">
@@ -6176,7 +6211,7 @@
         <v>7</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F133" s="1">
         <v>10340006</v>
@@ -6189,7 +6224,7 @@
         <v>45</v>
       </c>
       <c r="M133" s="1" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="134" spans="1:15">
@@ -6206,7 +6241,7 @@
         <v>8</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F134" s="1">
         <v>10340006</v>
@@ -6219,7 +6254,7 @@
         <v>45</v>
       </c>
       <c r="M134" s="1" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
     </row>
     <row r="135" spans="1:15">
@@ -6236,7 +6271,7 @@
         <v>9</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F135" s="1">
         <v>10340006</v>
@@ -6249,7 +6284,7 @@
         <v>45</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
     </row>
     <row r="136" spans="1:15">
@@ -6266,7 +6301,7 @@
         <v>10</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F136" s="1">
         <v>10340006</v>
@@ -6279,7 +6314,7 @@
         <v>45</v>
       </c>
       <c r="M136" s="1" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
     </row>
     <row r="137" spans="1:15">
@@ -6296,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F137" s="1">
         <v>10340007</v>
@@ -6320,7 +6355,7 @@
         <v>1</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F138" s="1">
         <v>10340007</v>
@@ -6330,10 +6365,10 @@
       </c>
       <c r="H138" s="2"/>
       <c r="N138" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="O138" s="1" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="139" spans="1:15">
@@ -6350,7 +6385,7 @@
         <v>2</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F139" s="1">
         <v>10340007</v>
@@ -6360,10 +6395,10 @@
       </c>
       <c r="H139" s="2"/>
       <c r="N139" s="1" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="O139" s="1" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
     </row>
     <row r="140" spans="1:15">
@@ -6380,7 +6415,7 @@
         <v>3</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F140" s="1">
         <v>10340007</v>
@@ -6390,10 +6425,10 @@
       </c>
       <c r="H140" s="2"/>
       <c r="N140" s="1" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="O140" s="1" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="141" spans="1:15">
@@ -6410,7 +6445,7 @@
         <v>4</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F141" s="1">
         <v>10340007</v>
@@ -6420,10 +6455,10 @@
       </c>
       <c r="H141" s="2"/>
       <c r="N141" s="1" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="O141" s="1" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="142" spans="1:15">
@@ -6440,7 +6475,7 @@
         <v>5</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F142" s="1">
         <v>10340007</v>
@@ -6450,10 +6485,10 @@
       </c>
       <c r="H142" s="2"/>
       <c r="N142" s="1" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="O142" s="1" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="143" spans="1:15">
@@ -6470,7 +6505,7 @@
         <v>6</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F143" s="1">
         <v>10340007</v>
@@ -6480,10 +6515,10 @@
       </c>
       <c r="H143" s="2"/>
       <c r="N143" s="1" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="144" spans="1:15">
@@ -6500,7 +6535,7 @@
         <v>7</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F144" s="1">
         <v>10340007</v>
@@ -6510,10 +6545,10 @@
       </c>
       <c r="H144" s="2"/>
       <c r="N144" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="O144" s="1" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
     </row>
     <row r="145" spans="1:15">
@@ -6530,7 +6565,7 @@
         <v>8</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F145" s="1">
         <v>10340007</v>
@@ -6540,10 +6575,10 @@
       </c>
       <c r="H145" s="2"/>
       <c r="N145" s="1" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
     </row>
     <row r="146" spans="1:15">
@@ -6560,7 +6595,7 @@
         <v>9</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F146" s="1">
         <v>10340007</v>
@@ -6570,10 +6605,10 @@
       </c>
       <c r="H146" s="2"/>
       <c r="N146" s="1" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="O146" s="1" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
     </row>
     <row r="147" spans="1:15">
@@ -6590,7 +6625,7 @@
         <v>10</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F147" s="1">
         <v>10340007</v>
@@ -6600,10 +6635,10 @@
       </c>
       <c r="H147" s="2"/>
       <c r="N147" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="O147" s="1" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
     </row>
     <row r="148" spans="1:15">
@@ -6620,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F148" s="1">
         <v>10340008</v>
@@ -6644,7 +6679,7 @@
         <v>1</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F149" s="1">
         <v>10340008</v>
@@ -6654,10 +6689,10 @@
       </c>
       <c r="H149" s="2"/>
       <c r="N149" s="1" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="O149" s="1" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="150" spans="1:15">
@@ -6674,7 +6709,7 @@
         <v>2</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F150" s="1">
         <v>10340008</v>
@@ -6684,10 +6719,10 @@
       </c>
       <c r="H150" s="2"/>
       <c r="N150" s="1" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="O150" s="1" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
     </row>
     <row r="151" spans="1:15">
@@ -6704,7 +6739,7 @@
         <v>3</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F151" s="1">
         <v>10340008</v>
@@ -6714,10 +6749,10 @@
       </c>
       <c r="H151" s="2"/>
       <c r="N151" s="1" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="O151" s="1" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
     </row>
     <row r="152" spans="1:15">
@@ -6734,7 +6769,7 @@
         <v>4</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F152" s="1">
         <v>10340008</v>
@@ -6744,10 +6779,10 @@
       </c>
       <c r="H152" s="2"/>
       <c r="N152" s="1" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
     </row>
     <row r="153" spans="1:15">
@@ -6764,7 +6799,7 @@
         <v>5</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F153" s="1">
         <v>10340008</v>
@@ -6774,10 +6809,10 @@
       </c>
       <c r="H153" s="2"/>
       <c r="N153" s="1" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="O153" s="1" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
     </row>
     <row r="154" spans="1:15">
@@ -6794,7 +6829,7 @@
         <v>6</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F154" s="1">
         <v>10340008</v>
@@ -6804,10 +6839,10 @@
       </c>
       <c r="H154" s="2"/>
       <c r="N154" s="1" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="O154" s="1" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="155" spans="1:15">
@@ -6824,7 +6859,7 @@
         <v>7</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F155" s="1">
         <v>10340008</v>
@@ -6834,10 +6869,10 @@
       </c>
       <c r="H155" s="2"/>
       <c r="N155" s="1" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="O155" s="1" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="156" spans="1:15">
@@ -6854,7 +6889,7 @@
         <v>8</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F156" s="1">
         <v>10340008</v>
@@ -6864,10 +6899,10 @@
       </c>
       <c r="H156" s="2"/>
       <c r="N156" s="1" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="O156" s="1" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
     </row>
     <row r="157" spans="1:15">
@@ -6884,7 +6919,7 @@
         <v>9</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F157" s="1">
         <v>10340008</v>
@@ -6894,10 +6929,10 @@
       </c>
       <c r="H157" s="2"/>
       <c r="N157" s="1" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="O157" s="1" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="158" spans="1:15">
@@ -6914,7 +6949,7 @@
         <v>10</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F158" s="1">
         <v>10340008</v>
@@ -6924,10 +6959,10 @@
       </c>
       <c r="H158" s="2"/>
       <c r="N158" s="1" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="O158" s="1" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
     </row>
     <row r="159" spans="1:15">
@@ -6944,7 +6979,7 @@
         <v>0</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F159" s="1">
         <v>10340009</v>
@@ -6968,7 +7003,7 @@
         <v>1</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F160" s="1">
         <v>10340009</v>
@@ -6978,10 +7013,10 @@
       </c>
       <c r="H160" s="2"/>
       <c r="L160" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M160" s="1" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
     </row>
     <row r="161" spans="1:13">
@@ -6998,7 +7033,7 @@
         <v>2</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F161" s="1">
         <v>10340009</v>
@@ -7008,10 +7043,10 @@
       </c>
       <c r="H161" s="2"/>
       <c r="L161" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M161" s="1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="162" spans="1:13">
@@ -7028,7 +7063,7 @@
         <v>3</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F162" s="1">
         <v>10340009</v>
@@ -7038,10 +7073,10 @@
       </c>
       <c r="H162" s="2"/>
       <c r="L162" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M162" s="1" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="163" spans="1:13">
@@ -7058,7 +7093,7 @@
         <v>4</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F163" s="1">
         <v>10340009</v>
@@ -7068,10 +7103,10 @@
       </c>
       <c r="H163" s="2"/>
       <c r="L163" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M163" s="1" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="164" spans="1:13">
@@ -7088,7 +7123,7 @@
         <v>5</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F164" s="1">
         <v>10340009</v>
@@ -7098,10 +7133,10 @@
       </c>
       <c r="H164" s="2"/>
       <c r="L164" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M164" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="165" spans="1:13">
@@ -7118,7 +7153,7 @@
         <v>6</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F165" s="1">
         <v>10340009</v>
@@ -7128,10 +7163,10 @@
       </c>
       <c r="H165" s="2"/>
       <c r="L165" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M165" s="1" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="166" spans="1:13">
@@ -7148,7 +7183,7 @@
         <v>7</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F166" s="1">
         <v>10340009</v>
@@ -7158,10 +7193,10 @@
       </c>
       <c r="H166" s="2"/>
       <c r="L166" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M166" s="1" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
     <row r="167" spans="1:13">
@@ -7178,7 +7213,7 @@
         <v>8</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F167" s="1">
         <v>10340009</v>
@@ -7188,10 +7223,10 @@
       </c>
       <c r="H167" s="2"/>
       <c r="L167" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M167" s="1" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="168" spans="1:13">
@@ -7208,7 +7243,7 @@
         <v>9</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F168" s="1">
         <v>10340009</v>
@@ -7218,10 +7253,10 @@
       </c>
       <c r="H168" s="2"/>
       <c r="L168" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M168" s="1" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="169" spans="1:13">
@@ -7238,7 +7273,7 @@
         <v>10</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F169" s="1">
         <v>10340009</v>
@@ -7248,10 +7283,10 @@
       </c>
       <c r="H169" s="2"/>
       <c r="L169" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M169" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="170" spans="1:13">
@@ -7268,7 +7303,7 @@
         <v>0</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F170" s="1">
         <v>10350001</v>
@@ -7292,7 +7327,7 @@
         <v>1</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F171" s="1">
         <v>10350001</v>
@@ -7321,7 +7356,7 @@
         <v>2</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F172" s="1">
         <v>10350001</v>
@@ -7350,7 +7385,7 @@
         <v>3</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F173" s="1">
         <v>10350001</v>
@@ -7379,7 +7414,7 @@
         <v>4</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F174" s="1">
         <v>10350001</v>
@@ -7408,7 +7443,7 @@
         <v>5</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F175" s="1">
         <v>10350001</v>
@@ -7437,7 +7472,7 @@
         <v>6</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F176" s="1">
         <v>10350001</v>
@@ -7466,7 +7501,7 @@
         <v>7</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F177" s="1">
         <v>10350001</v>
@@ -7495,7 +7530,7 @@
         <v>8</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F178" s="1">
         <v>10350001</v>
@@ -7524,7 +7559,7 @@
         <v>9</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F179" s="1">
         <v>10350001</v>
@@ -7553,7 +7588,7 @@
         <v>10</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F180" s="1">
         <v>10350001</v>
@@ -7582,7 +7617,7 @@
         <v>0</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F181" s="1">
         <v>10350002</v>
@@ -7606,7 +7641,7 @@
         <v>1</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F182" s="1">
         <v>10350002</v>
@@ -7633,7 +7668,7 @@
         <v>2</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F183" s="1">
         <v>10350002</v>
@@ -7660,7 +7695,7 @@
         <v>3</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F184" s="1">
         <v>10350002</v>
@@ -7687,7 +7722,7 @@
         <v>4</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F185" s="1">
         <v>10350002</v>
@@ -7714,7 +7749,7 @@
         <v>5</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F186" s="1">
         <v>10350002</v>
@@ -7741,7 +7776,7 @@
         <v>6</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F187" s="1">
         <v>10350002</v>
@@ -7768,7 +7803,7 @@
         <v>7</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F188" s="1">
         <v>10350002</v>
@@ -7795,7 +7830,7 @@
         <v>8</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F189" s="1">
         <v>10350002</v>
@@ -7822,7 +7857,7 @@
         <v>9</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F190" s="1">
         <v>10350002</v>
@@ -7849,7 +7884,7 @@
         <v>10</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F191" s="1">
         <v>10350002</v>
@@ -7876,7 +7911,7 @@
         <v>0</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F192" s="1">
         <v>10350003</v>
@@ -7900,7 +7935,7 @@
         <v>1</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F193" s="1">
         <v>10350003</v>
@@ -7927,7 +7962,7 @@
         <v>2</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F194" s="1">
         <v>10350003</v>
@@ -7954,7 +7989,7 @@
         <v>3</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F195" s="1">
         <v>10350003</v>
@@ -7981,7 +8016,7 @@
         <v>4</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F196" s="1">
         <v>10350003</v>
@@ -8008,7 +8043,7 @@
         <v>5</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F197" s="1">
         <v>10350003</v>
@@ -8035,7 +8070,7 @@
         <v>6</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F198" s="1">
         <v>10350003</v>
@@ -8062,7 +8097,7 @@
         <v>7</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F199" s="1">
         <v>10350003</v>
@@ -8089,7 +8124,7 @@
         <v>8</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F200" s="1">
         <v>10350003</v>
@@ -8116,7 +8151,7 @@
         <v>9</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F201" s="1">
         <v>10350003</v>
@@ -8143,7 +8178,7 @@
         <v>10</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F202" s="1">
         <v>10350003</v>
@@ -8170,7 +8205,7 @@
         <v>0</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F203" s="1">
         <v>10350004</v>
@@ -8194,7 +8229,7 @@
         <v>1</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F204" s="1">
         <v>10350004</v>
@@ -8221,7 +8256,7 @@
         <v>2</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F205" s="1">
         <v>10350004</v>
@@ -8248,7 +8283,7 @@
         <v>3</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F206" s="1">
         <v>10350004</v>
@@ -8275,7 +8310,7 @@
         <v>4</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F207" s="1">
         <v>10350004</v>
@@ -8302,7 +8337,7 @@
         <v>5</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F208" s="1">
         <v>10350004</v>
@@ -8329,7 +8364,7 @@
         <v>6</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F209" s="1">
         <v>10350004</v>
@@ -8356,7 +8391,7 @@
         <v>7</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F210" s="1">
         <v>10350004</v>
@@ -8383,7 +8418,7 @@
         <v>8</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F211" s="1">
         <v>10350004</v>
@@ -8410,7 +8445,7 @@
         <v>9</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F212" s="1">
         <v>10350004</v>
@@ -8437,7 +8472,7 @@
         <v>10</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F213" s="1">
         <v>10350004</v>
@@ -8464,7 +8499,7 @@
         <v>0</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F214" s="1">
         <v>10350005</v>
@@ -8488,7 +8523,7 @@
         <v>1</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F215" s="1">
         <v>10350005</v>
@@ -8498,7 +8533,7 @@
       </c>
       <c r="H215" s="2"/>
       <c r="K215" s="1" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
     </row>
     <row r="216" spans="1:11">
@@ -8515,7 +8550,7 @@
         <v>2</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F216" s="1">
         <v>10350005</v>
@@ -8525,7 +8560,7 @@
       </c>
       <c r="H216" s="2"/>
       <c r="K216" s="1" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
     </row>
     <row r="217" spans="1:11">
@@ -8542,7 +8577,7 @@
         <v>3</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F217" s="1">
         <v>10350005</v>
@@ -8552,7 +8587,7 @@
       </c>
       <c r="H217" s="2"/>
       <c r="K217" s="1" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
     </row>
     <row r="218" spans="1:11">
@@ -8569,7 +8604,7 @@
         <v>4</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F218" s="1">
         <v>10350005</v>
@@ -8579,7 +8614,7 @@
       </c>
       <c r="H218" s="2"/>
       <c r="K218" s="1" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
     </row>
     <row r="219" spans="1:11">
@@ -8596,7 +8631,7 @@
         <v>5</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F219" s="1">
         <v>10350005</v>
@@ -8606,7 +8641,7 @@
       </c>
       <c r="H219" s="2"/>
       <c r="K219" s="1" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="220" spans="1:11">
@@ -8623,7 +8658,7 @@
         <v>6</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F220" s="1">
         <v>10350005</v>
@@ -8633,7 +8668,7 @@
       </c>
       <c r="H220" s="2"/>
       <c r="K220" s="1" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
     </row>
     <row r="221" spans="1:11">
@@ -8650,7 +8685,7 @@
         <v>7</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F221" s="1">
         <v>10350005</v>
@@ -8660,7 +8695,7 @@
       </c>
       <c r="H221" s="2"/>
       <c r="K221" s="1" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="222" spans="1:11">
@@ -8677,7 +8712,7 @@
         <v>8</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F222" s="1">
         <v>10350005</v>
@@ -8687,7 +8722,7 @@
       </c>
       <c r="H222" s="2"/>
       <c r="K222" s="1" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
     </row>
     <row r="223" spans="1:11">
@@ -8704,7 +8739,7 @@
         <v>9</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F223" s="1">
         <v>10350005</v>
@@ -8714,7 +8749,7 @@
       </c>
       <c r="H223" s="2"/>
       <c r="K223" s="1" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="224" spans="1:11">
@@ -8731,7 +8766,7 @@
         <v>10</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F224" s="1">
         <v>10350005</v>
@@ -8741,7 +8776,7 @@
       </c>
       <c r="H224" s="2"/>
       <c r="K224" s="1" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="225" spans="1:15">
@@ -8758,7 +8793,7 @@
         <v>0</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F225" s="1">
         <v>10350006</v>
@@ -8782,7 +8817,7 @@
         <v>1</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F226" s="1">
         <v>10350006</v>
@@ -8795,7 +8830,7 @@
         <v>45</v>
       </c>
       <c r="M226" s="1" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row r="227" spans="1:15">
@@ -8812,7 +8847,7 @@
         <v>2</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F227" s="1">
         <v>10350006</v>
@@ -8825,7 +8860,7 @@
         <v>45</v>
       </c>
       <c r="M227" s="1" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
     </row>
     <row r="228" spans="1:15">
@@ -8842,7 +8877,7 @@
         <v>3</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F228" s="1">
         <v>10350006</v>
@@ -8855,7 +8890,7 @@
         <v>45</v>
       </c>
       <c r="M228" s="1" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
     </row>
     <row r="229" spans="1:15">
@@ -8872,7 +8907,7 @@
         <v>4</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F229" s="1">
         <v>10350006</v>
@@ -8885,7 +8920,7 @@
         <v>45</v>
       </c>
       <c r="M229" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="230" spans="1:15">
@@ -8902,7 +8937,7 @@
         <v>5</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F230" s="1">
         <v>10350006</v>
@@ -8915,7 +8950,7 @@
         <v>45</v>
       </c>
       <c r="M230" s="1" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="231" spans="1:15">
@@ -8932,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F231" s="1">
         <v>10350006</v>
@@ -8945,7 +8980,7 @@
         <v>45</v>
       </c>
       <c r="M231" s="1" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
     </row>
     <row r="232" spans="1:15">
@@ -8962,7 +8997,7 @@
         <v>7</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F232" s="1">
         <v>10350006</v>
@@ -8975,7 +9010,7 @@
         <v>45</v>
       </c>
       <c r="M232" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
     </row>
     <row r="233" spans="1:15">
@@ -8992,7 +9027,7 @@
         <v>8</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F233" s="1">
         <v>10350006</v>
@@ -9005,7 +9040,7 @@
         <v>45</v>
       </c>
       <c r="M233" s="1" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="234" spans="1:15">
@@ -9022,7 +9057,7 @@
         <v>9</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F234" s="1">
         <v>10350006</v>
@@ -9035,7 +9070,7 @@
         <v>45</v>
       </c>
       <c r="M234" s="1" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
     </row>
     <row r="235" spans="1:15">
@@ -9052,7 +9087,7 @@
         <v>10</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F235" s="1">
         <v>10350006</v>
@@ -9065,7 +9100,7 @@
         <v>45</v>
       </c>
       <c r="M235" s="1" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="236" spans="1:15">
@@ -9082,7 +9117,7 @@
         <v>0</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F236" s="1">
         <v>10350007</v>
@@ -9106,7 +9141,7 @@
         <v>1</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F237" s="1">
         <v>10350007</v>
@@ -9116,7 +9151,7 @@
       </c>
       <c r="H237" s="2"/>
       <c r="O237" s="1" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="238" spans="1:15">
@@ -9133,7 +9168,7 @@
         <v>2</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F238" s="1">
         <v>10350007</v>
@@ -9143,7 +9178,7 @@
       </c>
       <c r="H238" s="2"/>
       <c r="O238" s="1" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="239" spans="1:15">
@@ -9160,7 +9195,7 @@
         <v>3</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F239" s="1">
         <v>10350007</v>
@@ -9170,7 +9205,7 @@
       </c>
       <c r="H239" s="2"/>
       <c r="O239" s="1" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
     </row>
     <row r="240" spans="1:15">
@@ -9187,7 +9222,7 @@
         <v>4</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F240" s="1">
         <v>10350007</v>
@@ -9197,7 +9232,7 @@
       </c>
       <c r="H240" s="2"/>
       <c r="O240" s="1" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
     </row>
     <row r="241" spans="1:15">
@@ -9214,7 +9249,7 @@
         <v>5</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F241" s="1">
         <v>10350007</v>
@@ -9224,7 +9259,7 @@
       </c>
       <c r="H241" s="2"/>
       <c r="O241" s="1" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
     </row>
     <row r="242" spans="1:15">
@@ -9241,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F242" s="1">
         <v>10350007</v>
@@ -9251,7 +9286,7 @@
       </c>
       <c r="H242" s="2"/>
       <c r="O242" s="1" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
     </row>
     <row r="243" spans="1:15">
@@ -9268,7 +9303,7 @@
         <v>7</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F243" s="1">
         <v>10350007</v>
@@ -9278,7 +9313,7 @@
       </c>
       <c r="H243" s="2"/>
       <c r="O243" s="1" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="244" spans="1:15">
@@ -9295,7 +9330,7 @@
         <v>8</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F244" s="1">
         <v>10350007</v>
@@ -9305,7 +9340,7 @@
       </c>
       <c r="H244" s="2"/>
       <c r="O244" s="1" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
     </row>
     <row r="245" spans="1:15">
@@ -9322,7 +9357,7 @@
         <v>9</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F245" s="1">
         <v>10350007</v>
@@ -9332,7 +9367,7 @@
       </c>
       <c r="H245" s="2"/>
       <c r="O245" s="1" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
     </row>
     <row r="246" spans="1:15">
@@ -9349,7 +9384,7 @@
         <v>10</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F246" s="1">
         <v>10350007</v>
@@ -9359,7 +9394,7 @@
       </c>
       <c r="H246" s="2"/>
       <c r="O246" s="1" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="247" spans="1:15">
@@ -9376,7 +9411,7 @@
         <v>0</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F247" s="1">
         <v>10350008</v>
@@ -9400,7 +9435,7 @@
         <v>1</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F248" s="1">
         <v>10350008</v>
@@ -9410,7 +9445,7 @@
       </c>
       <c r="H248" s="2"/>
       <c r="O248" s="1" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
     </row>
     <row r="249" spans="1:15">
@@ -9427,7 +9462,7 @@
         <v>2</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F249" s="1">
         <v>10350008</v>
@@ -9437,7 +9472,7 @@
       </c>
       <c r="H249" s="2"/>
       <c r="O249" s="1" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="250" spans="1:15">
@@ -9454,7 +9489,7 @@
         <v>3</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F250" s="1">
         <v>10350008</v>
@@ -9464,7 +9499,7 @@
       </c>
       <c r="H250" s="2"/>
       <c r="O250" s="1" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
     </row>
     <row r="251" spans="1:15">
@@ -9481,7 +9516,7 @@
         <v>4</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F251" s="1">
         <v>10350008</v>
@@ -9491,7 +9526,7 @@
       </c>
       <c r="H251" s="2"/>
       <c r="O251" s="1" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
     </row>
     <row r="252" spans="1:15">
@@ -9508,7 +9543,7 @@
         <v>5</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F252" s="1">
         <v>10350008</v>
@@ -9518,7 +9553,7 @@
       </c>
       <c r="H252" s="2"/>
       <c r="O252" s="1" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
     </row>
     <row r="253" spans="1:15">
@@ -9535,7 +9570,7 @@
         <v>6</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F253" s="1">
         <v>10350008</v>
@@ -9545,7 +9580,7 @@
       </c>
       <c r="H253" s="2"/>
       <c r="O253" s="1" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
     <row r="254" spans="1:15">
@@ -9562,7 +9597,7 @@
         <v>7</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F254" s="1">
         <v>10350008</v>
@@ -9572,7 +9607,7 @@
       </c>
       <c r="H254" s="2"/>
       <c r="O254" s="1" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
     </row>
     <row r="255" spans="1:15">
@@ -9589,7 +9624,7 @@
         <v>8</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F255" s="1">
         <v>10350008</v>
@@ -9599,7 +9634,7 @@
       </c>
       <c r="H255" s="2"/>
       <c r="O255" s="1" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
     </row>
     <row r="256" spans="1:15">
@@ -9616,7 +9651,7 @@
         <v>9</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F256" s="1">
         <v>10350008</v>
@@ -9626,7 +9661,7 @@
       </c>
       <c r="H256" s="2"/>
       <c r="O256" s="1" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="257" spans="1:15">
@@ -9643,7 +9678,7 @@
         <v>10</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F257" s="1">
         <v>10350008</v>
@@ -9653,7 +9688,7 @@
       </c>
       <c r="H257" s="2"/>
       <c r="O257" s="1" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
     </row>
     <row r="258" spans="1:15">
@@ -9670,7 +9705,7 @@
         <v>0</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F258" s="1">
         <v>10350009</v>
@@ -9694,7 +9729,7 @@
         <v>1</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F259" s="1">
         <v>10350009</v>
@@ -9704,10 +9739,10 @@
       </c>
       <c r="H259" s="2"/>
       <c r="L259" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M259" s="1" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
     </row>
     <row r="260" spans="1:15">
@@ -9724,7 +9759,7 @@
         <v>2</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F260" s="1">
         <v>10350009</v>
@@ -9734,10 +9769,10 @@
       </c>
       <c r="H260" s="2"/>
       <c r="L260" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M260" s="1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="261" spans="1:15">
@@ -9754,7 +9789,7 @@
         <v>3</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F261" s="1">
         <v>10350009</v>
@@ -9764,10 +9799,10 @@
       </c>
       <c r="H261" s="2"/>
       <c r="L261" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M261" s="1" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="262" spans="1:15">
@@ -9784,7 +9819,7 @@
         <v>4</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F262" s="1">
         <v>10350009</v>
@@ -9794,10 +9829,10 @@
       </c>
       <c r="H262" s="2"/>
       <c r="L262" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M262" s="1" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="263" spans="1:15">
@@ -9814,7 +9849,7 @@
         <v>5</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F263" s="1">
         <v>10350009</v>
@@ -9824,10 +9859,10 @@
       </c>
       <c r="H263" s="2"/>
       <c r="L263" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M263" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="264" spans="1:15">
@@ -9844,7 +9879,7 @@
         <v>6</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F264" s="1">
         <v>10350009</v>
@@ -9854,10 +9889,10 @@
       </c>
       <c r="H264" s="2"/>
       <c r="L264" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M264" s="1" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="265" spans="1:15">
@@ -9874,7 +9909,7 @@
         <v>7</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F265" s="1">
         <v>10350009</v>
@@ -9884,10 +9919,10 @@
       </c>
       <c r="H265" s="2"/>
       <c r="L265" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M265" s="1" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
     <row r="266" spans="1:15">
@@ -9904,7 +9939,7 @@
         <v>8</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F266" s="1">
         <v>10350009</v>
@@ -9914,10 +9949,10 @@
       </c>
       <c r="H266" s="2"/>
       <c r="L266" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M266" s="1" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="267" spans="1:15">
@@ -9934,7 +9969,7 @@
         <v>9</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F267" s="1">
         <v>10350009</v>
@@ -9944,10 +9979,10 @@
       </c>
       <c r="H267" s="2"/>
       <c r="L267" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M267" s="1" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="268" spans="1:15">
@@ -9964,7 +9999,7 @@
         <v>10</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F268" s="1">
         <v>10350009</v>
@@ -9974,10 +10009,10 @@
       </c>
       <c r="H268" s="2"/>
       <c r="L268" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M268" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="269" spans="1:15">
@@ -9994,7 +10029,7 @@
         <v>0</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F269" s="1">
         <v>10170001</v>
@@ -10018,7 +10053,7 @@
         <v>1</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F270" s="1">
         <v>10170001</v>
@@ -10047,7 +10082,7 @@
         <v>2</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F271" s="1">
         <v>10170001</v>
@@ -10076,7 +10111,7 @@
         <v>3</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F272" s="1">
         <v>10170001</v>
@@ -10105,7 +10140,7 @@
         <v>4</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F273" s="1">
         <v>10170001</v>
@@ -10134,7 +10169,7 @@
         <v>5</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F274" s="1">
         <v>10170001</v>
@@ -10163,7 +10198,7 @@
         <v>6</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F275" s="1">
         <v>10170001</v>
@@ -10192,7 +10227,7 @@
         <v>7</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F276" s="1">
         <v>10170001</v>
@@ -10221,7 +10256,7 @@
         <v>8</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F277" s="1">
         <v>10170001</v>
@@ -10250,7 +10285,7 @@
         <v>9</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F278" s="1">
         <v>10170001</v>
@@ -10279,7 +10314,7 @@
         <v>10</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F279" s="1">
         <v>10170001</v>
@@ -10308,7 +10343,7 @@
         <v>0</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F280" s="1">
         <v>10170002</v>
@@ -10332,7 +10367,7 @@
         <v>1</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F281" s="1">
         <v>10170002</v>
@@ -10359,7 +10394,7 @@
         <v>2</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F282" s="1">
         <v>10170002</v>
@@ -10386,7 +10421,7 @@
         <v>3</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F283" s="1">
         <v>10170002</v>
@@ -10413,7 +10448,7 @@
         <v>4</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F284" s="1">
         <v>10170002</v>
@@ -10440,7 +10475,7 @@
         <v>5</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F285" s="1">
         <v>10170002</v>
@@ -10467,7 +10502,7 @@
         <v>6</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F286" s="1">
         <v>10170002</v>
@@ -10494,7 +10529,7 @@
         <v>7</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F287" s="1">
         <v>10170002</v>
@@ -10521,7 +10556,7 @@
         <v>8</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F288" s="1">
         <v>10170002</v>
@@ -10548,7 +10583,7 @@
         <v>9</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F289" s="1">
         <v>10170002</v>
@@ -10575,7 +10610,7 @@
         <v>10</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F290" s="1">
         <v>10170002</v>
@@ -10602,7 +10637,7 @@
         <v>0</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F291" s="1">
         <v>10170003</v>
@@ -10626,7 +10661,7 @@
         <v>1</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F292" s="1">
         <v>10170003</v>
@@ -10636,7 +10671,7 @@
       </c>
       <c r="H292" s="2"/>
       <c r="K292" s="1" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
     </row>
     <row r="293" spans="1:11">
@@ -10653,7 +10688,7 @@
         <v>2</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F293" s="1">
         <v>10170003</v>
@@ -10663,7 +10698,7 @@
       </c>
       <c r="H293" s="2"/>
       <c r="K293" s="1" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
     </row>
     <row r="294" spans="1:11">
@@ -10680,7 +10715,7 @@
         <v>3</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F294" s="1">
         <v>10170003</v>
@@ -10690,7 +10725,7 @@
       </c>
       <c r="H294" s="2"/>
       <c r="K294" s="1" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
     </row>
     <row r="295" spans="1:11">
@@ -10707,7 +10742,7 @@
         <v>4</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F295" s="1">
         <v>10170003</v>
@@ -10717,7 +10752,7 @@
       </c>
       <c r="H295" s="2"/>
       <c r="K295" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
     </row>
     <row r="296" spans="1:11">
@@ -10734,7 +10769,7 @@
         <v>5</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F296" s="1">
         <v>10170003</v>
@@ -10744,7 +10779,7 @@
       </c>
       <c r="H296" s="2"/>
       <c r="K296" s="1" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
     </row>
     <row r="297" spans="1:11">
@@ -10761,7 +10796,7 @@
         <v>6</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F297" s="1">
         <v>10170003</v>
@@ -10771,7 +10806,7 @@
       </c>
       <c r="H297" s="2"/>
       <c r="K297" s="1" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="298" spans="1:11">
@@ -10788,7 +10823,7 @@
         <v>7</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F298" s="1">
         <v>10170003</v>
@@ -10798,7 +10833,7 @@
       </c>
       <c r="H298" s="2"/>
       <c r="K298" s="1" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
     </row>
     <row r="299" spans="1:11">
@@ -10815,7 +10850,7 @@
         <v>8</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F299" s="1">
         <v>10170003</v>
@@ -10825,7 +10860,7 @@
       </c>
       <c r="H299" s="2"/>
       <c r="K299" s="1" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
     </row>
     <row r="300" spans="1:11">
@@ -10842,7 +10877,7 @@
         <v>9</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F300" s="1">
         <v>10170003</v>
@@ -10852,7 +10887,7 @@
       </c>
       <c r="H300" s="2"/>
       <c r="K300" s="1" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
     </row>
     <row r="301" spans="1:11">
@@ -10869,7 +10904,7 @@
         <v>10</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F301" s="1">
         <v>10170003</v>
@@ -10879,7 +10914,7 @@
       </c>
       <c r="H301" s="2"/>
       <c r="K301" s="1" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
     </row>
     <row r="302" spans="1:11">
@@ -10896,7 +10931,7 @@
         <v>0</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F302" s="1">
         <v>10170004</v>
@@ -10920,7 +10955,7 @@
         <v>1</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F303" s="1">
         <v>10170004</v>
@@ -10930,7 +10965,7 @@
       </c>
       <c r="H303" s="2"/>
       <c r="K303" s="1" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="304" spans="1:11">
@@ -10947,7 +10982,7 @@
         <v>2</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F304" s="1">
         <v>10170004</v>
@@ -10957,7 +10992,7 @@
       </c>
       <c r="H304" s="2"/>
       <c r="K304" s="1" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
     </row>
     <row r="305" spans="1:11">
@@ -10974,7 +11009,7 @@
         <v>3</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F305" s="1">
         <v>10170004</v>
@@ -10984,7 +11019,7 @@
       </c>
       <c r="H305" s="2"/>
       <c r="K305" s="1" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
     </row>
     <row r="306" spans="1:11">
@@ -11001,7 +11036,7 @@
         <v>4</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F306" s="1">
         <v>10170004</v>
@@ -11011,7 +11046,7 @@
       </c>
       <c r="H306" s="2"/>
       <c r="K306" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
     </row>
     <row r="307" spans="1:11">
@@ -11028,7 +11063,7 @@
         <v>5</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F307" s="1">
         <v>10170004</v>
@@ -11038,7 +11073,7 @@
       </c>
       <c r="H307" s="2"/>
       <c r="K307" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
     </row>
     <row r="308" spans="1:11">
@@ -11055,7 +11090,7 @@
         <v>6</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F308" s="1">
         <v>10170004</v>
@@ -11065,7 +11100,7 @@
       </c>
       <c r="H308" s="2"/>
       <c r="K308" s="1" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
     </row>
     <row r="309" spans="1:11">
@@ -11082,7 +11117,7 @@
         <v>7</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F309" s="1">
         <v>10170004</v>
@@ -11092,7 +11127,7 @@
       </c>
       <c r="H309" s="2"/>
       <c r="K309" s="1" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
     </row>
     <row r="310" spans="1:11">
@@ -11109,7 +11144,7 @@
         <v>8</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F310" s="1">
         <v>10170004</v>
@@ -11119,7 +11154,7 @@
       </c>
       <c r="H310" s="2"/>
       <c r="K310" s="1" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
     </row>
     <row r="311" spans="1:11">
@@ -11136,7 +11171,7 @@
         <v>9</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F311" s="1">
         <v>10170004</v>
@@ -11146,7 +11181,7 @@
       </c>
       <c r="H311" s="2"/>
       <c r="K311" s="1" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
     </row>
     <row r="312" spans="1:11">
@@ -11163,7 +11198,7 @@
         <v>10</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F312" s="1">
         <v>10170004</v>
@@ -11173,7 +11208,7 @@
       </c>
       <c r="H312" s="2"/>
       <c r="K312" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
     </row>
     <row r="313" spans="1:11">
@@ -11190,7 +11225,7 @@
         <v>0</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F313" s="1">
         <v>10170005</v>
@@ -11214,7 +11249,7 @@
         <v>1</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F314" s="1">
         <v>10170005</v>
@@ -11224,7 +11259,7 @@
       </c>
       <c r="H314" s="2"/>
       <c r="K314" s="1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
     </row>
     <row r="315" spans="1:11">
@@ -11241,7 +11276,7 @@
         <v>2</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F315" s="1">
         <v>10170005</v>
@@ -11251,7 +11286,7 @@
       </c>
       <c r="H315" s="2"/>
       <c r="K315" s="1" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
     </row>
     <row r="316" spans="1:11">
@@ -11268,7 +11303,7 @@
         <v>3</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F316" s="1">
         <v>10170005</v>
@@ -11278,7 +11313,7 @@
       </c>
       <c r="H316" s="2"/>
       <c r="K316" s="1" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
     </row>
     <row r="317" spans="1:11">
@@ -11295,7 +11330,7 @@
         <v>4</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F317" s="1">
         <v>10170005</v>
@@ -11305,7 +11340,7 @@
       </c>
       <c r="H317" s="2"/>
       <c r="K317" s="1" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
     </row>
     <row r="318" spans="1:11">
@@ -11322,7 +11357,7 @@
         <v>5</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F318" s="1">
         <v>10170005</v>
@@ -11332,7 +11367,7 @@
       </c>
       <c r="H318" s="2"/>
       <c r="K318" s="1" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
     </row>
     <row r="319" spans="1:11">
@@ -11349,7 +11384,7 @@
         <v>6</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F319" s="1">
         <v>10170005</v>
@@ -11359,7 +11394,7 @@
       </c>
       <c r="H319" s="2"/>
       <c r="K319" s="1" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
     </row>
     <row r="320" spans="1:11">
@@ -11376,7 +11411,7 @@
         <v>7</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F320" s="1">
         <v>10170005</v>
@@ -11386,7 +11421,7 @@
       </c>
       <c r="H320" s="2"/>
       <c r="K320" s="1" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
     </row>
     <row r="321" spans="1:15">
@@ -11403,7 +11438,7 @@
         <v>8</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F321" s="1">
         <v>10170005</v>
@@ -11413,7 +11448,7 @@
       </c>
       <c r="H321" s="2"/>
       <c r="K321" s="1" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
     </row>
     <row r="322" spans="1:15">
@@ -11430,7 +11465,7 @@
         <v>9</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F322" s="1">
         <v>10170005</v>
@@ -11440,7 +11475,7 @@
       </c>
       <c r="H322" s="2"/>
       <c r="K322" s="1" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
     </row>
     <row r="323" spans="1:15">
@@ -11457,7 +11492,7 @@
         <v>10</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F323" s="1">
         <v>10170005</v>
@@ -11467,7 +11502,7 @@
       </c>
       <c r="H323" s="2"/>
       <c r="K323" s="1" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
     </row>
     <row r="324" spans="1:15">
@@ -11484,7 +11519,7 @@
         <v>0</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F324" s="1">
         <v>10170006</v>
@@ -11508,7 +11543,7 @@
         <v>1</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F325" s="1">
         <v>10170006</v>
@@ -11521,7 +11556,7 @@
         <v>45</v>
       </c>
       <c r="M325" s="1" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
     </row>
     <row r="326" spans="1:15">
@@ -11538,7 +11573,7 @@
         <v>2</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F326" s="1">
         <v>10170006</v>
@@ -11551,7 +11586,7 @@
         <v>45</v>
       </c>
       <c r="M326" s="1" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
     </row>
     <row r="327" spans="1:15">
@@ -11568,7 +11603,7 @@
         <v>3</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F327" s="1">
         <v>10170006</v>
@@ -11581,7 +11616,7 @@
         <v>45</v>
       </c>
       <c r="M327" s="1" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
     </row>
     <row r="328" spans="1:15">
@@ -11598,7 +11633,7 @@
         <v>4</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F328" s="1">
         <v>10170006</v>
@@ -11611,7 +11646,7 @@
         <v>45</v>
       </c>
       <c r="M328" s="1" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
     </row>
     <row r="329" spans="1:15">
@@ -11628,7 +11663,7 @@
         <v>5</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F329" s="1">
         <v>10170006</v>
@@ -11641,7 +11676,7 @@
         <v>45</v>
       </c>
       <c r="M329" s="1" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
     </row>
     <row r="330" spans="1:15">
@@ -11658,7 +11693,7 @@
         <v>6</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F330" s="1">
         <v>10170006</v>
@@ -11671,7 +11706,7 @@
         <v>45</v>
       </c>
       <c r="M330" s="1" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
     </row>
     <row r="331" spans="1:15">
@@ -11688,7 +11723,7 @@
         <v>7</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F331" s="1">
         <v>10170006</v>
@@ -11701,7 +11736,7 @@
         <v>45</v>
       </c>
       <c r="M331" s="1" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
     </row>
     <row r="332" spans="1:15">
@@ -11718,7 +11753,7 @@
         <v>8</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F332" s="1">
         <v>10170006</v>
@@ -11731,7 +11766,7 @@
         <v>45</v>
       </c>
       <c r="M332" s="1" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
     <row r="333" spans="1:15">
@@ -11748,7 +11783,7 @@
         <v>9</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F333" s="1">
         <v>10170006</v>
@@ -11761,7 +11796,7 @@
         <v>45</v>
       </c>
       <c r="M333" s="1" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
     </row>
     <row r="334" spans="1:15">
@@ -11778,7 +11813,7 @@
         <v>10</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F334" s="1">
         <v>10170006</v>
@@ -11791,7 +11826,7 @@
         <v>45</v>
       </c>
       <c r="M334" s="1" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
     </row>
     <row r="335" spans="1:15">
@@ -11808,7 +11843,7 @@
         <v>0</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F335" s="1">
         <v>10170007</v>
@@ -11832,7 +11867,7 @@
         <v>1</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F336" s="1">
         <v>10170007</v>
@@ -11842,7 +11877,7 @@
       </c>
       <c r="H336" s="2"/>
       <c r="O336" s="1" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
     </row>
     <row r="337" spans="1:15">
@@ -11859,7 +11894,7 @@
         <v>2</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F337" s="1">
         <v>10170007</v>
@@ -11869,7 +11904,7 @@
       </c>
       <c r="H337" s="2"/>
       <c r="O337" s="1" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
     </row>
     <row r="338" spans="1:15">
@@ -11886,7 +11921,7 @@
         <v>3</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F338" s="1">
         <v>10170007</v>
@@ -11896,7 +11931,7 @@
       </c>
       <c r="H338" s="2"/>
       <c r="O338" s="1" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
     </row>
     <row r="339" spans="1:15">
@@ -11913,7 +11948,7 @@
         <v>4</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F339" s="1">
         <v>10170007</v>
@@ -11923,7 +11958,7 @@
       </c>
       <c r="H339" s="2"/>
       <c r="O339" s="1" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
     </row>
     <row r="340" spans="1:15">
@@ -11940,7 +11975,7 @@
         <v>5</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F340" s="1">
         <v>10170007</v>
@@ -11950,7 +11985,7 @@
       </c>
       <c r="H340" s="2"/>
       <c r="O340" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="341" spans="1:15">
@@ -11967,7 +12002,7 @@
         <v>6</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F341" s="1">
         <v>10170007</v>
@@ -11977,7 +12012,7 @@
       </c>
       <c r="H341" s="2"/>
       <c r="O341" s="1" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
     <row r="342" spans="1:15">
@@ -11994,7 +12029,7 @@
         <v>7</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F342" s="1">
         <v>10170007</v>
@@ -12004,7 +12039,7 @@
       </c>
       <c r="H342" s="2"/>
       <c r="O342" s="1" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
     </row>
     <row r="343" spans="1:15">
@@ -12021,7 +12056,7 @@
         <v>8</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F343" s="1">
         <v>10170007</v>
@@ -12031,7 +12066,7 @@
       </c>
       <c r="H343" s="2"/>
       <c r="O343" s="1" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
     </row>
     <row r="344" spans="1:15">
@@ -12048,7 +12083,7 @@
         <v>9</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F344" s="1">
         <v>10170007</v>
@@ -12058,7 +12093,7 @@
       </c>
       <c r="H344" s="2"/>
       <c r="O344" s="1" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
     </row>
     <row r="345" spans="1:15">
@@ -12075,7 +12110,7 @@
         <v>10</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F345" s="1">
         <v>10170007</v>
@@ -12085,7 +12120,7 @@
       </c>
       <c r="H345" s="2"/>
       <c r="O345" s="1" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
     </row>
     <row r="346" spans="1:15">
@@ -12102,7 +12137,7 @@
         <v>0</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F346" s="1">
         <v>10170008</v>
@@ -12126,7 +12161,7 @@
         <v>1</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F347" s="1">
         <v>10170008</v>
@@ -12136,7 +12171,7 @@
       </c>
       <c r="H347" s="2"/>
       <c r="O347" s="1" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
     </row>
     <row r="348" spans="1:15">
@@ -12153,7 +12188,7 @@
         <v>2</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F348" s="1">
         <v>10170008</v>
@@ -12163,7 +12198,7 @@
       </c>
       <c r="H348" s="2"/>
       <c r="O348" s="1" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
     </row>
     <row r="349" spans="1:15">
@@ -12180,7 +12215,7 @@
         <v>3</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F349" s="1">
         <v>10170008</v>
@@ -12190,7 +12225,7 @@
       </c>
       <c r="H349" s="2"/>
       <c r="O349" s="1" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
     </row>
     <row r="350" spans="1:15">
@@ -12207,7 +12242,7 @@
         <v>4</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F350" s="1">
         <v>10170008</v>
@@ -12217,7 +12252,7 @@
       </c>
       <c r="H350" s="2"/>
       <c r="O350" s="1" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
     </row>
     <row r="351" spans="1:15">
@@ -12234,7 +12269,7 @@
         <v>5</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F351" s="1">
         <v>10170008</v>
@@ -12244,7 +12279,7 @@
       </c>
       <c r="H351" s="2"/>
       <c r="O351" s="1" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
     </row>
     <row r="352" spans="1:15">
@@ -12261,7 +12296,7 @@
         <v>6</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F352" s="1">
         <v>10170008</v>
@@ -12271,7 +12306,7 @@
       </c>
       <c r="H352" s="2"/>
       <c r="O352" s="1" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
     </row>
     <row r="353" spans="1:15">
@@ -12288,7 +12323,7 @@
         <v>7</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F353" s="1">
         <v>10170008</v>
@@ -12298,7 +12333,7 @@
       </c>
       <c r="H353" s="2"/>
       <c r="O353" s="1" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
     </row>
     <row r="354" spans="1:15">
@@ -12315,7 +12350,7 @@
         <v>8</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F354" s="1">
         <v>10170008</v>
@@ -12325,7 +12360,7 @@
       </c>
       <c r="H354" s="2"/>
       <c r="O354" s="1" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
     </row>
     <row r="355" spans="1:15">
@@ -12342,7 +12377,7 @@
         <v>9</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F355" s="1">
         <v>10170008</v>
@@ -12352,7 +12387,7 @@
       </c>
       <c r="H355" s="2"/>
       <c r="O355" s="1" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
     </row>
     <row r="356" spans="1:15">
@@ -12369,7 +12404,7 @@
         <v>10</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F356" s="1">
         <v>10170008</v>
@@ -12379,7 +12414,7 @@
       </c>
       <c r="H356" s="2"/>
       <c r="O356" s="1" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
     </row>
     <row r="357" spans="1:15">
@@ -12396,7 +12431,7 @@
         <v>0</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F357" s="1">
         <v>10170009</v>
@@ -12420,7 +12455,7 @@
         <v>1</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F358" s="1">
         <v>10170009</v>
@@ -12430,7 +12465,7 @@
       </c>
       <c r="H358" s="2"/>
       <c r="O358" s="1" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
     </row>
     <row r="359" spans="1:15">
@@ -12447,7 +12482,7 @@
         <v>2</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F359" s="1">
         <v>10170009</v>
@@ -12457,7 +12492,7 @@
       </c>
       <c r="H359" s="2"/>
       <c r="O359" s="1" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
     </row>
     <row r="360" spans="1:15">
@@ -12474,7 +12509,7 @@
         <v>3</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F360" s="1">
         <v>10170009</v>
@@ -12484,7 +12519,7 @@
       </c>
       <c r="H360" s="2"/>
       <c r="O360" s="1" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
     </row>
     <row r="361" spans="1:15">
@@ -12501,7 +12536,7 @@
         <v>4</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F361" s="1">
         <v>10170009</v>
@@ -12511,7 +12546,7 @@
       </c>
       <c r="H361" s="2"/>
       <c r="O361" s="1" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
     </row>
     <row r="362" spans="1:15">
@@ -12528,7 +12563,7 @@
         <v>5</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F362" s="1">
         <v>10170009</v>
@@ -12538,7 +12573,7 @@
       </c>
       <c r="H362" s="2"/>
       <c r="O362" s="1" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
     </row>
     <row r="363" spans="1:15">
@@ -12555,7 +12590,7 @@
         <v>6</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F363" s="1">
         <v>10170009</v>
@@ -12565,7 +12600,7 @@
       </c>
       <c r="H363" s="2"/>
       <c r="O363" s="1" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
     </row>
     <row r="364" spans="1:15">
@@ -12582,7 +12617,7 @@
         <v>7</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F364" s="1">
         <v>10170009</v>
@@ -12592,7 +12627,7 @@
       </c>
       <c r="H364" s="2"/>
       <c r="O364" s="1" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
     </row>
     <row r="365" spans="1:15">
@@ -12609,7 +12644,7 @@
         <v>8</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F365" s="1">
         <v>10170009</v>
@@ -12619,7 +12654,7 @@
       </c>
       <c r="H365" s="2"/>
       <c r="O365" s="1" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
     </row>
     <row r="366" spans="1:15">
@@ -12636,7 +12671,7 @@
         <v>9</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F366" s="1">
         <v>10170009</v>
@@ -12646,7 +12681,7 @@
       </c>
       <c r="H366" s="2"/>
       <c r="O366" s="1" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
     </row>
     <row r="367" spans="1:15">
@@ -12663,7 +12698,7 @@
         <v>10</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F367" s="1">
         <v>10170009</v>
@@ -12673,7 +12708,7 @@
       </c>
       <c r="H367" s="2"/>
       <c r="O367" s="1" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
     </row>
     <row r="368" spans="1:15">
@@ -12690,7 +12725,7 @@
         <v>0</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F368" s="1">
         <v>10170010</v>
@@ -12714,7 +12749,7 @@
         <v>1</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F369" s="1">
         <v>10170010</v>
@@ -12724,10 +12759,10 @@
       </c>
       <c r="H369" s="2"/>
       <c r="L369" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M369" s="1" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
     </row>
     <row r="370" spans="1:13">
@@ -12744,7 +12779,7 @@
         <v>2</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F370" s="1">
         <v>10170010</v>
@@ -12754,10 +12789,10 @@
       </c>
       <c r="H370" s="2"/>
       <c r="L370" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M370" s="1" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="371" spans="1:13">
@@ -12774,7 +12809,7 @@
         <v>3</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F371" s="1">
         <v>10170010</v>
@@ -12784,10 +12819,10 @@
       </c>
       <c r="H371" s="2"/>
       <c r="L371" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M371" s="1" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
     </row>
     <row r="372" spans="1:13">
@@ -12804,7 +12839,7 @@
         <v>4</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F372" s="1">
         <v>10170010</v>
@@ -12814,10 +12849,10 @@
       </c>
       <c r="H372" s="2"/>
       <c r="L372" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M372" s="1" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
     </row>
     <row r="373" spans="1:13">
@@ -12834,7 +12869,7 @@
         <v>5</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F373" s="1">
         <v>10170010</v>
@@ -12844,10 +12879,10 @@
       </c>
       <c r="H373" s="2"/>
       <c r="L373" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M373" s="1" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
     </row>
     <row r="374" spans="1:13">
@@ -12864,7 +12899,7 @@
         <v>6</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F374" s="1">
         <v>10170010</v>
@@ -12874,10 +12909,10 @@
       </c>
       <c r="H374" s="2"/>
       <c r="L374" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M374" s="1" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="375" spans="1:13">
@@ -12894,7 +12929,7 @@
         <v>7</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F375" s="1">
         <v>10170010</v>
@@ -12904,10 +12939,10 @@
       </c>
       <c r="H375" s="2"/>
       <c r="L375" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M375" s="1" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
     </row>
     <row r="376" spans="1:13">
@@ -12924,7 +12959,7 @@
         <v>8</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F376" s="1">
         <v>10170010</v>
@@ -12934,10 +12969,10 @@
       </c>
       <c r="H376" s="2"/>
       <c r="L376" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M376" s="1" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="377" spans="1:13">
@@ -12954,7 +12989,7 @@
         <v>9</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F377" s="1">
         <v>10170010</v>
@@ -12964,10 +12999,10 @@
       </c>
       <c r="H377" s="2"/>
       <c r="L377" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M377" s="1" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
     </row>
     <row r="378" spans="1:13">
@@ -12984,7 +13019,7 @@
         <v>10</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F378" s="1">
         <v>10170010</v>
@@ -12994,10 +13029,10 @@
       </c>
       <c r="H378" s="2"/>
       <c r="L378" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M378" s="1" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
     </row>
     <row r="379" spans="1:13">
@@ -13014,7 +13049,7 @@
         <v>0</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F379" s="1">
         <v>10180001</v>
@@ -13038,7 +13073,7 @@
         <v>1</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F380" s="1">
         <v>10180001</v>
@@ -13067,7 +13102,7 @@
         <v>2</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F381" s="1">
         <v>10180001</v>
@@ -13096,7 +13131,7 @@
         <v>3</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F382" s="1">
         <v>10180001</v>
@@ -13125,7 +13160,7 @@
         <v>4</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F383" s="1">
         <v>10180001</v>
@@ -13154,7 +13189,7 @@
         <v>5</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F384" s="1">
         <v>10180001</v>
@@ -13183,7 +13218,7 @@
         <v>6</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F385" s="1">
         <v>10180001</v>
@@ -13212,7 +13247,7 @@
         <v>7</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F386" s="1">
         <v>10180001</v>
@@ -13241,7 +13276,7 @@
         <v>8</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F387" s="1">
         <v>10180001</v>
@@ -13270,7 +13305,7 @@
         <v>9</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F388" s="1">
         <v>10180001</v>
@@ -13299,7 +13334,7 @@
         <v>10</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F389" s="1">
         <v>10180001</v>
@@ -13328,7 +13363,7 @@
         <v>0</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F390" s="1">
         <v>10180002</v>
@@ -13352,7 +13387,7 @@
         <v>1</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F391" s="1">
         <v>10180002</v>
@@ -13379,7 +13414,7 @@
         <v>2</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F392" s="1">
         <v>10180002</v>
@@ -13406,7 +13441,7 @@
         <v>3</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F393" s="1">
         <v>10180002</v>
@@ -13433,7 +13468,7 @@
         <v>4</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F394" s="1">
         <v>10180002</v>
@@ -13460,7 +13495,7 @@
         <v>5</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F395" s="1">
         <v>10180002</v>
@@ -13487,7 +13522,7 @@
         <v>6</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F396" s="1">
         <v>10180002</v>
@@ -13514,7 +13549,7 @@
         <v>7</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F397" s="1">
         <v>10180002</v>
@@ -13541,7 +13576,7 @@
         <v>8</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F398" s="1">
         <v>10180002</v>
@@ -13568,7 +13603,7 @@
         <v>9</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F399" s="1">
         <v>10180002</v>
@@ -13595,7 +13630,7 @@
         <v>10</v>
       </c>
       <c r="E400" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F400" s="1">
         <v>10180002</v>
@@ -13622,7 +13657,7 @@
         <v>0</v>
       </c>
       <c r="E401" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F401" s="1">
         <v>10180003</v>
@@ -13646,7 +13681,7 @@
         <v>1</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F402" s="1">
         <v>10180003</v>
@@ -13656,7 +13691,7 @@
       </c>
       <c r="H402" s="2"/>
       <c r="K402" s="1" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
     </row>
     <row r="403" spans="1:11">
@@ -13673,7 +13708,7 @@
         <v>2</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F403" s="1">
         <v>10180003</v>
@@ -13683,7 +13718,7 @@
       </c>
       <c r="H403" s="2"/>
       <c r="K403" s="1" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
     </row>
     <row r="404" spans="1:11">
@@ -13700,7 +13735,7 @@
         <v>3</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F404" s="1">
         <v>10180003</v>
@@ -13710,7 +13745,7 @@
       </c>
       <c r="H404" s="2"/>
       <c r="K404" s="1" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
     </row>
     <row r="405" spans="1:11">
@@ -13727,7 +13762,7 @@
         <v>4</v>
       </c>
       <c r="E405" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F405" s="1">
         <v>10180003</v>
@@ -13737,7 +13772,7 @@
       </c>
       <c r="H405" s="2"/>
       <c r="K405" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
     </row>
     <row r="406" spans="1:11">
@@ -13754,7 +13789,7 @@
         <v>5</v>
       </c>
       <c r="E406" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F406" s="1">
         <v>10180003</v>
@@ -13764,7 +13799,7 @@
       </c>
       <c r="H406" s="2"/>
       <c r="K406" s="1" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
     </row>
     <row r="407" spans="1:11">
@@ -13781,7 +13816,7 @@
         <v>6</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F407" s="1">
         <v>10180003</v>
@@ -13791,7 +13826,7 @@
       </c>
       <c r="H407" s="2"/>
       <c r="K407" s="1" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="408" spans="1:11">
@@ -13808,7 +13843,7 @@
         <v>7</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F408" s="1">
         <v>10180003</v>
@@ -13818,7 +13853,7 @@
       </c>
       <c r="H408" s="2"/>
       <c r="K408" s="1" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
     </row>
     <row r="409" spans="1:11">
@@ -13835,7 +13870,7 @@
         <v>8</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F409" s="1">
         <v>10180003</v>
@@ -13845,7 +13880,7 @@
       </c>
       <c r="H409" s="2"/>
       <c r="K409" s="1" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
     </row>
     <row r="410" spans="1:11">
@@ -13862,7 +13897,7 @@
         <v>9</v>
       </c>
       <c r="E410" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F410" s="1">
         <v>10180003</v>
@@ -13872,7 +13907,7 @@
       </c>
       <c r="H410" s="2"/>
       <c r="K410" s="1" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
     </row>
     <row r="411" spans="1:11">
@@ -13889,7 +13924,7 @@
         <v>10</v>
       </c>
       <c r="E411" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F411" s="1">
         <v>10180003</v>
@@ -13899,7 +13934,7 @@
       </c>
       <c r="H411" s="2"/>
       <c r="K411" s="1" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
     </row>
     <row r="412" spans="1:11">
@@ -13916,7 +13951,7 @@
         <v>0</v>
       </c>
       <c r="E412" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F412" s="1">
         <v>10180004</v>
@@ -13940,7 +13975,7 @@
         <v>1</v>
       </c>
       <c r="E413" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F413" s="1">
         <v>10180004</v>
@@ -13950,7 +13985,7 @@
       </c>
       <c r="H413" s="2"/>
       <c r="K413" s="1" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="414" spans="1:11">
@@ -13967,7 +14002,7 @@
         <v>2</v>
       </c>
       <c r="E414" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F414" s="1">
         <v>10180004</v>
@@ -13977,7 +14012,7 @@
       </c>
       <c r="H414" s="2"/>
       <c r="K414" s="1" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
     </row>
     <row r="415" spans="1:11">
@@ -13994,7 +14029,7 @@
         <v>3</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F415" s="1">
         <v>10180004</v>
@@ -14004,7 +14039,7 @@
       </c>
       <c r="H415" s="2"/>
       <c r="K415" s="1" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
     </row>
     <row r="416" spans="1:11">
@@ -14021,7 +14056,7 @@
         <v>4</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F416" s="1">
         <v>10180004</v>
@@ -14031,7 +14066,7 @@
       </c>
       <c r="H416" s="2"/>
       <c r="K416" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
     </row>
     <row r="417" spans="1:11">
@@ -14048,7 +14083,7 @@
         <v>5</v>
       </c>
       <c r="E417" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F417" s="1">
         <v>10180004</v>
@@ -14058,7 +14093,7 @@
       </c>
       <c r="H417" s="2"/>
       <c r="K417" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
     </row>
     <row r="418" spans="1:11">
@@ -14075,7 +14110,7 @@
         <v>6</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F418" s="1">
         <v>10180004</v>
@@ -14085,7 +14120,7 @@
       </c>
       <c r="H418" s="2"/>
       <c r="K418" s="1" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
     </row>
     <row r="419" spans="1:11">
@@ -14102,7 +14137,7 @@
         <v>7</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F419" s="1">
         <v>10180004</v>
@@ -14112,7 +14147,7 @@
       </c>
       <c r="H419" s="2"/>
       <c r="K419" s="1" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
     </row>
     <row r="420" spans="1:11">
@@ -14129,7 +14164,7 @@
         <v>8</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F420" s="1">
         <v>10180004</v>
@@ -14139,7 +14174,7 @@
       </c>
       <c r="H420" s="2"/>
       <c r="K420" s="1" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
     </row>
     <row r="421" spans="1:11">
@@ -14156,7 +14191,7 @@
         <v>9</v>
       </c>
       <c r="E421" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F421" s="1">
         <v>10180004</v>
@@ -14166,7 +14201,7 @@
       </c>
       <c r="H421" s="2"/>
       <c r="K421" s="1" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
     </row>
     <row r="422" spans="1:11">
@@ -14183,7 +14218,7 @@
         <v>10</v>
       </c>
       <c r="E422" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F422" s="1">
         <v>10180004</v>
@@ -14193,7 +14228,7 @@
       </c>
       <c r="H422" s="2"/>
       <c r="K422" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
     </row>
     <row r="423" spans="1:11">
@@ -14210,7 +14245,7 @@
         <v>0</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F423" s="1">
         <v>10180005</v>
@@ -14234,7 +14269,7 @@
         <v>1</v>
       </c>
       <c r="E424" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F424" s="1">
         <v>10180005</v>
@@ -14244,7 +14279,7 @@
       </c>
       <c r="H424" s="2"/>
       <c r="K424" s="1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
     </row>
     <row r="425" spans="1:11">
@@ -14261,7 +14296,7 @@
         <v>2</v>
       </c>
       <c r="E425" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F425" s="1">
         <v>10180005</v>
@@ -14271,7 +14306,7 @@
       </c>
       <c r="H425" s="2"/>
       <c r="K425" s="1" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
     </row>
     <row r="426" spans="1:11">
@@ -14288,7 +14323,7 @@
         <v>3</v>
       </c>
       <c r="E426" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F426" s="1">
         <v>10180005</v>
@@ -14298,7 +14333,7 @@
       </c>
       <c r="H426" s="2"/>
       <c r="K426" s="1" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
     </row>
     <row r="427" spans="1:11">
@@ -14315,7 +14350,7 @@
         <v>4</v>
       </c>
       <c r="E427" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F427" s="1">
         <v>10180005</v>
@@ -14325,7 +14360,7 @@
       </c>
       <c r="H427" s="2"/>
       <c r="K427" s="1" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
     </row>
     <row r="428" spans="1:11">
@@ -14342,7 +14377,7 @@
         <v>5</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F428" s="1">
         <v>10180005</v>
@@ -14352,7 +14387,7 @@
       </c>
       <c r="H428" s="2"/>
       <c r="K428" s="1" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
     </row>
     <row r="429" spans="1:11">
@@ -14369,7 +14404,7 @@
         <v>6</v>
       </c>
       <c r="E429" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F429" s="1">
         <v>10180005</v>
@@ -14379,7 +14414,7 @@
       </c>
       <c r="H429" s="2"/>
       <c r="K429" s="1" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
     </row>
     <row r="430" spans="1:11">
@@ -14396,7 +14431,7 @@
         <v>7</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F430" s="1">
         <v>10180005</v>
@@ -14406,7 +14441,7 @@
       </c>
       <c r="H430" s="2"/>
       <c r="K430" s="1" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
     </row>
     <row r="431" spans="1:11">
@@ -14423,7 +14458,7 @@
         <v>8</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F431" s="1">
         <v>10180005</v>
@@ -14433,7 +14468,7 @@
       </c>
       <c r="H431" s="2"/>
       <c r="K431" s="1" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
     </row>
     <row r="432" spans="1:11">
@@ -14450,7 +14485,7 @@
         <v>9</v>
       </c>
       <c r="E432" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F432" s="1">
         <v>10180005</v>
@@ -14460,7 +14495,7 @@
       </c>
       <c r="H432" s="2"/>
       <c r="K432" s="1" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
     </row>
     <row r="433" spans="1:15">
@@ -14477,7 +14512,7 @@
         <v>10</v>
       </c>
       <c r="E433" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F433" s="1">
         <v>10180005</v>
@@ -14487,7 +14522,7 @@
       </c>
       <c r="H433" s="2"/>
       <c r="K433" s="1" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
     </row>
     <row r="434" spans="1:15">
@@ -14504,7 +14539,7 @@
         <v>0</v>
       </c>
       <c r="E434" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F434" s="1">
         <v>10180006</v>
@@ -14528,7 +14563,7 @@
         <v>1</v>
       </c>
       <c r="E435" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F435" s="1">
         <v>10180006</v>
@@ -14541,7 +14576,7 @@
         <v>45</v>
       </c>
       <c r="M435" s="1" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
     </row>
     <row r="436" spans="1:15">
@@ -14558,7 +14593,7 @@
         <v>2</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F436" s="1">
         <v>10180006</v>
@@ -14571,7 +14606,7 @@
         <v>45</v>
       </c>
       <c r="M436" s="1" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
     </row>
     <row r="437" spans="1:15">
@@ -14588,7 +14623,7 @@
         <v>3</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F437" s="1">
         <v>10180006</v>
@@ -14601,7 +14636,7 @@
         <v>45</v>
       </c>
       <c r="M437" s="1" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
     </row>
     <row r="438" spans="1:15">
@@ -14618,7 +14653,7 @@
         <v>4</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F438" s="1">
         <v>10180006</v>
@@ -14631,7 +14666,7 @@
         <v>45</v>
       </c>
       <c r="M438" s="1" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
     </row>
     <row r="439" spans="1:15">
@@ -14648,7 +14683,7 @@
         <v>5</v>
       </c>
       <c r="E439" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F439" s="1">
         <v>10180006</v>
@@ -14661,7 +14696,7 @@
         <v>45</v>
       </c>
       <c r="M439" s="1" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
     </row>
     <row r="440" spans="1:15">
@@ -14678,7 +14713,7 @@
         <v>6</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F440" s="1">
         <v>10180006</v>
@@ -14691,7 +14726,7 @@
         <v>45</v>
       </c>
       <c r="M440" s="1" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
     </row>
     <row r="441" spans="1:15">
@@ -14708,7 +14743,7 @@
         <v>7</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F441" s="1">
         <v>10180006</v>
@@ -14721,7 +14756,7 @@
         <v>45</v>
       </c>
       <c r="M441" s="1" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
     </row>
     <row r="442" spans="1:15">
@@ -14738,7 +14773,7 @@
         <v>8</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F442" s="1">
         <v>10180006</v>
@@ -14751,7 +14786,7 @@
         <v>45</v>
       </c>
       <c r="M442" s="1" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
     <row r="443" spans="1:15">
@@ -14768,7 +14803,7 @@
         <v>9</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F443" s="1">
         <v>10180006</v>
@@ -14781,7 +14816,7 @@
         <v>45</v>
       </c>
       <c r="M443" s="1" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
     </row>
     <row r="444" spans="1:15">
@@ -14798,7 +14833,7 @@
         <v>10</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F444" s="1">
         <v>10180006</v>
@@ -14811,7 +14846,7 @@
         <v>45</v>
       </c>
       <c r="M444" s="1" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
     </row>
     <row r="445" spans="1:15">
@@ -14828,7 +14863,7 @@
         <v>0</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F445" s="1">
         <v>10180007</v>
@@ -14852,7 +14887,7 @@
         <v>1</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F446" s="1">
         <v>10180007</v>
@@ -14862,7 +14897,7 @@
       </c>
       <c r="H446" s="2"/>
       <c r="O446" s="1" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
     </row>
     <row r="447" spans="1:15">
@@ -14879,7 +14914,7 @@
         <v>2</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F447" s="1">
         <v>10180007</v>
@@ -14889,7 +14924,7 @@
       </c>
       <c r="H447" s="2"/>
       <c r="O447" s="1" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
     </row>
     <row r="448" spans="1:15">
@@ -14906,7 +14941,7 @@
         <v>3</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F448" s="1">
         <v>10180007</v>
@@ -14916,7 +14951,7 @@
       </c>
       <c r="H448" s="2"/>
       <c r="O448" s="1" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
     </row>
     <row r="449" spans="1:15">
@@ -14933,7 +14968,7 @@
         <v>4</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F449" s="1">
         <v>10180007</v>
@@ -14943,7 +14978,7 @@
       </c>
       <c r="H449" s="2"/>
       <c r="O449" s="1" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
     </row>
     <row r="450" spans="1:15">
@@ -14960,7 +14995,7 @@
         <v>5</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F450" s="1">
         <v>10180007</v>
@@ -14970,7 +15005,7 @@
       </c>
       <c r="H450" s="2"/>
       <c r="O450" s="1" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
     </row>
     <row r="451" spans="1:15">
@@ -14987,7 +15022,7 @@
         <v>6</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F451" s="1">
         <v>10180007</v>
@@ -14997,7 +15032,7 @@
       </c>
       <c r="H451" s="2"/>
       <c r="O451" s="1" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
     </row>
     <row r="452" spans="1:15">
@@ -15014,7 +15049,7 @@
         <v>7</v>
       </c>
       <c r="E452" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F452" s="1">
         <v>10180007</v>
@@ -15024,7 +15059,7 @@
       </c>
       <c r="H452" s="2"/>
       <c r="O452" s="1" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
     </row>
     <row r="453" spans="1:15">
@@ -15041,7 +15076,7 @@
         <v>8</v>
       </c>
       <c r="E453" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F453" s="1">
         <v>10180007</v>
@@ -15051,7 +15086,7 @@
       </c>
       <c r="H453" s="2"/>
       <c r="O453" s="1" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
     </row>
     <row r="454" spans="1:15">
@@ -15068,7 +15103,7 @@
         <v>9</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F454" s="1">
         <v>10180007</v>
@@ -15078,7 +15113,7 @@
       </c>
       <c r="H454" s="2"/>
       <c r="O454" s="1" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
     </row>
     <row r="455" spans="1:15">
@@ -15095,7 +15130,7 @@
         <v>10</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F455" s="1">
         <v>10180007</v>
@@ -15105,7 +15140,7 @@
       </c>
       <c r="H455" s="2"/>
       <c r="O455" s="1" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
     </row>
     <row r="456" spans="1:15">
@@ -15122,7 +15157,7 @@
         <v>0</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F456" s="1">
         <v>10180008</v>
@@ -15146,7 +15181,7 @@
         <v>1</v>
       </c>
       <c r="E457" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F457" s="1">
         <v>10180008</v>
@@ -15156,7 +15191,7 @@
       </c>
       <c r="H457" s="2"/>
       <c r="O457" s="1" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
     </row>
     <row r="458" spans="1:15">
@@ -15173,7 +15208,7 @@
         <v>2</v>
       </c>
       <c r="E458" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F458" s="1">
         <v>10180008</v>
@@ -15183,7 +15218,7 @@
       </c>
       <c r="H458" s="2"/>
       <c r="O458" s="1" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
     </row>
     <row r="459" spans="1:15">
@@ -15200,7 +15235,7 @@
         <v>3</v>
       </c>
       <c r="E459" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F459" s="1">
         <v>10180008</v>
@@ -15210,7 +15245,7 @@
       </c>
       <c r="H459" s="2"/>
       <c r="O459" s="1" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="460" spans="1:15">
@@ -15227,7 +15262,7 @@
         <v>4</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F460" s="1">
         <v>10180008</v>
@@ -15237,7 +15272,7 @@
       </c>
       <c r="H460" s="2"/>
       <c r="O460" s="1" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
     </row>
     <row r="461" spans="1:15">
@@ -15254,7 +15289,7 @@
         <v>5</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F461" s="1">
         <v>10180008</v>
@@ -15264,7 +15299,7 @@
       </c>
       <c r="H461" s="2"/>
       <c r="O461" s="1" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
     </row>
     <row r="462" spans="1:15">
@@ -15281,7 +15316,7 @@
         <v>6</v>
       </c>
       <c r="E462" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F462" s="1">
         <v>10180008</v>
@@ -15291,7 +15326,7 @@
       </c>
       <c r="H462" s="2"/>
       <c r="O462" s="1" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
     </row>
     <row r="463" spans="1:15">
@@ -15308,7 +15343,7 @@
         <v>7</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F463" s="1">
         <v>10180008</v>
@@ -15318,7 +15353,7 @@
       </c>
       <c r="H463" s="2"/>
       <c r="O463" s="1" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="464" spans="1:15">
@@ -15335,7 +15370,7 @@
         <v>8</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F464" s="1">
         <v>10180008</v>
@@ -15345,7 +15380,7 @@
       </c>
       <c r="H464" s="2"/>
       <c r="O464" s="1" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
     </row>
     <row r="465" spans="1:15">
@@ -15362,7 +15397,7 @@
         <v>9</v>
       </c>
       <c r="E465" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F465" s="1">
         <v>10180008</v>
@@ -15372,7 +15407,7 @@
       </c>
       <c r="H465" s="2"/>
       <c r="O465" s="1" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
     </row>
     <row r="466" spans="1:15">
@@ -15389,7 +15424,7 @@
         <v>10</v>
       </c>
       <c r="E466" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F466" s="1">
         <v>10180008</v>
@@ -15399,7 +15434,7 @@
       </c>
       <c r="H466" s="2"/>
       <c r="O466" s="1" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
     </row>
     <row r="467" spans="1:15">
@@ -15416,7 +15451,7 @@
         <v>0</v>
       </c>
       <c r="E467" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F467" s="1">
         <v>10180009</v>
@@ -15440,7 +15475,7 @@
         <v>1</v>
       </c>
       <c r="E468" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F468" s="1">
         <v>10180009</v>
@@ -15450,7 +15485,7 @@
       </c>
       <c r="H468" s="2"/>
       <c r="O468" s="1" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="469" spans="1:15">
@@ -15467,7 +15502,7 @@
         <v>2</v>
       </c>
       <c r="E469" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F469" s="1">
         <v>10180009</v>
@@ -15477,7 +15512,7 @@
       </c>
       <c r="H469" s="2"/>
       <c r="O469" s="1" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
     </row>
     <row r="470" spans="1:15">
@@ -15494,7 +15529,7 @@
         <v>3</v>
       </c>
       <c r="E470" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F470" s="1">
         <v>10180009</v>
@@ -15504,7 +15539,7 @@
       </c>
       <c r="H470" s="2"/>
       <c r="O470" s="1" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
     </row>
     <row r="471" spans="1:15">
@@ -15521,7 +15556,7 @@
         <v>4</v>
       </c>
       <c r="E471" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F471" s="1">
         <v>10180009</v>
@@ -15531,7 +15566,7 @@
       </c>
       <c r="H471" s="2"/>
       <c r="O471" s="1" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
     </row>
     <row r="472" spans="1:15">
@@ -15548,7 +15583,7 @@
         <v>5</v>
       </c>
       <c r="E472" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F472" s="1">
         <v>10180009</v>
@@ -15558,7 +15593,7 @@
       </c>
       <c r="H472" s="2"/>
       <c r="O472" s="1" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
     </row>
     <row r="473" spans="1:15">
@@ -15575,7 +15610,7 @@
         <v>6</v>
       </c>
       <c r="E473" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F473" s="1">
         <v>10180009</v>
@@ -15585,7 +15620,7 @@
       </c>
       <c r="H473" s="2"/>
       <c r="O473" s="1" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
     </row>
     <row r="474" spans="1:15">
@@ -15602,7 +15637,7 @@
         <v>7</v>
       </c>
       <c r="E474" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F474" s="1">
         <v>10180009</v>
@@ -15612,7 +15647,7 @@
       </c>
       <c r="H474" s="2"/>
       <c r="O474" s="1" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
     </row>
     <row r="475" spans="1:15">
@@ -15629,7 +15664,7 @@
         <v>8</v>
       </c>
       <c r="E475" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F475" s="1">
         <v>10180009</v>
@@ -15639,7 +15674,7 @@
       </c>
       <c r="H475" s="2"/>
       <c r="O475" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
     </row>
     <row r="476" spans="1:15">
@@ -15656,7 +15691,7 @@
         <v>9</v>
       </c>
       <c r="E476" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F476" s="1">
         <v>10180009</v>
@@ -15666,7 +15701,7 @@
       </c>
       <c r="H476" s="2"/>
       <c r="O476" s="1" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
     </row>
     <row r="477" spans="1:15">
@@ -15683,7 +15718,7 @@
         <v>10</v>
       </c>
       <c r="E477" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F477" s="1">
         <v>10180009</v>
@@ -15693,7 +15728,7 @@
       </c>
       <c r="H477" s="2"/>
       <c r="O477" s="1" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
     </row>
     <row r="478" spans="1:15">
@@ -15710,7 +15745,7 @@
         <v>0</v>
       </c>
       <c r="E478" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F478" s="1">
         <v>10180010</v>
@@ -15734,7 +15769,7 @@
         <v>1</v>
       </c>
       <c r="E479" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F479" s="1">
         <v>10180010</v>
@@ -15744,10 +15779,10 @@
       </c>
       <c r="H479" s="2"/>
       <c r="L479" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M479" s="1" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
     </row>
     <row r="480" spans="1:15">
@@ -15764,7 +15799,7 @@
         <v>2</v>
       </c>
       <c r="E480" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F480" s="1">
         <v>10180010</v>
@@ -15774,10 +15809,10 @@
       </c>
       <c r="H480" s="2"/>
       <c r="L480" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M480" s="1" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="481" spans="1:13">
@@ -15794,7 +15829,7 @@
         <v>3</v>
       </c>
       <c r="E481" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F481" s="1">
         <v>10180010</v>
@@ -15804,10 +15839,10 @@
       </c>
       <c r="H481" s="2"/>
       <c r="L481" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M481" s="1" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
     </row>
     <row r="482" spans="1:13">
@@ -15824,7 +15859,7 @@
         <v>4</v>
       </c>
       <c r="E482" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F482" s="1">
         <v>10180010</v>
@@ -15834,10 +15869,10 @@
       </c>
       <c r="H482" s="2"/>
       <c r="L482" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M482" s="1" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
     </row>
     <row r="483" spans="1:13">
@@ -15854,7 +15889,7 @@
         <v>5</v>
       </c>
       <c r="E483" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F483" s="1">
         <v>10180010</v>
@@ -15864,10 +15899,10 @@
       </c>
       <c r="H483" s="2"/>
       <c r="L483" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M483" s="1" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
     </row>
     <row r="484" spans="1:13">
@@ -15884,7 +15919,7 @@
         <v>6</v>
       </c>
       <c r="E484" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F484" s="1">
         <v>10180010</v>
@@ -15894,10 +15929,10 @@
       </c>
       <c r="H484" s="2"/>
       <c r="L484" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M484" s="1" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="485" spans="1:13">
@@ -15914,7 +15949,7 @@
         <v>7</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F485" s="1">
         <v>10180010</v>
@@ -15924,10 +15959,10 @@
       </c>
       <c r="H485" s="2"/>
       <c r="L485" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M485" s="1" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
     </row>
     <row r="486" spans="1:13">
@@ -15944,7 +15979,7 @@
         <v>8</v>
       </c>
       <c r="E486" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F486" s="1">
         <v>10180010</v>
@@ -15954,10 +15989,10 @@
       </c>
       <c r="H486" s="2"/>
       <c r="L486" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M486" s="1" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="487" spans="1:13">
@@ -15974,7 +16009,7 @@
         <v>9</v>
       </c>
       <c r="E487" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F487" s="1">
         <v>10180010</v>
@@ -15984,10 +16019,10 @@
       </c>
       <c r="H487" s="2"/>
       <c r="L487" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M487" s="1" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
     </row>
     <row r="488" spans="1:13">
@@ -16004,7 +16039,7 @@
         <v>10</v>
       </c>
       <c r="E488" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F488" s="1">
         <v>10180010</v>
@@ -16014,10 +16049,10 @@
       </c>
       <c r="H488" s="2"/>
       <c r="L488" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M488" s="1" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
     </row>
     <row r="489" spans="1:13">
@@ -16034,7 +16069,7 @@
         <v>0</v>
       </c>
       <c r="E489" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F489" s="1">
         <v>10210001</v>
@@ -16058,7 +16093,7 @@
         <v>1</v>
       </c>
       <c r="E490" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F490" s="1">
         <v>10210001</v>
@@ -16087,7 +16122,7 @@
         <v>2</v>
       </c>
       <c r="E491" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F491" s="1">
         <v>10210001</v>
@@ -16116,7 +16151,7 @@
         <v>3</v>
       </c>
       <c r="E492" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F492" s="1">
         <v>10210001</v>
@@ -16145,7 +16180,7 @@
         <v>4</v>
       </c>
       <c r="E493" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F493" s="1">
         <v>10210001</v>
@@ -16174,7 +16209,7 @@
         <v>5</v>
       </c>
       <c r="E494" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F494" s="1">
         <v>10210001</v>
@@ -16203,7 +16238,7 @@
         <v>6</v>
       </c>
       <c r="E495" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F495" s="1">
         <v>10210001</v>
@@ -16232,7 +16267,7 @@
         <v>7</v>
       </c>
       <c r="E496" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F496" s="1">
         <v>10210001</v>
@@ -16261,7 +16296,7 @@
         <v>8</v>
       </c>
       <c r="E497" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F497" s="1">
         <v>10210001</v>
@@ -16290,7 +16325,7 @@
         <v>9</v>
       </c>
       <c r="E498" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F498" s="1">
         <v>10210001</v>
@@ -16319,7 +16354,7 @@
         <v>10</v>
       </c>
       <c r="E499" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F499" s="1">
         <v>10210001</v>
@@ -16348,7 +16383,7 @@
         <v>0</v>
       </c>
       <c r="E500" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F500" s="1">
         <v>10210002</v>
@@ -16372,7 +16407,7 @@
         <v>1</v>
       </c>
       <c r="E501" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F501" s="1">
         <v>10210002</v>
@@ -16399,7 +16434,7 @@
         <v>2</v>
       </c>
       <c r="E502" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F502" s="1">
         <v>10210002</v>
@@ -16426,7 +16461,7 @@
         <v>3</v>
       </c>
       <c r="E503" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F503" s="1">
         <v>10210002</v>
@@ -16453,7 +16488,7 @@
         <v>4</v>
       </c>
       <c r="E504" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F504" s="1">
         <v>10210002</v>
@@ -16480,7 +16515,7 @@
         <v>5</v>
       </c>
       <c r="E505" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F505" s="1">
         <v>10210002</v>
@@ -16506,7 +16541,7 @@
         <v>6</v>
       </c>
       <c r="E506" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F506" s="1">
         <v>10210002</v>
@@ -16532,7 +16567,7 @@
         <v>7</v>
       </c>
       <c r="E507" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F507" s="1">
         <v>10210002</v>
@@ -16558,7 +16593,7 @@
         <v>8</v>
       </c>
       <c r="E508" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F508" s="1">
         <v>10210002</v>
@@ -16584,7 +16619,7 @@
         <v>9</v>
       </c>
       <c r="E509" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F509" s="1">
         <v>10210002</v>
@@ -16610,7 +16645,7 @@
         <v>10</v>
       </c>
       <c r="E510" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F510" s="1">
         <v>10210002</v>
@@ -16636,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="E511" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F511" s="1">
         <v>10210003</v>
@@ -16659,7 +16694,7 @@
         <v>1</v>
       </c>
       <c r="E512" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F512" s="1">
         <v>10210003</v>
@@ -16668,7 +16703,7 @@
         <v>27</v>
       </c>
       <c r="K512" s="1" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
     </row>
     <row r="513" spans="1:11">
@@ -16685,7 +16720,7 @@
         <v>2</v>
       </c>
       <c r="E513" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F513" s="1">
         <v>10210003</v>
@@ -16694,7 +16729,7 @@
         <v>29</v>
       </c>
       <c r="K513" s="1" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
     </row>
     <row r="514" spans="1:11">
@@ -16711,7 +16746,7 @@
         <v>3</v>
       </c>
       <c r="E514" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F514" s="1">
         <v>10210003</v>
@@ -16720,7 +16755,7 @@
         <v>31</v>
       </c>
       <c r="K514" s="1" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
     </row>
     <row r="515" spans="1:11">
@@ -16737,7 +16772,7 @@
         <v>4</v>
       </c>
       <c r="E515" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F515" s="1">
         <v>10210003</v>
@@ -16746,7 +16781,7 @@
         <v>33</v>
       </c>
       <c r="K515" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
     </row>
     <row r="516" spans="1:11">
@@ -16763,7 +16798,7 @@
         <v>5</v>
       </c>
       <c r="E516" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F516" s="1">
         <v>10210003</v>
@@ -16772,7 +16807,7 @@
         <v>35</v>
       </c>
       <c r="K516" s="1" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
     </row>
     <row r="517" spans="1:11">
@@ -16789,7 +16824,7 @@
         <v>6</v>
       </c>
       <c r="E517" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F517" s="1">
         <v>10210003</v>
@@ -16798,7 +16833,7 @@
         <v>37</v>
       </c>
       <c r="K517" s="1" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="518" spans="1:11">
@@ -16815,7 +16850,7 @@
         <v>7</v>
       </c>
       <c r="E518" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F518" s="1">
         <v>10210003</v>
@@ -16824,7 +16859,7 @@
         <v>39</v>
       </c>
       <c r="K518" s="1" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
     </row>
     <row r="519" spans="1:11">
@@ -16841,7 +16876,7 @@
         <v>8</v>
       </c>
       <c r="E519" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F519" s="1">
         <v>10210003</v>
@@ -16850,7 +16885,7 @@
         <v>41</v>
       </c>
       <c r="K519" s="1" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
     </row>
     <row r="520" spans="1:11">
@@ -16867,7 +16902,7 @@
         <v>9</v>
       </c>
       <c r="E520" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F520" s="1">
         <v>10210003</v>
@@ -16876,7 +16911,7 @@
         <v>43</v>
       </c>
       <c r="K520" s="1" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
     </row>
     <row r="521" spans="1:11">
@@ -16893,7 +16928,7 @@
         <v>10</v>
       </c>
       <c r="E521" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F521" s="1">
         <v>10210003</v>
@@ -16902,7 +16937,7 @@
         <v>45</v>
       </c>
       <c r="K521" s="1" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
     </row>
     <row r="522" spans="1:11">
@@ -16919,7 +16954,7 @@
         <v>0</v>
       </c>
       <c r="E522" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F522" s="1">
         <v>10210004</v>
@@ -16942,7 +16977,7 @@
         <v>1</v>
       </c>
       <c r="E523" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F523" s="1">
         <v>10210004</v>
@@ -16951,7 +16986,7 @@
         <v>27</v>
       </c>
       <c r="K523" s="1" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="524" spans="1:11">
@@ -16968,7 +17003,7 @@
         <v>2</v>
       </c>
       <c r="E524" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F524" s="1">
         <v>10210004</v>
@@ -16977,7 +17012,7 @@
         <v>29</v>
       </c>
       <c r="K524" s="1" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
     </row>
     <row r="525" spans="1:11">
@@ -16994,7 +17029,7 @@
         <v>3</v>
       </c>
       <c r="E525" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F525" s="1">
         <v>10210004</v>
@@ -17003,7 +17038,7 @@
         <v>31</v>
       </c>
       <c r="K525" s="1" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
     </row>
     <row r="526" spans="1:11">
@@ -17020,7 +17055,7 @@
         <v>4</v>
       </c>
       <c r="E526" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F526" s="1">
         <v>10210004</v>
@@ -17029,7 +17064,7 @@
         <v>33</v>
       </c>
       <c r="K526" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
     </row>
     <row r="527" spans="1:11">
@@ -17046,7 +17081,7 @@
         <v>5</v>
       </c>
       <c r="E527" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F527" s="1">
         <v>10210004</v>
@@ -17055,7 +17090,7 @@
         <v>35</v>
       </c>
       <c r="K527" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
     </row>
     <row r="528" spans="1:11">
@@ -17072,7 +17107,7 @@
         <v>6</v>
       </c>
       <c r="E528" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F528" s="1">
         <v>10210004</v>
@@ -17081,7 +17116,7 @@
         <v>37</v>
       </c>
       <c r="K528" s="1" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
     </row>
     <row r="529" spans="1:11">
@@ -17098,7 +17133,7 @@
         <v>7</v>
       </c>
       <c r="E529" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F529" s="1">
         <v>10210004</v>
@@ -17107,7 +17142,7 @@
         <v>39</v>
       </c>
       <c r="K529" s="1" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
     </row>
     <row r="530" spans="1:11">
@@ -17124,7 +17159,7 @@
         <v>8</v>
       </c>
       <c r="E530" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F530" s="1">
         <v>10210004</v>
@@ -17133,7 +17168,7 @@
         <v>41</v>
       </c>
       <c r="K530" s="1" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
     </row>
     <row r="531" spans="1:11">
@@ -17150,7 +17185,7 @@
         <v>9</v>
       </c>
       <c r="E531" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F531" s="1">
         <v>10210004</v>
@@ -17159,7 +17194,7 @@
         <v>43</v>
       </c>
       <c r="K531" s="1" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
     </row>
     <row r="532" spans="1:11">
@@ -17176,7 +17211,7 @@
         <v>10</v>
       </c>
       <c r="E532" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F532" s="1">
         <v>10210004</v>
@@ -17185,7 +17220,7 @@
         <v>45</v>
       </c>
       <c r="K532" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
     </row>
     <row r="533" spans="1:11">
@@ -17202,7 +17237,7 @@
         <v>0</v>
       </c>
       <c r="E533" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F533" s="1">
         <v>10210005</v>
@@ -17225,7 +17260,7 @@
         <v>1</v>
       </c>
       <c r="E534" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F534" s="1">
         <v>10210005</v>
@@ -17234,7 +17269,7 @@
         <v>27</v>
       </c>
       <c r="K534" s="1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
     </row>
     <row r="535" spans="1:11">
@@ -17251,7 +17286,7 @@
         <v>2</v>
       </c>
       <c r="E535" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F535" s="1">
         <v>10210005</v>
@@ -17260,7 +17295,7 @@
         <v>29</v>
       </c>
       <c r="K535" s="1" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
     </row>
     <row r="536" spans="1:11">
@@ -17277,7 +17312,7 @@
         <v>3</v>
       </c>
       <c r="E536" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F536" s="1">
         <v>10210005</v>
@@ -17286,7 +17321,7 @@
         <v>31</v>
       </c>
       <c r="K536" s="1" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
     </row>
     <row r="537" spans="1:11">
@@ -17303,7 +17338,7 @@
         <v>4</v>
       </c>
       <c r="E537" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F537" s="1">
         <v>10210005</v>
@@ -17312,7 +17347,7 @@
         <v>33</v>
       </c>
       <c r="K537" s="1" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
     </row>
     <row r="538" spans="1:11">
@@ -17329,7 +17364,7 @@
         <v>5</v>
       </c>
       <c r="E538" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F538" s="1">
         <v>10210005</v>
@@ -17338,7 +17373,7 @@
         <v>35</v>
       </c>
       <c r="K538" s="1" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
     </row>
     <row r="539" spans="1:11">
@@ -17355,7 +17390,7 @@
         <v>6</v>
       </c>
       <c r="E539" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F539" s="1">
         <v>10210005</v>
@@ -17364,7 +17399,7 @@
         <v>37</v>
       </c>
       <c r="K539" s="1" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
     </row>
     <row r="540" spans="1:11">
@@ -17381,7 +17416,7 @@
         <v>7</v>
       </c>
       <c r="E540" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F540" s="1">
         <v>10210005</v>
@@ -17390,7 +17425,7 @@
         <v>39</v>
       </c>
       <c r="K540" s="1" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
     </row>
     <row r="541" spans="1:11">
@@ -17407,7 +17442,7 @@
         <v>8</v>
       </c>
       <c r="E541" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F541" s="1">
         <v>10210005</v>
@@ -17416,7 +17451,7 @@
         <v>41</v>
       </c>
       <c r="K541" s="1" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
     </row>
     <row r="542" spans="1:11">
@@ -17433,7 +17468,7 @@
         <v>9</v>
       </c>
       <c r="E542" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F542" s="1">
         <v>10210005</v>
@@ -17442,7 +17477,7 @@
         <v>43</v>
       </c>
       <c r="K542" s="1" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
     </row>
     <row r="543" spans="1:11">
@@ -17459,7 +17494,7 @@
         <v>10</v>
       </c>
       <c r="E543" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F543" s="1">
         <v>10210005</v>
@@ -17468,7 +17503,7 @@
         <v>45</v>
       </c>
       <c r="K543" s="1" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
     </row>
     <row r="544" spans="1:11">
@@ -17485,7 +17520,7 @@
         <v>0</v>
       </c>
       <c r="E544" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F544" s="1">
         <v>10210006</v>
@@ -17508,7 +17543,7 @@
         <v>1</v>
       </c>
       <c r="E545" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F545" s="1">
         <v>10210006</v>
@@ -17520,7 +17555,7 @@
         <v>45</v>
       </c>
       <c r="M545" s="1" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
     </row>
     <row r="546" spans="1:15">
@@ -17537,7 +17572,7 @@
         <v>2</v>
       </c>
       <c r="E546" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F546" s="1">
         <v>10210006</v>
@@ -17549,7 +17584,7 @@
         <v>45</v>
       </c>
       <c r="M546" s="1" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
     </row>
     <row r="547" spans="1:15">
@@ -17566,7 +17601,7 @@
         <v>3</v>
       </c>
       <c r="E547" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F547" s="1">
         <v>10210006</v>
@@ -17578,7 +17613,7 @@
         <v>45</v>
       </c>
       <c r="M547" s="1" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
     </row>
     <row r="548" spans="1:15">
@@ -17595,7 +17630,7 @@
         <v>4</v>
       </c>
       <c r="E548" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F548" s="1">
         <v>10210006</v>
@@ -17607,7 +17642,7 @@
         <v>45</v>
       </c>
       <c r="M548" s="1" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="549" spans="1:15">
@@ -17624,7 +17659,7 @@
         <v>5</v>
       </c>
       <c r="E549" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F549" s="1">
         <v>10210006</v>
@@ -17636,7 +17671,7 @@
         <v>45</v>
       </c>
       <c r="M549" s="1" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
     </row>
     <row r="550" spans="1:15">
@@ -17653,7 +17688,7 @@
         <v>6</v>
       </c>
       <c r="E550" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F550" s="1">
         <v>10210006</v>
@@ -17665,7 +17700,7 @@
         <v>45</v>
       </c>
       <c r="M550" s="1" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
     </row>
     <row r="551" spans="1:15">
@@ -17682,7 +17717,7 @@
         <v>7</v>
       </c>
       <c r="E551" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F551" s="1">
         <v>10210006</v>
@@ -17694,7 +17729,7 @@
         <v>45</v>
       </c>
       <c r="M551" s="1" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
     </row>
     <row r="552" spans="1:15">
@@ -17711,7 +17746,7 @@
         <v>8</v>
       </c>
       <c r="E552" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F552" s="1">
         <v>10210006</v>
@@ -17723,7 +17758,7 @@
         <v>45</v>
       </c>
       <c r="M552" s="1" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
     </row>
     <row r="553" spans="1:15">
@@ -17740,7 +17775,7 @@
         <v>9</v>
       </c>
       <c r="E553" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F553" s="1">
         <v>10210006</v>
@@ -17752,7 +17787,7 @@
         <v>45</v>
       </c>
       <c r="M553" s="1" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
     </row>
     <row r="554" spans="1:15">
@@ -17769,7 +17804,7 @@
         <v>10</v>
       </c>
       <c r="E554" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F554" s="1">
         <v>10210006</v>
@@ -17781,7 +17816,7 @@
         <v>45</v>
       </c>
       <c r="M554" s="1" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
     </row>
     <row r="555" spans="1:15">
@@ -17798,7 +17833,7 @@
         <v>0</v>
       </c>
       <c r="E555" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F555" s="1">
         <v>10210007</v>
@@ -17821,7 +17856,7 @@
         <v>1</v>
       </c>
       <c r="E556" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F556" s="1">
         <v>10210007</v>
@@ -17830,7 +17865,7 @@
         <v>27</v>
       </c>
       <c r="O556" s="1" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
     </row>
     <row r="557" spans="1:15">
@@ -17847,7 +17882,7 @@
         <v>2</v>
       </c>
       <c r="E557" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F557" s="1">
         <v>10210007</v>
@@ -17856,7 +17891,7 @@
         <v>29</v>
       </c>
       <c r="O557" s="1" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
     </row>
     <row r="558" spans="1:15">
@@ -17873,7 +17908,7 @@
         <v>3</v>
       </c>
       <c r="E558" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F558" s="1">
         <v>10210007</v>
@@ -17882,7 +17917,7 @@
         <v>31</v>
       </c>
       <c r="O558" s="1" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
     </row>
     <row r="559" spans="1:15">
@@ -17899,7 +17934,7 @@
         <v>4</v>
       </c>
       <c r="E559" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F559" s="1">
         <v>10210007</v>
@@ -17908,7 +17943,7 @@
         <v>33</v>
       </c>
       <c r="O559" s="1" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
     </row>
     <row r="560" spans="1:15">
@@ -17925,7 +17960,7 @@
         <v>5</v>
       </c>
       <c r="E560" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F560" s="1">
         <v>10210007</v>
@@ -17934,7 +17969,7 @@
         <v>35</v>
       </c>
       <c r="O560" s="1" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
     </row>
     <row r="561" spans="1:15">
@@ -17951,7 +17986,7 @@
         <v>6</v>
       </c>
       <c r="E561" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F561" s="1">
         <v>10210007</v>
@@ -17960,7 +17995,7 @@
         <v>37</v>
       </c>
       <c r="O561" s="1" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
     </row>
     <row r="562" spans="1:15">
@@ -17977,7 +18012,7 @@
         <v>7</v>
       </c>
       <c r="E562" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F562" s="1">
         <v>10210007</v>
@@ -17986,7 +18021,7 @@
         <v>39</v>
       </c>
       <c r="O562" s="1" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
     </row>
     <row r="563" spans="1:15">
@@ -18003,7 +18038,7 @@
         <v>8</v>
       </c>
       <c r="E563" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F563" s="1">
         <v>10210007</v>
@@ -18012,7 +18047,7 @@
         <v>41</v>
       </c>
       <c r="O563" s="1" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
     </row>
     <row r="564" spans="1:15">
@@ -18029,7 +18064,7 @@
         <v>9</v>
       </c>
       <c r="E564" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F564" s="1">
         <v>10210007</v>
@@ -18038,7 +18073,7 @@
         <v>43</v>
       </c>
       <c r="O564" s="1" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
     </row>
     <row r="565" spans="1:15">
@@ -18055,7 +18090,7 @@
         <v>10</v>
       </c>
       <c r="E565" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F565" s="1">
         <v>10210007</v>
@@ -18064,7 +18099,7 @@
         <v>45</v>
       </c>
       <c r="O565" s="1" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
     </row>
     <row r="566" spans="1:15">
@@ -18081,7 +18116,7 @@
         <v>0</v>
       </c>
       <c r="E566" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F566" s="1">
         <v>10210008</v>
@@ -18104,7 +18139,7 @@
         <v>1</v>
       </c>
       <c r="E567" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F567" s="1">
         <v>10210008</v>
@@ -18113,7 +18148,7 @@
         <v>27</v>
       </c>
       <c r="O567" s="1" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
     </row>
     <row r="568" spans="1:15">
@@ -18130,7 +18165,7 @@
         <v>2</v>
       </c>
       <c r="E568" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F568" s="1">
         <v>10210008</v>
@@ -18139,7 +18174,7 @@
         <v>29</v>
       </c>
       <c r="O568" s="1" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
     </row>
     <row r="569" spans="1:15">
@@ -18156,7 +18191,7 @@
         <v>3</v>
       </c>
       <c r="E569" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F569" s="1">
         <v>10210008</v>
@@ -18165,7 +18200,7 @@
         <v>31</v>
       </c>
       <c r="O569" s="1" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="570" spans="1:15">
@@ -18182,7 +18217,7 @@
         <v>4</v>
       </c>
       <c r="E570" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F570" s="1">
         <v>10210008</v>
@@ -18191,7 +18226,7 @@
         <v>33</v>
       </c>
       <c r="O570" s="1" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
     </row>
     <row r="571" spans="1:15">
@@ -18208,7 +18243,7 @@
         <v>5</v>
       </c>
       <c r="E571" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F571" s="1">
         <v>10210008</v>
@@ -18217,7 +18252,7 @@
         <v>35</v>
       </c>
       <c r="O571" s="1" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
     </row>
     <row r="572" spans="1:15">
@@ -18234,7 +18269,7 @@
         <v>6</v>
       </c>
       <c r="E572" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F572" s="1">
         <v>10210008</v>
@@ -18243,7 +18278,7 @@
         <v>37</v>
       </c>
       <c r="O572" s="1" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
     </row>
     <row r="573" spans="1:15">
@@ -18260,7 +18295,7 @@
         <v>7</v>
       </c>
       <c r="E573" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F573" s="1">
         <v>10210008</v>
@@ -18269,7 +18304,7 @@
         <v>39</v>
       </c>
       <c r="O573" s="1" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="574" spans="1:15">
@@ -18286,7 +18321,7 @@
         <v>8</v>
       </c>
       <c r="E574" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F574" s="1">
         <v>10210008</v>
@@ -18295,7 +18330,7 @@
         <v>41</v>
       </c>
       <c r="O574" s="1" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
     </row>
     <row r="575" spans="1:15">
@@ -18312,7 +18347,7 @@
         <v>9</v>
       </c>
       <c r="E575" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F575" s="1">
         <v>10210008</v>
@@ -18321,7 +18356,7 @@
         <v>43</v>
       </c>
       <c r="O575" s="1" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
     </row>
     <row r="576" spans="1:15">
@@ -18338,7 +18373,7 @@
         <v>10</v>
       </c>
       <c r="E576" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F576" s="1">
         <v>10210008</v>
@@ -18347,7 +18382,7 @@
         <v>45</v>
       </c>
       <c r="O576" s="1" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
     </row>
     <row r="577" spans="1:15">
@@ -18364,7 +18399,7 @@
         <v>0</v>
       </c>
       <c r="E577" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F577" s="1">
         <v>10210009</v>
@@ -18387,7 +18422,7 @@
         <v>1</v>
       </c>
       <c r="E578" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F578" s="1">
         <v>10210009</v>
@@ -18396,7 +18431,7 @@
         <v>27</v>
       </c>
       <c r="O578" s="1" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="579" spans="1:15">
@@ -18413,7 +18448,7 @@
         <v>2</v>
       </c>
       <c r="E579" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F579" s="1">
         <v>10210009</v>
@@ -18422,7 +18457,7 @@
         <v>29</v>
       </c>
       <c r="O579" s="1" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
     </row>
     <row r="580" spans="1:15">
@@ -18439,7 +18474,7 @@
         <v>3</v>
       </c>
       <c r="E580" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F580" s="1">
         <v>10210009</v>
@@ -18448,7 +18483,7 @@
         <v>31</v>
       </c>
       <c r="O580" s="1" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
     </row>
     <row r="581" spans="1:15">
@@ -18465,7 +18500,7 @@
         <v>4</v>
       </c>
       <c r="E581" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F581" s="1">
         <v>10210009</v>
@@ -18474,7 +18509,7 @@
         <v>33</v>
       </c>
       <c r="O581" s="1" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
     </row>
     <row r="582" spans="1:15">
@@ -18491,7 +18526,7 @@
         <v>5</v>
       </c>
       <c r="E582" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F582" s="1">
         <v>10210009</v>
@@ -18500,7 +18535,7 @@
         <v>35</v>
       </c>
       <c r="O582" s="1" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
     </row>
     <row r="583" spans="1:15">
@@ -18517,7 +18552,7 @@
         <v>6</v>
       </c>
       <c r="E583" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F583" s="1">
         <v>10210009</v>
@@ -18526,7 +18561,7 @@
         <v>37</v>
       </c>
       <c r="O583" s="1" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
     </row>
     <row r="584" spans="1:15">
@@ -18543,7 +18578,7 @@
         <v>7</v>
       </c>
       <c r="E584" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F584" s="1">
         <v>10210009</v>
@@ -18552,7 +18587,7 @@
         <v>39</v>
       </c>
       <c r="O584" s="1" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
     </row>
     <row r="585" spans="1:15">
@@ -18569,7 +18604,7 @@
         <v>8</v>
       </c>
       <c r="E585" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F585" s="1">
         <v>10210009</v>
@@ -18578,7 +18613,7 @@
         <v>41</v>
       </c>
       <c r="O585" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
     </row>
     <row r="586" spans="1:15">
@@ -18595,7 +18630,7 @@
         <v>9</v>
       </c>
       <c r="E586" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F586" s="1">
         <v>10210009</v>
@@ -18604,7 +18639,7 @@
         <v>43</v>
       </c>
       <c r="O586" s="1" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
     </row>
     <row r="587" spans="1:15">
@@ -18621,7 +18656,7 @@
         <v>10</v>
       </c>
       <c r="E587" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F587" s="1">
         <v>10210009</v>
@@ -18630,7 +18665,7 @@
         <v>45</v>
       </c>
       <c r="O587" s="1" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
     </row>
     <row r="588" spans="1:15">
@@ -18647,7 +18682,7 @@
         <v>0</v>
       </c>
       <c r="E588" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F588" s="1">
         <v>10210010</v>
@@ -18670,7 +18705,7 @@
         <v>1</v>
       </c>
       <c r="E589" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F589" s="1">
         <v>10210010</v>
@@ -18679,10 +18714,10 @@
         <v>27</v>
       </c>
       <c r="L589" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M589" s="1" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
     </row>
     <row r="590" spans="1:15">
@@ -18699,7 +18734,7 @@
         <v>2</v>
       </c>
       <c r="E590" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F590" s="1">
         <v>10210010</v>
@@ -18708,10 +18743,10 @@
         <v>29</v>
       </c>
       <c r="L590" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M590" s="1" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
     </row>
     <row r="591" spans="1:15">
@@ -18728,7 +18763,7 @@
         <v>3</v>
       </c>
       <c r="E591" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F591" s="1">
         <v>10210010</v>
@@ -18737,10 +18772,10 @@
         <v>31</v>
       </c>
       <c r="L591" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M591" s="1" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
     </row>
     <row r="592" spans="1:15">
@@ -18757,7 +18792,7 @@
         <v>4</v>
       </c>
       <c r="E592" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F592" s="1">
         <v>10210010</v>
@@ -18766,10 +18801,10 @@
         <v>33</v>
       </c>
       <c r="L592" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M592" s="1" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
     </row>
     <row r="593" spans="1:15">
@@ -18786,7 +18821,7 @@
         <v>5</v>
       </c>
       <c r="E593" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F593" s="1">
         <v>10210010</v>
@@ -18795,10 +18830,10 @@
         <v>35</v>
       </c>
       <c r="L593" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M593" s="1" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
     </row>
     <row r="594" spans="1:15">
@@ -18815,7 +18850,7 @@
         <v>6</v>
       </c>
       <c r="E594" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F594" s="1">
         <v>10210010</v>
@@ -18824,10 +18859,10 @@
         <v>37</v>
       </c>
       <c r="L594" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M594" s="1" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
     </row>
     <row r="595" spans="1:15">
@@ -18844,7 +18879,7 @@
         <v>7</v>
       </c>
       <c r="E595" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F595" s="1">
         <v>10210010</v>
@@ -18853,10 +18888,10 @@
         <v>39</v>
       </c>
       <c r="L595" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M595" s="1" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
     </row>
     <row r="596" spans="1:15">
@@ -18873,7 +18908,7 @@
         <v>8</v>
       </c>
       <c r="E596" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F596" s="1">
         <v>10210010</v>
@@ -18882,10 +18917,10 @@
         <v>41</v>
       </c>
       <c r="L596" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M596" s="1" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
     </row>
     <row r="597" spans="1:15">
@@ -18902,7 +18937,7 @@
         <v>9</v>
       </c>
       <c r="E597" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F597" s="1">
         <v>10210010</v>
@@ -18911,10 +18946,10 @@
         <v>43</v>
       </c>
       <c r="L597" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M597" s="1" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
     </row>
     <row r="598" spans="1:15">
@@ -18931,7 +18966,7 @@
         <v>10</v>
       </c>
       <c r="E598" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F598" s="1">
         <v>10210010</v>
@@ -18940,10 +18975,10 @@
         <v>45</v>
       </c>
       <c r="L598" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="M598" s="1" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
     </row>
     <row r="599" spans="1:15">
@@ -18960,7 +18995,7 @@
         <v>0</v>
       </c>
       <c r="E599" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F599" s="1">
         <v>10210011</v>
@@ -18983,7 +19018,7 @@
         <v>1</v>
       </c>
       <c r="E600" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F600" s="1">
         <v>10210011</v>
@@ -18992,7 +19027,7 @@
         <v>27</v>
       </c>
       <c r="O600" s="1" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
     </row>
     <row r="601" spans="1:15">
@@ -19009,7 +19044,7 @@
         <v>2</v>
       </c>
       <c r="E601" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F601" s="1">
         <v>10210011</v>
@@ -19018,7 +19053,7 @@
         <v>29</v>
       </c>
       <c r="O601" s="1" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
     </row>
     <row r="602" spans="1:15">
@@ -19035,7 +19070,7 @@
         <v>3</v>
       </c>
       <c r="E602" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F602" s="1">
         <v>10210011</v>
@@ -19044,7 +19079,7 @@
         <v>31</v>
       </c>
       <c r="O602" s="1" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
     </row>
     <row r="603" spans="1:15">
@@ -19061,7 +19096,7 @@
         <v>4</v>
       </c>
       <c r="E603" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F603" s="1">
         <v>10210011</v>
@@ -19070,7 +19105,7 @@
         <v>33</v>
       </c>
       <c r="O603" s="1" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
     </row>
     <row r="604" spans="1:15">
@@ -19087,7 +19122,7 @@
         <v>5</v>
       </c>
       <c r="E604" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F604" s="1">
         <v>10210011</v>
@@ -19096,7 +19131,7 @@
         <v>35</v>
       </c>
       <c r="O604" s="1" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
     </row>
     <row r="605" spans="1:15">
@@ -19113,7 +19148,7 @@
         <v>6</v>
       </c>
       <c r="E605" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F605" s="1">
         <v>10210011</v>
@@ -19122,7 +19157,7 @@
         <v>37</v>
       </c>
       <c r="O605" s="1" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
     </row>
     <row r="606" spans="1:15">
@@ -19139,7 +19174,7 @@
         <v>7</v>
       </c>
       <c r="E606" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F606" s="1">
         <v>10210011</v>
@@ -19148,7 +19183,7 @@
         <v>39</v>
       </c>
       <c r="O606" s="1" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
     </row>
     <row r="607" spans="1:15">
@@ -19165,7 +19200,7 @@
         <v>8</v>
       </c>
       <c r="E607" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F607" s="1">
         <v>10210011</v>
@@ -19174,7 +19209,7 @@
         <v>41</v>
       </c>
       <c r="O607" s="1" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
     </row>
     <row r="608" spans="1:15">
@@ -19191,7 +19226,7 @@
         <v>9</v>
       </c>
       <c r="E608" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F608" s="1">
         <v>10210011</v>
@@ -19200,7 +19235,7 @@
         <v>43</v>
       </c>
       <c r="O608" s="1" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
     </row>
     <row r="609" spans="1:15">
@@ -19217,7 +19252,7 @@
         <v>10</v>
       </c>
       <c r="E609" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F609" s="1">
         <v>10210011</v>
@@ -19226,7 +19261,7 @@
         <v>45</v>
       </c>
       <c r="O609" s="1" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
     </row>
     <row r="610" spans="1:15">
@@ -19243,7 +19278,7 @@
         <v>0</v>
       </c>
       <c r="E610" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F610" s="1">
         <v>10210012</v>
@@ -19266,7 +19301,7 @@
         <v>1</v>
       </c>
       <c r="E611" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F611" s="1">
         <v>10210012</v>
@@ -19275,7 +19310,7 @@
         <v>27</v>
       </c>
       <c r="O611" s="1" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
     </row>
     <row r="612" spans="1:15">
@@ -19292,7 +19327,7 @@
         <v>2</v>
       </c>
       <c r="E612" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F612" s="1">
         <v>10210012</v>
@@ -19301,7 +19336,7 @@
         <v>29</v>
       </c>
       <c r="O612" s="1" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
     </row>
     <row r="613" spans="1:15">
@@ -19318,7 +19353,7 @@
         <v>3</v>
       </c>
       <c r="E613" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F613" s="1">
         <v>10210012</v>
@@ -19327,7 +19362,7 @@
         <v>31</v>
       </c>
       <c r="O613" s="1" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
     </row>
     <row r="614" spans="1:15">
@@ -19344,7 +19379,7 @@
         <v>4</v>
       </c>
       <c r="E614" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F614" s="1">
         <v>10210012</v>
@@ -19353,7 +19388,7 @@
         <v>33</v>
       </c>
       <c r="O614" s="1" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
     </row>
     <row r="615" spans="1:15">
@@ -19370,7 +19405,7 @@
         <v>5</v>
       </c>
       <c r="E615" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F615" s="1">
         <v>10210012</v>
@@ -19379,7 +19414,7 @@
         <v>35</v>
       </c>
       <c r="O615" s="1" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
     </row>
     <row r="616" spans="1:15">
@@ -19396,7 +19431,7 @@
         <v>6</v>
       </c>
       <c r="E616" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F616" s="1">
         <v>10210012</v>
@@ -19405,7 +19440,7 @@
         <v>37</v>
       </c>
       <c r="O616" s="1" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
     </row>
     <row r="617" spans="1:15">
@@ -19422,7 +19457,7 @@
         <v>7</v>
       </c>
       <c r="E617" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F617" s="1">
         <v>10210012</v>
@@ -19431,7 +19466,7 @@
         <v>39</v>
       </c>
       <c r="O617" s="1" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
     </row>
     <row r="618" spans="1:15">
@@ -19448,7 +19483,7 @@
         <v>8</v>
       </c>
       <c r="E618" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F618" s="1">
         <v>10210012</v>
@@ -19457,7 +19492,7 @@
         <v>41</v>
       </c>
       <c r="O618" s="1" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
     </row>
     <row r="619" spans="1:15">
@@ -19474,7 +19509,7 @@
         <v>9</v>
       </c>
       <c r="E619" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F619" s="1">
         <v>10210012</v>
@@ -19483,7 +19518,7 @@
         <v>43</v>
       </c>
       <c r="O619" s="1" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
     </row>
     <row r="620" spans="1:15">
@@ -19500,7 +19535,7 @@
         <v>10</v>
       </c>
       <c r="E620" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F620" s="1">
         <v>10210012</v>
@@ -19509,7 +19544,7 @@
         <v>45</v>
       </c>
       <c r="O620" s="1" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
     </row>
     <row r="621" spans="1:15">
@@ -19526,7 +19561,7 @@
         <v>0</v>
       </c>
       <c r="E621" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F621" s="1">
         <v>10210013</v>
@@ -19549,7 +19584,7 @@
         <v>1</v>
       </c>
       <c r="E622" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F622" s="1">
         <v>10210013</v>
@@ -19558,10 +19593,10 @@
         <v>27</v>
       </c>
       <c r="L622" s="1" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="M622" s="1" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
     </row>
     <row r="623" spans="1:15">
@@ -19578,7 +19613,7 @@
         <v>2</v>
       </c>
       <c r="E623" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F623" s="1">
         <v>10210013</v>
@@ -19587,10 +19622,10 @@
         <v>29</v>
       </c>
       <c r="L623" s="1" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="M623" s="1" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="624" spans="1:15">
@@ -19607,7 +19642,7 @@
         <v>3</v>
       </c>
       <c r="E624" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F624" s="1">
         <v>10210013</v>
@@ -19616,10 +19651,10 @@
         <v>31</v>
       </c>
       <c r="L624" s="1" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="M624" s="1" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
     </row>
     <row r="625" spans="1:13">
@@ -19636,7 +19671,7 @@
         <v>4</v>
       </c>
       <c r="E625" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F625" s="1">
         <v>10210013</v>
@@ -19645,10 +19680,10 @@
         <v>33</v>
       </c>
       <c r="L625" s="1" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="M625" s="1" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
     </row>
     <row r="626" spans="1:13">
@@ -19665,7 +19700,7 @@
         <v>5</v>
       </c>
       <c r="E626" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F626" s="1">
         <v>10210013</v>
@@ -19674,10 +19709,10 @@
         <v>35</v>
       </c>
       <c r="L626" s="1" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="M626" s="1" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
     </row>
     <row r="627" spans="1:13">
@@ -19694,7 +19729,7 @@
         <v>6</v>
       </c>
       <c r="E627" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F627" s="1">
         <v>10210013</v>
@@ -19703,10 +19738,10 @@
         <v>37</v>
       </c>
       <c r="L627" s="1" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="M627" s="1" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="628" spans="1:13">
@@ -19723,7 +19758,7 @@
         <v>7</v>
       </c>
       <c r="E628" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F628" s="1">
         <v>10210013</v>
@@ -19732,10 +19767,10 @@
         <v>39</v>
       </c>
       <c r="L628" s="1" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="M628" s="1" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
     </row>
     <row r="629" spans="1:13">
@@ -19752,7 +19787,7 @@
         <v>8</v>
       </c>
       <c r="E629" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F629" s="1">
         <v>10210013</v>
@@ -19761,10 +19796,10 @@
         <v>41</v>
       </c>
       <c r="L629" s="1" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="M629" s="1" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="630" spans="1:13">
@@ -19781,7 +19816,7 @@
         <v>9</v>
       </c>
       <c r="E630" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F630" s="1">
         <v>10210013</v>
@@ -19790,10 +19825,10 @@
         <v>43</v>
       </c>
       <c r="L630" s="1" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="M630" s="1" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
     </row>
     <row r="631" spans="1:13">
@@ -19810,7 +19845,7 @@
         <v>10</v>
       </c>
       <c r="E631" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="F631" s="1">
         <v>10210013</v>
@@ -19819,10 +19854,10 @@
         <v>45</v>
       </c>
       <c r="L631" s="1" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="M631" s="1" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/ResearchSkills.xlsx
+++ b/hall/resources/sample/ResearchSkills.xlsx
@@ -201,7 +201,7 @@
     <t>Map&lt;int{,}int&gt;{|}</t>
   </si>
   <si>
-    <t>list&lt;int&gt;{_}</t>
+    <t>list&lt;long&gt;{_}</t>
   </si>
   <si>
     <t>map&lt;int{,}map&lt;int{_}int&gt;{|}&gt;{;}</t>
@@ -1588,12 +1588,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/hall/resources/sample/ResearchSkills.xlsx
+++ b/hall/resources/sample/ResearchSkills.xlsx
@@ -31628,7 +31628,7 @@
         <v>33</v>
       </c>
       <c r="G881" s="2">
-        <v>4020391</v>
+        <v>4020381</v>
       </c>
       <c r="H881" s="2">
         <v>1000</v>
@@ -31661,7 +31661,7 @@
         <v>33</v>
       </c>
       <c r="G882" s="2">
-        <v>4020392</v>
+        <v>4020382</v>
       </c>
       <c r="H882" s="2">
         <v>2000</v>
@@ -31694,7 +31694,7 @@
         <v>33</v>
       </c>
       <c r="G883" s="2">
-        <v>4020393</v>
+        <v>4020383</v>
       </c>
       <c r="H883" s="2">
         <v>3000</v>
@@ -31727,7 +31727,7 @@
         <v>33</v>
       </c>
       <c r="G884" s="2">
-        <v>4020394</v>
+        <v>4020384</v>
       </c>
       <c r="H884" s="2">
         <v>4000</v>
@@ -31760,7 +31760,7 @@
         <v>33</v>
       </c>
       <c r="G885" s="2">
-        <v>4020395</v>
+        <v>4020385</v>
       </c>
       <c r="H885" s="2">
         <v>5000</v>
@@ -31793,7 +31793,7 @@
         <v>33</v>
       </c>
       <c r="G886" s="2">
-        <v>4020396</v>
+        <v>4020386</v>
       </c>
       <c r="H886" s="2">
         <v>6000</v>
@@ -31826,7 +31826,7 @@
         <v>33</v>
       </c>
       <c r="G887" s="2">
-        <v>4020397</v>
+        <v>4020387</v>
       </c>
       <c r="H887" s="2">
         <v>7000</v>
@@ -31859,7 +31859,7 @@
         <v>33</v>
       </c>
       <c r="G888" s="2">
-        <v>4020398</v>
+        <v>4020388</v>
       </c>
       <c r="H888" s="2">
         <v>8000</v>
@@ -31892,7 +31892,7 @@
         <v>33</v>
       </c>
       <c r="G889" s="2">
-        <v>4020399</v>
+        <v>4020389</v>
       </c>
       <c r="H889" s="2">
         <v>9000</v>
@@ -31925,7 +31925,7 @@
         <v>33</v>
       </c>
       <c r="G890" s="2">
-        <v>4020400</v>
+        <v>4020390</v>
       </c>
       <c r="H890" s="2">
         <v>10000</v>
@@ -31981,7 +31981,7 @@
         <v>33</v>
       </c>
       <c r="G892" s="2">
-        <v>4020401</v>
+        <v>4020391</v>
       </c>
       <c r="H892" s="2">
         <v>1000</v>
@@ -32014,7 +32014,7 @@
         <v>33</v>
       </c>
       <c r="G893" s="2">
-        <v>4020402</v>
+        <v>4020392</v>
       </c>
       <c r="H893" s="2">
         <v>2000</v>
@@ -32047,7 +32047,7 @@
         <v>33</v>
       </c>
       <c r="G894" s="2">
-        <v>4020403</v>
+        <v>4020393</v>
       </c>
       <c r="H894" s="2">
         <v>3000</v>
@@ -32080,7 +32080,7 @@
         <v>33</v>
       </c>
       <c r="G895" s="2">
-        <v>4020404</v>
+        <v>4020394</v>
       </c>
       <c r="H895" s="2">
         <v>4000</v>
@@ -32113,7 +32113,7 @@
         <v>33</v>
       </c>
       <c r="G896" s="2">
-        <v>4020405</v>
+        <v>4020395</v>
       </c>
       <c r="H896" s="2">
         <v>5000</v>
@@ -32146,7 +32146,7 @@
         <v>33</v>
       </c>
       <c r="G897" s="2">
-        <v>4020406</v>
+        <v>4020396</v>
       </c>
       <c r="H897" s="2">
         <v>6000</v>
@@ -32179,7 +32179,7 @@
         <v>33</v>
       </c>
       <c r="G898" s="2">
-        <v>4020407</v>
+        <v>4020397</v>
       </c>
       <c r="H898" s="2">
         <v>7000</v>
@@ -32212,7 +32212,7 @@
         <v>33</v>
       </c>
       <c r="G899" s="2">
-        <v>4020408</v>
+        <v>4020398</v>
       </c>
       <c r="H899" s="2">
         <v>8000</v>
@@ -32245,7 +32245,7 @@
         <v>33</v>
       </c>
       <c r="G900" s="2">
-        <v>4020409</v>
+        <v>4020399</v>
       </c>
       <c r="H900" s="2">
         <v>9000</v>
@@ -32278,7 +32278,7 @@
         <v>33</v>
       </c>
       <c r="G901" s="2">
-        <v>4020410</v>
+        <v>4020400</v>
       </c>
       <c r="H901" s="2">
         <v>10000</v>

--- a/hall/resources/sample/ResearchSkills.xlsx
+++ b/hall/resources/sample/ResearchSkills.xlsx
@@ -35051,7 +35051,7 @@
         <v>33</v>
       </c>
       <c r="G989" s="2">
-        <v>4020391</v>
+        <v>4020381</v>
       </c>
       <c r="H989" s="2">
         <v>1000</v>
@@ -35084,7 +35084,7 @@
         <v>33</v>
       </c>
       <c r="G990" s="2">
-        <v>4020392</v>
+        <v>4020382</v>
       </c>
       <c r="H990" s="2">
         <v>2000</v>
@@ -35117,7 +35117,7 @@
         <v>33</v>
       </c>
       <c r="G991" s="2">
-        <v>4020393</v>
+        <v>4020383</v>
       </c>
       <c r="H991" s="2">
         <v>3000</v>
@@ -35150,7 +35150,7 @@
         <v>33</v>
       </c>
       <c r="G992" s="2">
-        <v>4020394</v>
+        <v>4020384</v>
       </c>
       <c r="H992" s="2">
         <v>4000</v>
@@ -35183,7 +35183,7 @@
         <v>33</v>
       </c>
       <c r="G993" s="2">
-        <v>4020395</v>
+        <v>4020385</v>
       </c>
       <c r="H993" s="2">
         <v>5000</v>
@@ -35216,7 +35216,7 @@
         <v>33</v>
       </c>
       <c r="G994" s="2">
-        <v>4020396</v>
+        <v>4020386</v>
       </c>
       <c r="H994" s="2">
         <v>6000</v>
@@ -35249,7 +35249,7 @@
         <v>33</v>
       </c>
       <c r="G995" s="2">
-        <v>4020397</v>
+        <v>4020387</v>
       </c>
       <c r="H995" s="2">
         <v>7000</v>
@@ -35282,7 +35282,7 @@
         <v>33</v>
       </c>
       <c r="G996" s="2">
-        <v>4020398</v>
+        <v>4020388</v>
       </c>
       <c r="H996" s="2">
         <v>8000</v>
@@ -35315,7 +35315,7 @@
         <v>33</v>
       </c>
       <c r="G997" s="2">
-        <v>4020399</v>
+        <v>4020389</v>
       </c>
       <c r="H997" s="2">
         <v>9000</v>
@@ -35348,7 +35348,7 @@
         <v>33</v>
       </c>
       <c r="G998" s="2">
-        <v>4020400</v>
+        <v>4020390</v>
       </c>
       <c r="H998" s="2">
         <v>10000</v>
@@ -35404,7 +35404,7 @@
         <v>33</v>
       </c>
       <c r="G1000" s="2">
-        <v>4020401</v>
+        <v>4020391</v>
       </c>
       <c r="H1000" s="2">
         <v>1000</v>
@@ -35437,7 +35437,7 @@
         <v>33</v>
       </c>
       <c r="G1001" s="2">
-        <v>4020402</v>
+        <v>4020392</v>
       </c>
       <c r="H1001" s="2">
         <v>2000</v>
@@ -35470,7 +35470,7 @@
         <v>33</v>
       </c>
       <c r="G1002" s="2">
-        <v>4020403</v>
+        <v>4020393</v>
       </c>
       <c r="H1002" s="2">
         <v>3000</v>
@@ -35503,7 +35503,7 @@
         <v>33</v>
       </c>
       <c r="G1003" s="2">
-        <v>4020404</v>
+        <v>4020394</v>
       </c>
       <c r="H1003" s="2">
         <v>4000</v>
@@ -35536,7 +35536,7 @@
         <v>33</v>
       </c>
       <c r="G1004" s="2">
-        <v>4020405</v>
+        <v>4020395</v>
       </c>
       <c r="H1004" s="2">
         <v>5000</v>
@@ -35569,7 +35569,7 @@
         <v>33</v>
       </c>
       <c r="G1005" s="2">
-        <v>4020406</v>
+        <v>4020396</v>
       </c>
       <c r="H1005" s="2">
         <v>6000</v>
@@ -35602,7 +35602,7 @@
         <v>33</v>
       </c>
       <c r="G1006" s="2">
-        <v>4020407</v>
+        <v>4020397</v>
       </c>
       <c r="H1006" s="2">
         <v>7000</v>
@@ -35635,7 +35635,7 @@
         <v>33</v>
       </c>
       <c r="G1007" s="2">
-        <v>4020408</v>
+        <v>4020398</v>
       </c>
       <c r="H1007" s="2">
         <v>8000</v>
@@ -35668,7 +35668,7 @@
         <v>33</v>
       </c>
       <c r="G1008" s="2">
-        <v>4020409</v>
+        <v>4020399</v>
       </c>
       <c r="H1008" s="2">
         <v>9000</v>
@@ -35701,7 +35701,7 @@
         <v>33</v>
       </c>
       <c r="G1009" s="2">
-        <v>4020410</v>
+        <v>4020400</v>
       </c>
       <c r="H1009" s="2">
         <v>10000</v>

--- a/hall/resources/sample/ResearchSkills.xlsx
+++ b/hall/resources/sample/ResearchSkills.xlsx
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3784" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4045" uniqueCount="859">
   <si>
     <t>id</t>
   </si>
@@ -2701,6 +2701,39 @@
   </si>
   <si>
     <t>3,9</t>
+  </si>
+  <si>
+    <t>财神到</t>
+  </si>
+  <si>
+    <t>触发财神到游戏概率提升1%</t>
+  </si>
+  <si>
+    <t>触发财神到游戏概率提升2%</t>
+  </si>
+  <si>
+    <t>触发财神到游戏概率提升3%</t>
+  </si>
+  <si>
+    <t>触发财神到游戏概率提升4%</t>
+  </si>
+  <si>
+    <t>触发财神到游戏概率提升5%</t>
+  </si>
+  <si>
+    <t>触发财神到游戏概率提升6%</t>
+  </si>
+  <si>
+    <t>触发财神到游戏概率提升7%</t>
+  </si>
+  <si>
+    <t>触发财神到游戏概率提升8%</t>
+  </si>
+  <si>
+    <t>触发财神到游戏概率提升9%</t>
+  </si>
+  <si>
+    <t>触发财神到游戏概率提升10%</t>
   </si>
 </sst>
 </file>
@@ -3717,7 +3750,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R1029"/>
+  <dimension ref="A1:R1115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13.5" style="1" customWidth="1"/>
@@ -36323,9 +36356,2576 @@
         <v>99999</v>
       </c>
     </row>
+    <row r="1030" spans="1:18">
+      <c r="A1030" s="1">
+        <v>101026</v>
+      </c>
+      <c r="B1030" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1030" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1030" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1030" s="1">
+        <v>10120001</v>
+      </c>
+      <c r="F1030" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1030" s="2"/>
+      <c r="H1030" s="2"/>
+      <c r="I1030" s="2"/>
+    </row>
+    <row r="1031" spans="1:18">
+      <c r="A1031" s="1">
+        <v>101027</v>
+      </c>
+      <c r="B1031" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1031" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1031" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1031" s="1">
+        <v>10120001</v>
+      </c>
+      <c r="F1031" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1031" s="2">
+        <v>4020027</v>
+      </c>
+      <c r="H1031" s="2">
+        <v>100</v>
+      </c>
+      <c r="I1031" s="2">
+        <v>2000</v>
+      </c>
+      <c r="J1031" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:18">
+      <c r="A1032" s="1">
+        <v>101028</v>
+      </c>
+      <c r="B1032" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1032" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1032" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1032" s="1">
+        <v>10120001</v>
+      </c>
+      <c r="F1032" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1032" s="2">
+        <v>4020028</v>
+      </c>
+      <c r="H1032" s="2">
+        <v>200</v>
+      </c>
+      <c r="I1032" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1032" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:18">
+      <c r="A1033" s="1">
+        <v>101029</v>
+      </c>
+      <c r="B1033" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1033" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1033" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1033" s="1">
+        <v>10120001</v>
+      </c>
+      <c r="F1033" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1033" s="2">
+        <v>4020029</v>
+      </c>
+      <c r="H1033" s="2">
+        <v>300</v>
+      </c>
+      <c r="I1033" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1033" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:18">
+      <c r="A1034" s="1">
+        <v>101030</v>
+      </c>
+      <c r="B1034" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1034" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1034" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1034" s="1">
+        <v>10120001</v>
+      </c>
+      <c r="F1034" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1034" s="2">
+        <v>4020030</v>
+      </c>
+      <c r="H1034" s="2">
+        <v>400</v>
+      </c>
+      <c r="I1034" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1034" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:18">
+      <c r="A1035" s="1">
+        <v>101031</v>
+      </c>
+      <c r="B1035" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1035" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1035" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1035" s="1">
+        <v>10120001</v>
+      </c>
+      <c r="F1035" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1035" s="2">
+        <v>4020031</v>
+      </c>
+      <c r="H1035" s="2">
+        <v>500</v>
+      </c>
+      <c r="I1035" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1035" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:18">
+      <c r="A1036" s="1">
+        <v>101032</v>
+      </c>
+      <c r="B1036" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1036" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1036" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1036" s="1">
+        <v>10120001</v>
+      </c>
+      <c r="F1036" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1036" s="2">
+        <v>4020032</v>
+      </c>
+      <c r="H1036" s="2">
+        <v>600</v>
+      </c>
+      <c r="I1036" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1036" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:18">
+      <c r="A1037" s="1">
+        <v>101033</v>
+      </c>
+      <c r="B1037" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1037" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1037" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1037" s="1">
+        <v>10120001</v>
+      </c>
+      <c r="F1037" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1037" s="2">
+        <v>4020033</v>
+      </c>
+      <c r="H1037" s="2">
+        <v>700</v>
+      </c>
+      <c r="I1037" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1037" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:18">
+      <c r="A1038" s="1">
+        <v>101034</v>
+      </c>
+      <c r="B1038" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1038" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1038" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1038" s="1">
+        <v>10120001</v>
+      </c>
+      <c r="F1038" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1038" s="2">
+        <v>4020034</v>
+      </c>
+      <c r="H1038" s="2">
+        <v>800</v>
+      </c>
+      <c r="I1038" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1038" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:18">
+      <c r="A1039" s="1">
+        <v>101035</v>
+      </c>
+      <c r="B1039" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1039" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1039" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1039" s="1">
+        <v>10120001</v>
+      </c>
+      <c r="F1039" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1039" s="2">
+        <v>4020035</v>
+      </c>
+      <c r="H1039" s="2">
+        <v>900</v>
+      </c>
+      <c r="I1039" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1039" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:18">
+      <c r="A1040" s="1">
+        <v>101036</v>
+      </c>
+      <c r="B1040" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1040" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1040" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1040" s="1">
+        <v>10120001</v>
+      </c>
+      <c r="F1040" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1040" s="2">
+        <v>4020036</v>
+      </c>
+      <c r="H1040" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I1040" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1040" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:12">
+      <c r="A1041" s="1">
+        <v>101037</v>
+      </c>
+      <c r="B1041" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1041" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1041" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1041" s="1">
+        <v>10120002</v>
+      </c>
+      <c r="F1041" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1041" s="2"/>
+      <c r="H1041" s="2"/>
+      <c r="I1041" s="2"/>
+    </row>
+    <row r="1042" spans="1:12">
+      <c r="A1042" s="1">
+        <v>101038</v>
+      </c>
+      <c r="B1042" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1042" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1042" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1042" s="1">
+        <v>10120002</v>
+      </c>
+      <c r="F1042" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1042" s="2">
+        <v>4020037</v>
+      </c>
+      <c r="H1042" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I1042" s="2"/>
+      <c r="K1042" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1042" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:12">
+      <c r="A1043" s="1">
+        <v>101039</v>
+      </c>
+      <c r="B1043" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1043" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1043" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1043" s="1">
+        <v>10120002</v>
+      </c>
+      <c r="F1043" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1043" s="2">
+        <v>4020038</v>
+      </c>
+      <c r="H1043" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I1043" s="2"/>
+      <c r="K1043" s="10" t="s">
+        <v>772</v>
+      </c>
+      <c r="L1043" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:12">
+      <c r="A1044" s="1">
+        <v>101040</v>
+      </c>
+      <c r="B1044" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1044" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1044" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1044" s="1">
+        <v>10120002</v>
+      </c>
+      <c r="F1044" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1044" s="2">
+        <v>4020039</v>
+      </c>
+      <c r="H1044" s="2">
+        <v>3000</v>
+      </c>
+      <c r="I1044" s="2"/>
+      <c r="K1044" s="10" t="s">
+        <v>773</v>
+      </c>
+      <c r="L1044" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:12">
+      <c r="A1045" s="1">
+        <v>101041</v>
+      </c>
+      <c r="B1045" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1045" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1045" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1045" s="1">
+        <v>10120002</v>
+      </c>
+      <c r="F1045" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1045" s="2">
+        <v>4020040</v>
+      </c>
+      <c r="H1045" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I1045" s="2"/>
+      <c r="K1045" s="10" t="s">
+        <v>774</v>
+      </c>
+      <c r="L1045" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:12">
+      <c r="A1046" s="1">
+        <v>101042</v>
+      </c>
+      <c r="B1046" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1046" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1046" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1046" s="1">
+        <v>10120002</v>
+      </c>
+      <c r="F1046" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1046" s="2">
+        <v>4020041</v>
+      </c>
+      <c r="H1046" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I1046" s="2"/>
+      <c r="K1046" s="10" t="s">
+        <v>775</v>
+      </c>
+      <c r="L1046" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:12">
+      <c r="A1047" s="1">
+        <v>101043</v>
+      </c>
+      <c r="B1047" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1047" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1047" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1047" s="1">
+        <v>10120002</v>
+      </c>
+      <c r="F1047" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1047" s="2">
+        <v>4020042</v>
+      </c>
+      <c r="H1047" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I1047" s="2"/>
+      <c r="K1047" s="10" t="s">
+        <v>776</v>
+      </c>
+      <c r="L1047" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:12">
+      <c r="A1048" s="1">
+        <v>101044</v>
+      </c>
+      <c r="B1048" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1048" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1048" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1048" s="1">
+        <v>10120002</v>
+      </c>
+      <c r="F1048" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1048" s="2">
+        <v>4020043</v>
+      </c>
+      <c r="H1048" s="2">
+        <v>7000</v>
+      </c>
+      <c r="I1048" s="2"/>
+      <c r="K1048" s="10" t="s">
+        <v>777</v>
+      </c>
+      <c r="L1048" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:12">
+      <c r="A1049" s="1">
+        <v>101045</v>
+      </c>
+      <c r="B1049" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1049" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1049" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1049" s="1">
+        <v>10120002</v>
+      </c>
+      <c r="F1049" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1049" s="2">
+        <v>4020044</v>
+      </c>
+      <c r="H1049" s="2">
+        <v>8000</v>
+      </c>
+      <c r="I1049" s="2"/>
+      <c r="K1049" s="10" t="s">
+        <v>778</v>
+      </c>
+      <c r="L1049" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:12">
+      <c r="A1050" s="1">
+        <v>101046</v>
+      </c>
+      <c r="B1050" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1050" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1050" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1050" s="1">
+        <v>10120002</v>
+      </c>
+      <c r="F1050" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1050" s="2">
+        <v>4020045</v>
+      </c>
+      <c r="H1050" s="2">
+        <v>9000</v>
+      </c>
+      <c r="I1050" s="2"/>
+      <c r="K1050" s="10" t="s">
+        <v>779</v>
+      </c>
+      <c r="L1050" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:12">
+      <c r="A1051" s="1">
+        <v>101047</v>
+      </c>
+      <c r="B1051" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1051" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1051" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1051" s="1">
+        <v>10120002</v>
+      </c>
+      <c r="F1051" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1051" s="2">
+        <v>4020046</v>
+      </c>
+      <c r="H1051" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I1051" s="2"/>
+      <c r="K1051" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="L1051" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:12">
+      <c r="A1052" s="1">
+        <v>101048</v>
+      </c>
+      <c r="B1052" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1052" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1052" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1052" s="1">
+        <v>10120003</v>
+      </c>
+      <c r="F1052" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1052" s="2"/>
+      <c r="H1052" s="2"/>
+      <c r="I1052" s="2"/>
+    </row>
+    <row r="1053" spans="1:12">
+      <c r="A1053" s="1">
+        <v>101049</v>
+      </c>
+      <c r="B1053" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1053" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1053" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1053" s="1">
+        <v>10120003</v>
+      </c>
+      <c r="F1053" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1053" s="2">
+        <v>4020047</v>
+      </c>
+      <c r="H1053" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I1053" s="2"/>
+      <c r="L1053" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:12">
+      <c r="A1054" s="1">
+        <v>101050</v>
+      </c>
+      <c r="B1054" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1054" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1054" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1054" s="1">
+        <v>10120003</v>
+      </c>
+      <c r="F1054" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1054" s="2">
+        <v>4020048</v>
+      </c>
+      <c r="H1054" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I1054" s="2"/>
+      <c r="L1054" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:12">
+      <c r="A1055" s="1">
+        <v>101051</v>
+      </c>
+      <c r="B1055" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1055" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1055" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1055" s="1">
+        <v>10120003</v>
+      </c>
+      <c r="F1055" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1055" s="2">
+        <v>4020049</v>
+      </c>
+      <c r="H1055" s="2">
+        <v>3000</v>
+      </c>
+      <c r="I1055" s="2"/>
+      <c r="L1055" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:12">
+      <c r="A1056" s="1">
+        <v>101052</v>
+      </c>
+      <c r="B1056" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1056" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1056" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1056" s="1">
+        <v>10120003</v>
+      </c>
+      <c r="F1056" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1056" s="2">
+        <v>4020050</v>
+      </c>
+      <c r="H1056" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I1056" s="2"/>
+      <c r="L1056" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:12">
+      <c r="A1057" s="1">
+        <v>101053</v>
+      </c>
+      <c r="B1057" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1057" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1057" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1057" s="1">
+        <v>10120003</v>
+      </c>
+      <c r="F1057" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1057" s="2">
+        <v>4020051</v>
+      </c>
+      <c r="H1057" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I1057" s="2"/>
+      <c r="L1057" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:12">
+      <c r="A1058" s="1">
+        <v>101054</v>
+      </c>
+      <c r="B1058" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1058" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1058" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1058" s="1">
+        <v>10120003</v>
+      </c>
+      <c r="F1058" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1058" s="2">
+        <v>4020052</v>
+      </c>
+      <c r="H1058" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I1058" s="2"/>
+      <c r="L1058" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:12">
+      <c r="A1059" s="1">
+        <v>101055</v>
+      </c>
+      <c r="B1059" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1059" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1059" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1059" s="1">
+        <v>10120003</v>
+      </c>
+      <c r="F1059" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1059" s="2">
+        <v>4020053</v>
+      </c>
+      <c r="H1059" s="2">
+        <v>7000</v>
+      </c>
+      <c r="I1059" s="2"/>
+      <c r="L1059" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:12">
+      <c r="A1060" s="1">
+        <v>101056</v>
+      </c>
+      <c r="B1060" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1060" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1060" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1060" s="1">
+        <v>10120003</v>
+      </c>
+      <c r="F1060" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1060" s="2">
+        <v>4020054</v>
+      </c>
+      <c r="H1060" s="2">
+        <v>8000</v>
+      </c>
+      <c r="I1060" s="2"/>
+      <c r="L1060" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:12">
+      <c r="A1061" s="1">
+        <v>101057</v>
+      </c>
+      <c r="B1061" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1061" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1061" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1061" s="1">
+        <v>10120003</v>
+      </c>
+      <c r="F1061" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1061" s="2">
+        <v>4020055</v>
+      </c>
+      <c r="H1061" s="2">
+        <v>9000</v>
+      </c>
+      <c r="I1061" s="2"/>
+      <c r="L1061" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:12">
+      <c r="A1062" s="1">
+        <v>101058</v>
+      </c>
+      <c r="B1062" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1062" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1062" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1062" s="1">
+        <v>10120003</v>
+      </c>
+      <c r="F1062" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1062" s="2">
+        <v>4020056</v>
+      </c>
+      <c r="H1062" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I1062" s="2"/>
+      <c r="L1062" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:12">
+      <c r="A1063" s="1">
+        <v>101059</v>
+      </c>
+      <c r="B1063" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1063" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1063" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1063" s="1">
+        <v>10120004</v>
+      </c>
+      <c r="F1063" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1063" s="2"/>
+      <c r="H1063" s="2"/>
+      <c r="I1063" s="2"/>
+    </row>
+    <row r="1064" spans="1:12">
+      <c r="A1064" s="1">
+        <v>101060</v>
+      </c>
+      <c r="B1064" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1064" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1064" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1064" s="1">
+        <v>10120004</v>
+      </c>
+      <c r="F1064" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1064" s="2">
+        <v>4020099</v>
+      </c>
+      <c r="H1064" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I1064" s="2"/>
+      <c r="L1064" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:12">
+      <c r="A1065" s="1">
+        <v>101061</v>
+      </c>
+      <c r="B1065" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1065" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1065" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1065" s="1">
+        <v>10120004</v>
+      </c>
+      <c r="F1065" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1065" s="2">
+        <v>4020100</v>
+      </c>
+      <c r="H1065" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I1065" s="2"/>
+      <c r="L1065" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:12">
+      <c r="A1066" s="1">
+        <v>101062</v>
+      </c>
+      <c r="B1066" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1066" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1066" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1066" s="1">
+        <v>10120004</v>
+      </c>
+      <c r="F1066" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1066" s="2">
+        <v>4020101</v>
+      </c>
+      <c r="H1066" s="2">
+        <v>3000</v>
+      </c>
+      <c r="I1066" s="2"/>
+      <c r="L1066" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:12">
+      <c r="A1067" s="1">
+        <v>101063</v>
+      </c>
+      <c r="B1067" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1067" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1067" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1067" s="1">
+        <v>10120004</v>
+      </c>
+      <c r="F1067" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1067" s="2">
+        <v>4020102</v>
+      </c>
+      <c r="H1067" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I1067" s="2"/>
+      <c r="L1067" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:12">
+      <c r="A1068" s="1">
+        <v>101064</v>
+      </c>
+      <c r="B1068" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1068" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1068" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1068" s="1">
+        <v>10120004</v>
+      </c>
+      <c r="F1068" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1068" s="2">
+        <v>4020103</v>
+      </c>
+      <c r="H1068" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I1068" s="2"/>
+      <c r="L1068" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:12">
+      <c r="A1069" s="1">
+        <v>101065</v>
+      </c>
+      <c r="B1069" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1069" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1069" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1069" s="1">
+        <v>10120004</v>
+      </c>
+      <c r="F1069" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1069" s="2">
+        <v>4020104</v>
+      </c>
+      <c r="H1069" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I1069" s="2"/>
+      <c r="L1069" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:12">
+      <c r="A1070" s="1">
+        <v>101066</v>
+      </c>
+      <c r="B1070" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1070" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1070" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1070" s="1">
+        <v>10120004</v>
+      </c>
+      <c r="F1070" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1070" s="2">
+        <v>4020105</v>
+      </c>
+      <c r="H1070" s="2">
+        <v>7000</v>
+      </c>
+      <c r="I1070" s="2"/>
+      <c r="L1070" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:12">
+      <c r="A1071" s="1">
+        <v>101067</v>
+      </c>
+      <c r="B1071" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1071" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1071" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1071" s="1">
+        <v>10120004</v>
+      </c>
+      <c r="F1071" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1071" s="2">
+        <v>4020106</v>
+      </c>
+      <c r="H1071" s="2">
+        <v>8000</v>
+      </c>
+      <c r="I1071" s="2"/>
+      <c r="L1071" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:12">
+      <c r="A1072" s="1">
+        <v>101068</v>
+      </c>
+      <c r="B1072" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1072" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1072" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1072" s="1">
+        <v>10120004</v>
+      </c>
+      <c r="F1072" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1072" s="2">
+        <v>4020107</v>
+      </c>
+      <c r="H1072" s="2">
+        <v>9000</v>
+      </c>
+      <c r="I1072" s="2"/>
+      <c r="L1072" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:14">
+      <c r="A1073" s="1">
+        <v>101069</v>
+      </c>
+      <c r="B1073" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1073" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1073" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1073" s="1">
+        <v>10120004</v>
+      </c>
+      <c r="F1073" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1073" s="2">
+        <v>4020108</v>
+      </c>
+      <c r="H1073" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I1073" s="2"/>
+      <c r="L1073" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:14">
+      <c r="A1074" s="1">
+        <v>101070</v>
+      </c>
+      <c r="B1074" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1074" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1074" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1074" s="1">
+        <v>10120005</v>
+      </c>
+      <c r="F1074" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1074" s="2"/>
+      <c r="H1074" s="2"/>
+      <c r="I1074" s="2"/>
+    </row>
+    <row r="1075" spans="1:14">
+      <c r="A1075" s="1">
+        <v>101071</v>
+      </c>
+      <c r="B1075" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1075" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1075" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1075" s="1">
+        <v>10120005</v>
+      </c>
+      <c r="F1075" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1075" s="2">
+        <v>4020109</v>
+      </c>
+      <c r="H1075" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I1075" s="2"/>
+      <c r="L1075" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:14">
+      <c r="A1076" s="1">
+        <v>101072</v>
+      </c>
+      <c r="B1076" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1076" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1076" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1076" s="1">
+        <v>10120005</v>
+      </c>
+      <c r="F1076" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1076" s="2">
+        <v>4020110</v>
+      </c>
+      <c r="H1076" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I1076" s="2"/>
+      <c r="L1076" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:14">
+      <c r="A1077" s="1">
+        <v>101073</v>
+      </c>
+      <c r="B1077" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1077" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1077" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1077" s="1">
+        <v>10120005</v>
+      </c>
+      <c r="F1077" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1077" s="2">
+        <v>4020111</v>
+      </c>
+      <c r="H1077" s="2">
+        <v>3000</v>
+      </c>
+      <c r="I1077" s="2"/>
+      <c r="L1077" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:14">
+      <c r="A1078" s="1">
+        <v>101074</v>
+      </c>
+      <c r="B1078" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1078" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1078" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1078" s="1">
+        <v>10120005</v>
+      </c>
+      <c r="F1078" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1078" s="2">
+        <v>4020112</v>
+      </c>
+      <c r="H1078" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I1078" s="2"/>
+      <c r="L1078" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:14">
+      <c r="A1079" s="1">
+        <v>101075</v>
+      </c>
+      <c r="B1079" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1079" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1079" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1079" s="1">
+        <v>10120005</v>
+      </c>
+      <c r="F1079" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1079" s="2">
+        <v>4020113</v>
+      </c>
+      <c r="H1079" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I1079" s="2"/>
+      <c r="L1079" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:14">
+      <c r="A1080" s="1">
+        <v>101076</v>
+      </c>
+      <c r="B1080" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1080" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1080" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1080" s="1">
+        <v>10120005</v>
+      </c>
+      <c r="F1080" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1080" s="2">
+        <v>4020114</v>
+      </c>
+      <c r="H1080" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I1080" s="2"/>
+      <c r="L1080" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:14">
+      <c r="A1081" s="1">
+        <v>101077</v>
+      </c>
+      <c r="B1081" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1081" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1081" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1081" s="1">
+        <v>10120005</v>
+      </c>
+      <c r="F1081" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1081" s="2">
+        <v>4020115</v>
+      </c>
+      <c r="H1081" s="2">
+        <v>7000</v>
+      </c>
+      <c r="I1081" s="2"/>
+      <c r="L1081" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:14">
+      <c r="A1082" s="1">
+        <v>101078</v>
+      </c>
+      <c r="B1082" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1082" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1082" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1082" s="1">
+        <v>10120005</v>
+      </c>
+      <c r="F1082" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1082" s="2">
+        <v>4020116</v>
+      </c>
+      <c r="H1082" s="2">
+        <v>8000</v>
+      </c>
+      <c r="I1082" s="2"/>
+      <c r="L1082" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:14">
+      <c r="A1083" s="1">
+        <v>101079</v>
+      </c>
+      <c r="B1083" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1083" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1083" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1083" s="1">
+        <v>10120005</v>
+      </c>
+      <c r="F1083" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1083" s="2">
+        <v>4020117</v>
+      </c>
+      <c r="H1083" s="2">
+        <v>9000</v>
+      </c>
+      <c r="I1083" s="2"/>
+      <c r="L1083" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:14">
+      <c r="A1084" s="1">
+        <v>101080</v>
+      </c>
+      <c r="B1084" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1084" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1084" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1084" s="1">
+        <v>10120005</v>
+      </c>
+      <c r="F1084" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1084" s="2">
+        <v>4020118</v>
+      </c>
+      <c r="H1084" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I1084" s="2"/>
+      <c r="L1084" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:14">
+      <c r="A1085" s="1">
+        <v>101081</v>
+      </c>
+      <c r="B1085" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1085" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1085" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1085" s="1">
+        <v>10120006</v>
+      </c>
+      <c r="F1085" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1085" s="2"/>
+      <c r="H1085" s="2"/>
+      <c r="I1085" s="2"/>
+    </row>
+    <row r="1086" spans="1:14">
+      <c r="A1086" s="1">
+        <v>101082</v>
+      </c>
+      <c r="B1086" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1086" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1086" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1086" s="1">
+        <v>10120006</v>
+      </c>
+      <c r="F1086" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1086" s="2">
+        <v>4020402</v>
+      </c>
+      <c r="H1086" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I1086" s="2"/>
+      <c r="N1086" s="1" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:14">
+      <c r="A1087" s="1">
+        <v>101083</v>
+      </c>
+      <c r="B1087" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1087" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1087" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1087" s="1">
+        <v>10120006</v>
+      </c>
+      <c r="F1087" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1087" s="2">
+        <v>4020403</v>
+      </c>
+      <c r="H1087" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I1087" s="2"/>
+      <c r="N1087" s="1" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:14">
+      <c r="A1088" s="1">
+        <v>101084</v>
+      </c>
+      <c r="B1088" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1088" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1088" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1088" s="1">
+        <v>10120006</v>
+      </c>
+      <c r="F1088" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1088" s="2">
+        <v>4020404</v>
+      </c>
+      <c r="H1088" s="2">
+        <v>3000</v>
+      </c>
+      <c r="I1088" s="2"/>
+      <c r="N1088" s="1" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:14">
+      <c r="A1089" s="1">
+        <v>101085</v>
+      </c>
+      <c r="B1089" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1089" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1089" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1089" s="1">
+        <v>10120006</v>
+      </c>
+      <c r="F1089" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1089" s="2">
+        <v>4020405</v>
+      </c>
+      <c r="H1089" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I1089" s="2"/>
+      <c r="N1089" s="1" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:14">
+      <c r="A1090" s="1">
+        <v>101086</v>
+      </c>
+      <c r="B1090" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1090" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1090" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1090" s="1">
+        <v>10120006</v>
+      </c>
+      <c r="F1090" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1090" s="2">
+        <v>4020406</v>
+      </c>
+      <c r="H1090" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I1090" s="2"/>
+      <c r="N1090" s="1" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:14">
+      <c r="A1091" s="1">
+        <v>101087</v>
+      </c>
+      <c r="B1091" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1091" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1091" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1091" s="1">
+        <v>10120006</v>
+      </c>
+      <c r="F1091" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1091" s="2">
+        <v>4020407</v>
+      </c>
+      <c r="H1091" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I1091" s="2"/>
+      <c r="N1091" s="1" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:14">
+      <c r="A1092" s="1">
+        <v>101088</v>
+      </c>
+      <c r="B1092" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1092" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1092" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1092" s="1">
+        <v>10120006</v>
+      </c>
+      <c r="F1092" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1092" s="2">
+        <v>4020408</v>
+      </c>
+      <c r="H1092" s="2">
+        <v>7000</v>
+      </c>
+      <c r="I1092" s="2"/>
+      <c r="N1092" s="1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:14">
+      <c r="A1093" s="1">
+        <v>101089</v>
+      </c>
+      <c r="B1093" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1093" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1093" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1093" s="1">
+        <v>10120006</v>
+      </c>
+      <c r="F1093" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1093" s="2">
+        <v>4020409</v>
+      </c>
+      <c r="H1093" s="2">
+        <v>8000</v>
+      </c>
+      <c r="I1093" s="2"/>
+      <c r="N1093" s="1" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:14">
+      <c r="A1094" s="1">
+        <v>101090</v>
+      </c>
+      <c r="B1094" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1094" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1094" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1094" s="1">
+        <v>10120006</v>
+      </c>
+      <c r="F1094" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1094" s="2">
+        <v>4020410</v>
+      </c>
+      <c r="H1094" s="2">
+        <v>9000</v>
+      </c>
+      <c r="I1094" s="2"/>
+      <c r="N1094" s="1" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:14">
+      <c r="A1095" s="1">
+        <v>101091</v>
+      </c>
+      <c r="B1095" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1095" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1095" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1095" s="1">
+        <v>10120006</v>
+      </c>
+      <c r="F1095" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1095" s="2">
+        <v>4020411</v>
+      </c>
+      <c r="H1095" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I1095" s="2"/>
+      <c r="N1095" s="1" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:14">
+      <c r="A1096" s="1">
+        <v>101092</v>
+      </c>
+      <c r="B1096" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1096" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1096" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1096" s="1">
+        <v>10120007</v>
+      </c>
+      <c r="F1096" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1096" s="2"/>
+      <c r="H1096" s="2"/>
+      <c r="I1096" s="2"/>
+    </row>
+    <row r="1097" spans="1:14">
+      <c r="A1097" s="1">
+        <v>101093</v>
+      </c>
+      <c r="B1097" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1097" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1097" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1097" s="1">
+        <v>10120007</v>
+      </c>
+      <c r="F1097" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1097" s="2">
+        <v>4020077</v>
+      </c>
+      <c r="H1097" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I1097" s="2"/>
+      <c r="N1097" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:14">
+      <c r="A1098" s="1">
+        <v>101094</v>
+      </c>
+      <c r="B1098" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1098" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1098" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1098" s="1">
+        <v>10120007</v>
+      </c>
+      <c r="F1098" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1098" s="2">
+        <v>4020078</v>
+      </c>
+      <c r="H1098" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I1098" s="2"/>
+      <c r="N1098" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:14">
+      <c r="A1099" s="1">
+        <v>101095</v>
+      </c>
+      <c r="B1099" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1099" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1099" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1099" s="1">
+        <v>10120007</v>
+      </c>
+      <c r="F1099" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1099" s="2">
+        <v>4020079</v>
+      </c>
+      <c r="H1099" s="2">
+        <v>3000</v>
+      </c>
+      <c r="I1099" s="2"/>
+      <c r="N1099" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:14">
+      <c r="A1100" s="1">
+        <v>101096</v>
+      </c>
+      <c r="B1100" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1100" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1100" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1100" s="1">
+        <v>10120007</v>
+      </c>
+      <c r="F1100" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1100" s="2">
+        <v>4020080</v>
+      </c>
+      <c r="H1100" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I1100" s="2"/>
+      <c r="N1100" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:14">
+      <c r="A1101" s="1">
+        <v>101097</v>
+      </c>
+      <c r="B1101" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1101" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1101" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1101" s="1">
+        <v>10120007</v>
+      </c>
+      <c r="F1101" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1101" s="2">
+        <v>4020081</v>
+      </c>
+      <c r="H1101" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I1101" s="2"/>
+      <c r="N1101" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:14">
+      <c r="A1102" s="1">
+        <v>101098</v>
+      </c>
+      <c r="B1102" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1102" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1102" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1102" s="1">
+        <v>10120007</v>
+      </c>
+      <c r="F1102" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1102" s="2">
+        <v>4020082</v>
+      </c>
+      <c r="H1102" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I1102" s="2"/>
+      <c r="N1102" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:14">
+      <c r="A1103" s="1">
+        <v>101099</v>
+      </c>
+      <c r="B1103" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1103" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1103" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1103" s="1">
+        <v>10120007</v>
+      </c>
+      <c r="F1103" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1103" s="2">
+        <v>4020083</v>
+      </c>
+      <c r="H1103" s="2">
+        <v>7000</v>
+      </c>
+      <c r="I1103" s="2"/>
+      <c r="N1103" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:14">
+      <c r="A1104" s="1">
+        <v>101100</v>
+      </c>
+      <c r="B1104" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1104" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1104" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1104" s="1">
+        <v>10120007</v>
+      </c>
+      <c r="F1104" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1104" s="2">
+        <v>4020084</v>
+      </c>
+      <c r="H1104" s="2">
+        <v>8000</v>
+      </c>
+      <c r="I1104" s="2"/>
+      <c r="N1104" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:18">
+      <c r="A1105" s="1">
+        <v>101101</v>
+      </c>
+      <c r="B1105" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1105" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1105" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1105" s="1">
+        <v>10120007</v>
+      </c>
+      <c r="F1105" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1105" s="2">
+        <v>4020085</v>
+      </c>
+      <c r="H1105" s="2">
+        <v>9000</v>
+      </c>
+      <c r="I1105" s="2"/>
+      <c r="N1105" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:18">
+      <c r="A1106" s="1">
+        <v>101102</v>
+      </c>
+      <c r="B1106" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1106" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1106" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1106" s="1">
+        <v>10120007</v>
+      </c>
+      <c r="F1106" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1106" s="2">
+        <v>4020086</v>
+      </c>
+      <c r="H1106" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I1106" s="2"/>
+      <c r="N1106" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:18">
+      <c r="A1107" s="1">
+        <v>101103</v>
+      </c>
+      <c r="B1107" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1107" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1107" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1107" s="1">
+        <v>10120008</v>
+      </c>
+      <c r="F1107" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1107" s="2"/>
+      <c r="H1107" s="2"/>
+      <c r="I1107" s="2"/>
+    </row>
+    <row r="1108" spans="1:18">
+      <c r="A1108" s="1">
+        <v>101104</v>
+      </c>
+      <c r="B1108" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1108" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1108" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1108" s="1">
+        <v>10120008</v>
+      </c>
+      <c r="F1108" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1108" s="2">
+        <v>4020087</v>
+      </c>
+      <c r="H1108" s="2">
+        <v>100</v>
+      </c>
+      <c r="I1108" s="2"/>
+      <c r="Q1108" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:18">
+      <c r="A1109" s="1">
+        <v>101105</v>
+      </c>
+      <c r="B1109" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1109" s="2">
+        <v>0</v>
+      </c>
+      <c r="D1109" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1109" s="1">
+        <v>10120009</v>
+      </c>
+      <c r="F1109" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1109" s="2"/>
+      <c r="H1109" s="2"/>
+      <c r="I1109" s="2"/>
+    </row>
+    <row r="1110" spans="1:18">
+      <c r="A1110" s="1">
+        <v>101106</v>
+      </c>
+      <c r="B1110" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1110" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1110" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1110" s="1">
+        <v>10120009</v>
+      </c>
+      <c r="F1110" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1110" s="2">
+        <v>4020088</v>
+      </c>
+      <c r="H1110" s="2">
+        <v>100</v>
+      </c>
+      <c r="I1110" s="2"/>
+      <c r="R1110" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:18">
+      <c r="A1111" s="1">
+        <v>101107</v>
+      </c>
+      <c r="B1111" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1111" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1111" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1111" s="1">
+        <v>10120009</v>
+      </c>
+      <c r="F1111" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1111" s="2">
+        <v>4020089</v>
+      </c>
+      <c r="H1111" s="2">
+        <v>200</v>
+      </c>
+      <c r="I1111" s="2"/>
+      <c r="R1111" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:18">
+      <c r="A1112" s="1">
+        <v>101108</v>
+      </c>
+      <c r="B1112" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1112" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1112" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1112" s="1">
+        <v>10120009</v>
+      </c>
+      <c r="F1112" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1112" s="2">
+        <v>4020090</v>
+      </c>
+      <c r="H1112" s="2">
+        <v>300</v>
+      </c>
+      <c r="I1112" s="2"/>
+      <c r="R1112" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:18">
+      <c r="A1113" s="1">
+        <v>101109</v>
+      </c>
+      <c r="B1113" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1113" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1113" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1113" s="1">
+        <v>10120009</v>
+      </c>
+      <c r="F1113" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1113" s="2">
+        <v>4020091</v>
+      </c>
+      <c r="H1113" s="2">
+        <v>400</v>
+      </c>
+      <c r="I1113" s="2"/>
+      <c r="R1113" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:18">
+      <c r="A1114" s="1">
+        <v>101110</v>
+      </c>
+      <c r="B1114" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1114" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1114" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1114" s="1">
+        <v>10120009</v>
+      </c>
+      <c r="F1114" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1114" s="2">
+        <v>4020092</v>
+      </c>
+      <c r="H1114" s="2">
+        <v>500</v>
+      </c>
+      <c r="I1114" s="2"/>
+      <c r="R1114" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:18">
+      <c r="A1115" s="1">
+        <v>101111</v>
+      </c>
+      <c r="B1115" s="2">
+        <v>101200</v>
+      </c>
+      <c r="C1115" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1115" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E1115" s="1">
+        <v>10120009</v>
+      </c>
+      <c r="F1115" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1115" s="2">
+        <v>4020093</v>
+      </c>
+      <c r="H1115" s="2">
+        <v>600</v>
+      </c>
+      <c r="I1115" s="2"/>
+      <c r="R1115" s="1">
+        <v>99999</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A$1:A$1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/hall/resources/sample/ResearchSkills.xlsx
+++ b/hall/resources/sample/ResearchSkills.xlsx
@@ -2999,12 +2999,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -8111,7 +8111,9 @@
       <c r="F137" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G137" s="2"/>
+      <c r="G137" s="2">
+        <v>4020449</v>
+      </c>
       <c r="H137" s="2">
         <v>100</v>
       </c>
@@ -8141,7 +8143,9 @@
       <c r="F138" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G138" s="2"/>
+      <c r="G138" s="2">
+        <v>4020450</v>
+      </c>
       <c r="H138" s="2">
         <v>200</v>
       </c>
@@ -8171,7 +8175,9 @@
       <c r="F139" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G139" s="2"/>
+      <c r="G139" s="2">
+        <v>4020451</v>
+      </c>
       <c r="H139" s="2">
         <v>300</v>
       </c>
@@ -8201,7 +8207,9 @@
       <c r="F140" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G140" s="2"/>
+      <c r="G140" s="2">
+        <v>4020452</v>
+      </c>
       <c r="H140" s="2">
         <v>400</v>
       </c>
@@ -8231,7 +8239,9 @@
       <c r="F141" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G141" s="2"/>
+      <c r="G141" s="2">
+        <v>4020453</v>
+      </c>
       <c r="H141" s="2">
         <v>500</v>
       </c>
@@ -8261,7 +8271,9 @@
       <c r="F142" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G142" s="2"/>
+      <c r="G142" s="2">
+        <v>4020454</v>
+      </c>
       <c r="H142" s="2">
         <v>600</v>
       </c>
@@ -8291,7 +8303,9 @@
       <c r="F143" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G143" s="2"/>
+      <c r="G143" s="2">
+        <v>4020455</v>
+      </c>
       <c r="H143" s="2">
         <v>700</v>
       </c>
@@ -34690,7 +34704,9 @@
       <c r="F975" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G975" s="2"/>
+      <c r="G975" s="2">
+        <v>4020456</v>
+      </c>
       <c r="H975" s="2">
         <v>100</v>
       </c>
@@ -34720,7 +34736,9 @@
       <c r="F976" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G976" s="2"/>
+      <c r="G976" s="2">
+        <v>4020457</v>
+      </c>
       <c r="H976" s="2">
         <v>200</v>
       </c>
@@ -34750,7 +34768,9 @@
       <c r="F977" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G977" s="2"/>
+      <c r="G977" s="2">
+        <v>4020458</v>
+      </c>
       <c r="H977" s="2">
         <v>300</v>
       </c>
@@ -34780,7 +34800,9 @@
       <c r="F978" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G978" s="2"/>
+      <c r="G978" s="2">
+        <v>4020459</v>
+      </c>
       <c r="H978" s="2">
         <v>400</v>
       </c>
@@ -34810,7 +34832,9 @@
       <c r="F979" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G979" s="2"/>
+      <c r="G979" s="2">
+        <v>4020460</v>
+      </c>
       <c r="H979" s="2">
         <v>500</v>
       </c>
@@ -34840,7 +34864,9 @@
       <c r="F980" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G980" s="2"/>
+      <c r="G980" s="2">
+        <v>4020461</v>
+      </c>
       <c r="H980" s="2">
         <v>600</v>
       </c>
@@ -34870,7 +34896,9 @@
       <c r="F981" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G981" s="2"/>
+      <c r="G981" s="2">
+        <v>4020462</v>
+      </c>
       <c r="H981" s="2">
         <v>700</v>
       </c>
@@ -34900,7 +34928,9 @@
       <c r="F982" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G982" s="2"/>
+      <c r="G982" s="2">
+        <v>4020463</v>
+      </c>
       <c r="H982" s="2">
         <v>800</v>
       </c>
@@ -34930,7 +34960,9 @@
       <c r="F983" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G983" s="2"/>
+      <c r="G983" s="2">
+        <v>4020464</v>
+      </c>
       <c r="H983" s="2">
         <v>900</v>
       </c>
@@ -34960,7 +34992,9 @@
       <c r="F984" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G984" s="2"/>
+      <c r="G984" s="2">
+        <v>4020465</v>
+      </c>
       <c r="H984" s="2">
         <v>1000</v>
       </c>

--- a/hall/resources/sample/ResearchSkills.xlsx
+++ b/hall/resources/sample/ResearchSkills.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\模拟经营数值相关\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17330,9 +17330,6 @@
       <c r="A89" s="2">
         <v>100300085</v>
       </c>
-      <c r="B89" s="3">
-        <v>100300</v>
-      </c>
       <c r="C89" s="3">
         <v>0</v>
       </c>
@@ -17352,9 +17349,6 @@
     <row r="90" spans="1:20">
       <c r="A90" s="2">
         <v>100300086</v>
-      </c>
-      <c r="B90" s="3">
-        <v>100300</v>
       </c>
       <c r="C90" s="3">
         <v>1</v>
@@ -17382,9 +17376,6 @@
       <c r="A91" s="2">
         <v>100300087</v>
       </c>
-      <c r="B91" s="3">
-        <v>100300</v>
-      </c>
       <c r="C91" s="3">
         <v>2</v>
       </c>
@@ -17411,9 +17402,6 @@
       <c r="A92" s="2">
         <v>100300088</v>
       </c>
-      <c r="B92" s="3">
-        <v>100300</v>
-      </c>
       <c r="C92" s="3">
         <v>3</v>
       </c>
@@ -17440,9 +17428,6 @@
       <c r="A93" s="2">
         <v>100300089</v>
       </c>
-      <c r="B93" s="3">
-        <v>100300</v>
-      </c>
       <c r="C93" s="3">
         <v>4</v>
       </c>
@@ -17469,9 +17454,6 @@
       <c r="A94" s="2">
         <v>100300090</v>
       </c>
-      <c r="B94" s="3">
-        <v>100300</v>
-      </c>
       <c r="C94" s="3">
         <v>5</v>
       </c>
@@ -17498,9 +17480,6 @@
       <c r="A95" s="2">
         <v>100300091</v>
       </c>
-      <c r="B95" s="3">
-        <v>100300</v>
-      </c>
       <c r="C95" s="3">
         <v>6</v>
       </c>
@@ -17527,9 +17506,6 @@
       <c r="A96" s="2">
         <v>100300092</v>
       </c>
-      <c r="B96" s="3">
-        <v>100300</v>
-      </c>
       <c r="C96" s="3">
         <v>7</v>
       </c>
@@ -17556,9 +17532,6 @@
       <c r="A97" s="2">
         <v>100300093</v>
       </c>
-      <c r="B97" s="3">
-        <v>100300</v>
-      </c>
       <c r="C97" s="3">
         <v>8</v>
       </c>
@@ -17585,9 +17558,6 @@
       <c r="A98" s="2">
         <v>100300094</v>
       </c>
-      <c r="B98" s="3">
-        <v>100300</v>
-      </c>
       <c r="C98" s="3">
         <v>9</v>
       </c>
@@ -17614,9 +17584,6 @@
       <c r="A99" s="2">
         <v>100300095</v>
       </c>
-      <c r="B99" s="3">
-        <v>100300</v>
-      </c>
       <c r="C99" s="3">
         <v>10</v>
       </c>
@@ -17643,9 +17610,6 @@
       <c r="A100" s="2">
         <v>100300096</v>
       </c>
-      <c r="B100" s="3">
-        <v>100300</v>
-      </c>
       <c r="C100" s="3">
         <v>11</v>
       </c>
@@ -17672,9 +17636,6 @@
       <c r="A101" s="2">
         <v>100300097</v>
       </c>
-      <c r="B101" s="3">
-        <v>100300</v>
-      </c>
       <c r="C101" s="3">
         <v>12</v>
       </c>
@@ -17701,9 +17662,6 @@
       <c r="A102" s="2">
         <v>100300098</v>
       </c>
-      <c r="B102" s="3">
-        <v>100300</v>
-      </c>
       <c r="C102" s="3">
         <v>13</v>
       </c>
@@ -17730,9 +17688,6 @@
       <c r="A103" s="2">
         <v>100300099</v>
       </c>
-      <c r="B103" s="3">
-        <v>100300</v>
-      </c>
       <c r="C103" s="3">
         <v>14</v>
       </c>
@@ -17759,9 +17714,6 @@
       <c r="A104" s="2">
         <v>100300100</v>
       </c>
-      <c r="B104" s="3">
-        <v>100300</v>
-      </c>
       <c r="C104" s="3">
         <v>15</v>
       </c>
@@ -17788,9 +17740,6 @@
       <c r="A105" s="2">
         <v>100300101</v>
       </c>
-      <c r="B105" s="3">
-        <v>100300</v>
-      </c>
       <c r="C105" s="3">
         <v>16</v>
       </c>
@@ -17817,9 +17766,6 @@
       <c r="A106" s="2">
         <v>100300102</v>
       </c>
-      <c r="B106" s="3">
-        <v>100300</v>
-      </c>
       <c r="C106" s="3">
         <v>17</v>
       </c>
@@ -17846,9 +17792,6 @@
       <c r="A107" s="2">
         <v>100300103</v>
       </c>
-      <c r="B107" s="3">
-        <v>100300</v>
-      </c>
       <c r="C107" s="3">
         <v>18</v>
       </c>
@@ -17875,9 +17818,6 @@
       <c r="A108" s="2">
         <v>100300104</v>
       </c>
-      <c r="B108" s="3">
-        <v>100300</v>
-      </c>
       <c r="C108" s="3">
         <v>19</v>
       </c>
@@ -17904,9 +17844,6 @@
       <c r="A109" s="2">
         <v>100300105</v>
       </c>
-      <c r="B109" s="3">
-        <v>100300</v>
-      </c>
       <c r="C109" s="3">
         <v>20</v>
       </c>
@@ -17933,9 +17870,6 @@
       <c r="A110" s="2">
         <v>100300106</v>
       </c>
-      <c r="B110" s="3">
-        <v>100300</v>
-      </c>
       <c r="C110" s="3">
         <v>21</v>
       </c>
@@ -17962,9 +17896,6 @@
       <c r="A111" s="2">
         <v>100300107</v>
       </c>
-      <c r="B111" s="3">
-        <v>100300</v>
-      </c>
       <c r="C111" s="3">
         <v>0</v>
       </c>
@@ -17985,9 +17916,6 @@
     <row r="112" spans="1:21">
       <c r="A112" s="2">
         <v>100300108</v>
-      </c>
-      <c r="B112" s="3">
-        <v>100300</v>
       </c>
       <c r="C112" s="3">
         <v>1</v>
@@ -18015,9 +17943,6 @@
       <c r="A113" s="2">
         <v>100300109</v>
       </c>
-      <c r="B113" s="3">
-        <v>100300</v>
-      </c>
       <c r="C113" s="3">
         <v>2</v>
       </c>
@@ -18044,9 +17969,6 @@
       <c r="A114" s="2">
         <v>100300110</v>
       </c>
-      <c r="B114" s="3">
-        <v>100300</v>
-      </c>
       <c r="C114" s="3">
         <v>3</v>
       </c>
@@ -18073,9 +17995,6 @@
       <c r="A115" s="2">
         <v>100300111</v>
       </c>
-      <c r="B115" s="3">
-        <v>100300</v>
-      </c>
       <c r="C115" s="3">
         <v>4</v>
       </c>
@@ -18102,9 +18021,6 @@
       <c r="A116" s="2">
         <v>100300112</v>
       </c>
-      <c r="B116" s="3">
-        <v>100300</v>
-      </c>
       <c r="C116" s="3">
         <v>5</v>
       </c>
@@ -18131,9 +18047,6 @@
       <c r="A117" s="2">
         <v>100300113</v>
       </c>
-      <c r="B117" s="3">
-        <v>100300</v>
-      </c>
       <c r="C117" s="3">
         <v>6</v>
       </c>
@@ -18160,9 +18073,6 @@
       <c r="A118" s="2">
         <v>100300114</v>
       </c>
-      <c r="B118" s="3">
-        <v>100300</v>
-      </c>
       <c r="C118" s="3">
         <v>7</v>
       </c>
@@ -18189,9 +18099,6 @@
       <c r="A119" s="2">
         <v>100300115</v>
       </c>
-      <c r="B119" s="3">
-        <v>100300</v>
-      </c>
       <c r="C119" s="3">
         <v>8</v>
       </c>
@@ -18218,9 +18125,6 @@
       <c r="A120" s="2">
         <v>100300116</v>
       </c>
-      <c r="B120" s="3">
-        <v>100300</v>
-      </c>
       <c r="C120" s="3">
         <v>9</v>
       </c>
@@ -18247,9 +18151,6 @@
       <c r="A121" s="2">
         <v>100300117</v>
       </c>
-      <c r="B121" s="3">
-        <v>100300</v>
-      </c>
       <c r="C121" s="3">
         <v>10</v>
       </c>
@@ -21377,7 +21278,7 @@
         <v>211</v>
       </c>
       <c r="E216" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>38</v>
@@ -21400,7 +21301,7 @@
         <v>211</v>
       </c>
       <c r="E217" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>39</v>
@@ -21429,7 +21330,7 @@
         <v>211</v>
       </c>
       <c r="E218" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>41</v>
@@ -21458,7 +21359,7 @@
         <v>211</v>
       </c>
       <c r="E219" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>44</v>
@@ -21487,7 +21388,7 @@
         <v>211</v>
       </c>
       <c r="E220" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>47</v>
@@ -21516,7 +21417,7 @@
         <v>211</v>
       </c>
       <c r="E221" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>50</v>
@@ -21545,7 +21446,7 @@
         <v>211</v>
       </c>
       <c r="E222" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>53</v>
@@ -21574,7 +21475,7 @@
         <v>211</v>
       </c>
       <c r="E223" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>68</v>
@@ -21603,7 +21504,7 @@
         <v>211</v>
       </c>
       <c r="E224" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>71</v>
@@ -21632,7 +21533,7 @@
         <v>211</v>
       </c>
       <c r="E225" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>74</v>
@@ -21661,7 +21562,7 @@
         <v>211</v>
       </c>
       <c r="E226" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>77</v>
@@ -21690,7 +21591,7 @@
         <v>211</v>
       </c>
       <c r="E227" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>200</v>
@@ -21719,7 +21620,7 @@
         <v>211</v>
       </c>
       <c r="E228" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>201</v>
@@ -21748,7 +21649,7 @@
         <v>211</v>
       </c>
       <c r="E229" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>202</v>
@@ -21777,7 +21678,7 @@
         <v>211</v>
       </c>
       <c r="E230" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>203</v>
@@ -21806,7 +21707,7 @@
         <v>211</v>
       </c>
       <c r="E231" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>204</v>
@@ -21835,7 +21736,7 @@
         <v>211</v>
       </c>
       <c r="E232" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>205</v>
@@ -21864,7 +21765,7 @@
         <v>211</v>
       </c>
       <c r="E233" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>206</v>
@@ -21893,7 +21794,7 @@
         <v>211</v>
       </c>
       <c r="E234" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>207</v>
@@ -21922,7 +21823,7 @@
         <v>211</v>
       </c>
       <c r="E235" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>208</v>
@@ -21951,7 +21852,7 @@
         <v>211</v>
       </c>
       <c r="E236" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>209</v>
@@ -21980,7 +21881,7 @@
         <v>211</v>
       </c>
       <c r="E237" s="2">
-        <v>10070010</v>
+        <v>10030009</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>210</v>
@@ -22009,7 +21910,7 @@
         <v>211</v>
       </c>
       <c r="E238" s="2">
-        <v>10070011</v>
+        <v>10030010</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>38</v>
@@ -22033,7 +21934,7 @@
         <v>211</v>
       </c>
       <c r="E239" s="2">
-        <v>10070011</v>
+        <v>10030010</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>39</v>
@@ -22062,7 +21963,7 @@
         <v>211</v>
       </c>
       <c r="E240" s="2">
-        <v>10070011</v>
+        <v>10030010</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>41</v>
@@ -22091,7 +21992,7 @@
         <v>211</v>
       </c>
       <c r="E241" s="2">
-        <v>10070011</v>
+        <v>10030010</v>
       </c>
       <c r="F241" s="3" t="s">
         <v>44</v>
@@ -22120,7 +22021,7 @@
         <v>211</v>
       </c>
       <c r="E242" s="2">
-        <v>10070011</v>
+        <v>10030010</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>47</v>
@@ -22149,7 +22050,7 @@
         <v>211</v>
       </c>
       <c r="E243" s="2">
-        <v>10070011</v>
+        <v>10030010</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>50</v>
@@ -22178,7 +22079,7 @@
         <v>211</v>
       </c>
       <c r="E244" s="2">
-        <v>10070011</v>
+        <v>10030010</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>53</v>
@@ -22207,7 +22108,7 @@
         <v>211</v>
       </c>
       <c r="E245" s="2">
-        <v>10070011</v>
+        <v>10030010</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>68</v>
@@ -22236,7 +22137,7 @@
         <v>211</v>
       </c>
       <c r="E246" s="2">
-        <v>10070011</v>
+        <v>10030010</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>71</v>
@@ -22265,7 +22166,7 @@
         <v>211</v>
       </c>
       <c r="E247" s="2">
-        <v>10070011</v>
+        <v>10030010</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>74</v>
@@ -22294,7 +22195,7 @@
         <v>211</v>
       </c>
       <c r="E248" s="2">
-        <v>10070011</v>
+        <v>10030010</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>77</v>
@@ -24707,9 +24608,6 @@
       <c r="A322" s="2">
         <v>101200074</v>
       </c>
-      <c r="B322" s="3">
-        <v>101200</v>
-      </c>
       <c r="C322" s="3">
         <v>0</v>
       </c>
@@ -24717,7 +24615,7 @@
         <v>350</v>
       </c>
       <c r="E322" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F322" s="3" t="s">
         <v>38</v>
@@ -24730,9 +24628,6 @@
       <c r="A323" s="2">
         <v>101200075</v>
       </c>
-      <c r="B323" s="3">
-        <v>101200</v>
-      </c>
       <c r="C323" s="3">
         <v>1</v>
       </c>
@@ -24740,7 +24635,7 @@
         <v>350</v>
       </c>
       <c r="E323" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F323" s="3" t="s">
         <v>39</v>
@@ -24759,9 +24654,6 @@
       <c r="A324" s="2">
         <v>101200076</v>
       </c>
-      <c r="B324" s="3">
-        <v>101200</v>
-      </c>
       <c r="C324" s="3">
         <v>2</v>
       </c>
@@ -24769,7 +24661,7 @@
         <v>350</v>
       </c>
       <c r="E324" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F324" s="3" t="s">
         <v>41</v>
@@ -24788,9 +24680,6 @@
       <c r="A325" s="2">
         <v>101200077</v>
       </c>
-      <c r="B325" s="3">
-        <v>101200</v>
-      </c>
       <c r="C325" s="3">
         <v>3</v>
       </c>
@@ -24798,7 +24687,7 @@
         <v>350</v>
       </c>
       <c r="E325" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F325" s="3" t="s">
         <v>44</v>
@@ -24817,9 +24706,6 @@
       <c r="A326" s="2">
         <v>101200078</v>
       </c>
-      <c r="B326" s="3">
-        <v>101200</v>
-      </c>
       <c r="C326" s="3">
         <v>4</v>
       </c>
@@ -24827,7 +24713,7 @@
         <v>350</v>
       </c>
       <c r="E326" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>47</v>
@@ -24846,9 +24732,6 @@
       <c r="A327" s="2">
         <v>101200079</v>
       </c>
-      <c r="B327" s="3">
-        <v>101200</v>
-      </c>
       <c r="C327" s="3">
         <v>5</v>
       </c>
@@ -24856,7 +24739,7 @@
         <v>350</v>
       </c>
       <c r="E327" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F327" s="3" t="s">
         <v>50</v>
@@ -24875,9 +24758,6 @@
       <c r="A328" s="2">
         <v>101200080</v>
       </c>
-      <c r="B328" s="3">
-        <v>101200</v>
-      </c>
       <c r="C328" s="3">
         <v>6</v>
       </c>
@@ -24885,7 +24765,7 @@
         <v>350</v>
       </c>
       <c r="E328" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F328" s="3" t="s">
         <v>53</v>
@@ -24904,9 +24784,6 @@
       <c r="A329" s="2">
         <v>101200081</v>
       </c>
-      <c r="B329" s="3">
-        <v>101200</v>
-      </c>
       <c r="C329" s="3">
         <v>7</v>
       </c>
@@ -24914,7 +24791,7 @@
         <v>350</v>
       </c>
       <c r="E329" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F329" s="3" t="s">
         <v>68</v>
@@ -24933,9 +24810,6 @@
       <c r="A330" s="2">
         <v>101200082</v>
       </c>
-      <c r="B330" s="3">
-        <v>101200</v>
-      </c>
       <c r="C330" s="3">
         <v>8</v>
       </c>
@@ -24943,7 +24817,7 @@
         <v>350</v>
       </c>
       <c r="E330" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F330" s="3" t="s">
         <v>71</v>
@@ -24962,9 +24836,6 @@
       <c r="A331" s="2">
         <v>101200083</v>
       </c>
-      <c r="B331" s="3">
-        <v>101200</v>
-      </c>
       <c r="C331" s="3">
         <v>9</v>
       </c>
@@ -24972,7 +24843,7 @@
         <v>350</v>
       </c>
       <c r="E331" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F331" s="3" t="s">
         <v>74</v>
@@ -24991,9 +24862,6 @@
       <c r="A332" s="2">
         <v>101200084</v>
       </c>
-      <c r="B332" s="3">
-        <v>101200</v>
-      </c>
       <c r="C332" s="3">
         <v>10</v>
       </c>
@@ -25001,7 +24869,7 @@
         <v>350</v>
       </c>
       <c r="E332" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F332" s="3" t="s">
         <v>77</v>
@@ -25020,9 +24888,6 @@
       <c r="A333" s="2">
         <v>101200085</v>
       </c>
-      <c r="B333" s="3">
-        <v>101200</v>
-      </c>
       <c r="C333" s="3">
         <v>11</v>
       </c>
@@ -25030,7 +24895,7 @@
         <v>350</v>
       </c>
       <c r="E333" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F333" s="3" t="s">
         <v>200</v>
@@ -25049,9 +24914,6 @@
       <c r="A334" s="2">
         <v>101200086</v>
       </c>
-      <c r="B334" s="3">
-        <v>101200</v>
-      </c>
       <c r="C334" s="3">
         <v>12</v>
       </c>
@@ -25059,7 +24921,7 @@
         <v>350</v>
       </c>
       <c r="E334" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F334" s="3" t="s">
         <v>201</v>
@@ -25078,9 +24940,6 @@
       <c r="A335" s="2">
         <v>101200087</v>
       </c>
-      <c r="B335" s="3">
-        <v>101200</v>
-      </c>
       <c r="C335" s="3">
         <v>13</v>
       </c>
@@ -25088,7 +24947,7 @@
         <v>350</v>
       </c>
       <c r="E335" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F335" s="3" t="s">
         <v>202</v>
@@ -25107,9 +24966,6 @@
       <c r="A336" s="2">
         <v>101200088</v>
       </c>
-      <c r="B336" s="3">
-        <v>101200</v>
-      </c>
       <c r="C336" s="3">
         <v>14</v>
       </c>
@@ -25117,7 +24973,7 @@
         <v>350</v>
       </c>
       <c r="E336" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F336" s="3" t="s">
         <v>203</v>
@@ -25136,9 +24992,6 @@
       <c r="A337" s="2">
         <v>101200089</v>
       </c>
-      <c r="B337" s="3">
-        <v>101200</v>
-      </c>
       <c r="C337" s="3">
         <v>15</v>
       </c>
@@ -25146,7 +24999,7 @@
         <v>350</v>
       </c>
       <c r="E337" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F337" s="3" t="s">
         <v>204</v>
@@ -25165,9 +25018,6 @@
       <c r="A338" s="2">
         <v>101200090</v>
       </c>
-      <c r="B338" s="3">
-        <v>101200</v>
-      </c>
       <c r="C338" s="3">
         <v>16</v>
       </c>
@@ -25175,7 +25025,7 @@
         <v>350</v>
       </c>
       <c r="E338" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F338" s="3" t="s">
         <v>205</v>
@@ -25194,9 +25044,6 @@
       <c r="A339" s="2">
         <v>101200091</v>
       </c>
-      <c r="B339" s="3">
-        <v>101200</v>
-      </c>
       <c r="C339" s="3">
         <v>17</v>
       </c>
@@ -25204,7 +25051,7 @@
         <v>350</v>
       </c>
       <c r="E339" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F339" s="3" t="s">
         <v>206</v>
@@ -25223,9 +25070,6 @@
       <c r="A340" s="2">
         <v>101200092</v>
       </c>
-      <c r="B340" s="3">
-        <v>101200</v>
-      </c>
       <c r="C340" s="3">
         <v>18</v>
       </c>
@@ -25233,7 +25077,7 @@
         <v>350</v>
       </c>
       <c r="E340" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F340" s="3" t="s">
         <v>207</v>
@@ -25252,9 +25096,6 @@
       <c r="A341" s="2">
         <v>101200093</v>
       </c>
-      <c r="B341" s="3">
-        <v>101200</v>
-      </c>
       <c r="C341" s="3">
         <v>19</v>
       </c>
@@ -25262,7 +25103,7 @@
         <v>350</v>
       </c>
       <c r="E341" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F341" s="3" t="s">
         <v>208</v>
@@ -25281,9 +25122,6 @@
       <c r="A342" s="2">
         <v>101200094</v>
       </c>
-      <c r="B342" s="3">
-        <v>101200</v>
-      </c>
       <c r="C342" s="3">
         <v>20</v>
       </c>
@@ -25291,7 +25129,7 @@
         <v>350</v>
       </c>
       <c r="E342" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F342" s="3" t="s">
         <v>209</v>
@@ -25310,9 +25148,6 @@
       <c r="A343" s="2">
         <v>101200095</v>
       </c>
-      <c r="B343" s="3">
-        <v>101200</v>
-      </c>
       <c r="C343" s="3">
         <v>21</v>
       </c>
@@ -25320,7 +25155,7 @@
         <v>350</v>
       </c>
       <c r="E343" s="2">
-        <v>10120008</v>
+        <v>10030009</v>
       </c>
       <c r="F343" s="3" t="s">
         <v>210</v>
@@ -25339,9 +25174,6 @@
       <c r="A344" s="2">
         <v>101200096</v>
       </c>
-      <c r="B344" s="3">
-        <v>101200</v>
-      </c>
       <c r="C344" s="3">
         <v>0</v>
       </c>
@@ -25349,7 +25181,7 @@
         <v>350</v>
       </c>
       <c r="E344" s="2">
-        <v>10120009</v>
+        <v>10030010</v>
       </c>
       <c r="F344" s="3" t="s">
         <v>38</v>
@@ -25363,9 +25195,6 @@
       <c r="A345" s="2">
         <v>101200097</v>
       </c>
-      <c r="B345" s="3">
-        <v>101200</v>
-      </c>
       <c r="C345" s="3">
         <v>1</v>
       </c>
@@ -25373,7 +25202,7 @@
         <v>350</v>
       </c>
       <c r="E345" s="2">
-        <v>10120009</v>
+        <v>10030010</v>
       </c>
       <c r="F345" s="3" t="s">
         <v>39</v>
@@ -25392,9 +25221,6 @@
       <c r="A346" s="2">
         <v>101200098</v>
       </c>
-      <c r="B346" s="3">
-        <v>101200</v>
-      </c>
       <c r="C346" s="3">
         <v>2</v>
       </c>
@@ -25402,7 +25228,7 @@
         <v>350</v>
       </c>
       <c r="E346" s="2">
-        <v>10120009</v>
+        <v>10030010</v>
       </c>
       <c r="F346" s="3" t="s">
         <v>41</v>
@@ -25421,9 +25247,6 @@
       <c r="A347" s="2">
         <v>101200099</v>
       </c>
-      <c r="B347" s="3">
-        <v>101200</v>
-      </c>
       <c r="C347" s="3">
         <v>3</v>
       </c>
@@ -25431,7 +25254,7 @@
         <v>350</v>
       </c>
       <c r="E347" s="2">
-        <v>10120009</v>
+        <v>10030010</v>
       </c>
       <c r="F347" s="3" t="s">
         <v>44</v>
@@ -25450,9 +25273,6 @@
       <c r="A348" s="2">
         <v>101200100</v>
       </c>
-      <c r="B348" s="3">
-        <v>101200</v>
-      </c>
       <c r="C348" s="3">
         <v>4</v>
       </c>
@@ -25460,7 +25280,7 @@
         <v>350</v>
       </c>
       <c r="E348" s="2">
-        <v>10120009</v>
+        <v>10030010</v>
       </c>
       <c r="F348" s="3" t="s">
         <v>47</v>
@@ -25479,9 +25299,6 @@
       <c r="A349" s="2">
         <v>101200101</v>
       </c>
-      <c r="B349" s="3">
-        <v>101200</v>
-      </c>
       <c r="C349" s="3">
         <v>5</v>
       </c>
@@ -25489,7 +25306,7 @@
         <v>350</v>
       </c>
       <c r="E349" s="2">
-        <v>10120009</v>
+        <v>10030010</v>
       </c>
       <c r="F349" s="3" t="s">
         <v>50</v>
@@ -25508,9 +25325,6 @@
       <c r="A350" s="2">
         <v>101200102</v>
       </c>
-      <c r="B350" s="3">
-        <v>101200</v>
-      </c>
       <c r="C350" s="3">
         <v>6</v>
       </c>
@@ -25518,7 +25332,7 @@
         <v>350</v>
       </c>
       <c r="E350" s="2">
-        <v>10120009</v>
+        <v>10030010</v>
       </c>
       <c r="F350" s="3" t="s">
         <v>53</v>
@@ -25537,9 +25351,6 @@
       <c r="A351" s="2">
         <v>101200103</v>
       </c>
-      <c r="B351" s="3">
-        <v>101200</v>
-      </c>
       <c r="C351" s="3">
         <v>7</v>
       </c>
@@ -25547,7 +25358,7 @@
         <v>350</v>
       </c>
       <c r="E351" s="2">
-        <v>10120009</v>
+        <v>10030010</v>
       </c>
       <c r="F351" s="3" t="s">
         <v>68</v>
@@ -25566,9 +25377,6 @@
       <c r="A352" s="2">
         <v>101200104</v>
       </c>
-      <c r="B352" s="3">
-        <v>101200</v>
-      </c>
       <c r="C352" s="3">
         <v>8</v>
       </c>
@@ -25576,7 +25384,7 @@
         <v>350</v>
       </c>
       <c r="E352" s="2">
-        <v>10120009</v>
+        <v>10030010</v>
       </c>
       <c r="F352" s="3" t="s">
         <v>71</v>
@@ -25595,9 +25403,6 @@
       <c r="A353" s="2">
         <v>101200105</v>
       </c>
-      <c r="B353" s="3">
-        <v>101200</v>
-      </c>
       <c r="C353" s="3">
         <v>9</v>
       </c>
@@ -25605,7 +25410,7 @@
         <v>350</v>
       </c>
       <c r="E353" s="2">
-        <v>10120009</v>
+        <v>10030010</v>
       </c>
       <c r="F353" s="3" t="s">
         <v>74</v>
@@ -25624,9 +25429,6 @@
       <c r="A354" s="2">
         <v>101200106</v>
       </c>
-      <c r="B354" s="3">
-        <v>101200</v>
-      </c>
       <c r="C354" s="3">
         <v>10</v>
       </c>
@@ -25634,7 +25436,7 @@
         <v>350</v>
       </c>
       <c r="E354" s="2">
-        <v>10120009</v>
+        <v>10030010</v>
       </c>
       <c r="F354" s="3" t="s">
         <v>77</v>
@@ -29139,9 +28941,6 @@
       <c r="A461" s="2">
         <v>101800107</v>
       </c>
-      <c r="B461" s="3">
-        <v>101800</v>
-      </c>
       <c r="C461" s="3">
         <v>0</v>
       </c>
@@ -29149,7 +28948,7 @@
         <v>439</v>
       </c>
       <c r="E461" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F461" s="3" t="s">
         <v>38</v>
@@ -29163,9 +28962,6 @@
       <c r="A462" s="2">
         <v>101800108</v>
       </c>
-      <c r="B462" s="3">
-        <v>101800</v>
-      </c>
       <c r="C462" s="3">
         <v>1</v>
       </c>
@@ -29173,7 +28969,7 @@
         <v>439</v>
       </c>
       <c r="E462" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F462" s="3" t="s">
         <v>39</v>
@@ -29192,9 +28988,6 @@
       <c r="A463" s="2">
         <v>101800109</v>
       </c>
-      <c r="B463" s="3">
-        <v>101800</v>
-      </c>
       <c r="C463" s="3">
         <v>2</v>
       </c>
@@ -29202,7 +28995,7 @@
         <v>439</v>
       </c>
       <c r="E463" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F463" s="3" t="s">
         <v>41</v>
@@ -29221,9 +29014,6 @@
       <c r="A464" s="2">
         <v>101800110</v>
       </c>
-      <c r="B464" s="3">
-        <v>101800</v>
-      </c>
       <c r="C464" s="3">
         <v>3</v>
       </c>
@@ -29231,7 +29021,7 @@
         <v>439</v>
       </c>
       <c r="E464" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F464" s="3" t="s">
         <v>44</v>
@@ -29250,9 +29040,6 @@
       <c r="A465" s="2">
         <v>101800111</v>
       </c>
-      <c r="B465" s="3">
-        <v>101800</v>
-      </c>
       <c r="C465" s="3">
         <v>4</v>
       </c>
@@ -29260,7 +29047,7 @@
         <v>439</v>
       </c>
       <c r="E465" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F465" s="3" t="s">
         <v>47</v>
@@ -29279,9 +29066,6 @@
       <c r="A466" s="2">
         <v>101800112</v>
       </c>
-      <c r="B466" s="3">
-        <v>101800</v>
-      </c>
       <c r="C466" s="3">
         <v>5</v>
       </c>
@@ -29289,7 +29073,7 @@
         <v>439</v>
       </c>
       <c r="E466" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F466" s="3" t="s">
         <v>50</v>
@@ -29308,9 +29092,6 @@
       <c r="A467" s="2">
         <v>101800113</v>
       </c>
-      <c r="B467" s="3">
-        <v>101800</v>
-      </c>
       <c r="C467" s="3">
         <v>6</v>
       </c>
@@ -29318,7 +29099,7 @@
         <v>439</v>
       </c>
       <c r="E467" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F467" s="3" t="s">
         <v>53</v>
@@ -29337,9 +29118,6 @@
       <c r="A468" s="2">
         <v>101800114</v>
       </c>
-      <c r="B468" s="3">
-        <v>101800</v>
-      </c>
       <c r="C468" s="3">
         <v>7</v>
       </c>
@@ -29347,7 +29125,7 @@
         <v>439</v>
       </c>
       <c r="E468" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F468" s="3" t="s">
         <v>68</v>
@@ -29366,9 +29144,6 @@
       <c r="A469" s="2">
         <v>101800115</v>
       </c>
-      <c r="B469" s="3">
-        <v>101800</v>
-      </c>
       <c r="C469" s="3">
         <v>8</v>
       </c>
@@ -29376,7 +29151,7 @@
         <v>439</v>
       </c>
       <c r="E469" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F469" s="3" t="s">
         <v>71</v>
@@ -29395,9 +29170,6 @@
       <c r="A470" s="2">
         <v>101800116</v>
       </c>
-      <c r="B470" s="3">
-        <v>101800</v>
-      </c>
       <c r="C470" s="3">
         <v>9</v>
       </c>
@@ -29405,7 +29177,7 @@
         <v>439</v>
       </c>
       <c r="E470" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F470" s="3" t="s">
         <v>74</v>
@@ -29424,9 +29196,6 @@
       <c r="A471" s="2">
         <v>101800117</v>
       </c>
-      <c r="B471" s="3">
-        <v>101800</v>
-      </c>
       <c r="C471" s="3">
         <v>10</v>
       </c>
@@ -29434,7 +29203,7 @@
         <v>439</v>
       </c>
       <c r="E471" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F471" s="3" t="s">
         <v>77</v>
@@ -29453,9 +29222,6 @@
       <c r="A472" s="2">
         <v>101800118</v>
       </c>
-      <c r="B472" s="3">
-        <v>101800</v>
-      </c>
       <c r="C472" s="3">
         <v>11</v>
       </c>
@@ -29463,7 +29229,7 @@
         <v>439</v>
       </c>
       <c r="E472" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F472" s="3" t="s">
         <v>200</v>
@@ -29482,9 +29248,6 @@
       <c r="A473" s="2">
         <v>101800119</v>
       </c>
-      <c r="B473" s="3">
-        <v>101800</v>
-      </c>
       <c r="C473" s="3">
         <v>12</v>
       </c>
@@ -29492,7 +29255,7 @@
         <v>439</v>
       </c>
       <c r="E473" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F473" s="3" t="s">
         <v>201</v>
@@ -29511,9 +29274,6 @@
       <c r="A474" s="2">
         <v>101800120</v>
       </c>
-      <c r="B474" s="3">
-        <v>101800</v>
-      </c>
       <c r="C474" s="3">
         <v>13</v>
       </c>
@@ -29521,7 +29281,7 @@
         <v>439</v>
       </c>
       <c r="E474" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F474" s="3" t="s">
         <v>202</v>
@@ -29540,9 +29300,6 @@
       <c r="A475" s="2">
         <v>101800121</v>
       </c>
-      <c r="B475" s="3">
-        <v>101800</v>
-      </c>
       <c r="C475" s="3">
         <v>14</v>
       </c>
@@ -29550,7 +29307,7 @@
         <v>439</v>
       </c>
       <c r="E475" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F475" s="3" t="s">
         <v>203</v>
@@ -29569,9 +29326,6 @@
       <c r="A476" s="2">
         <v>101800122</v>
       </c>
-      <c r="B476" s="3">
-        <v>101800</v>
-      </c>
       <c r="C476" s="3">
         <v>15</v>
       </c>
@@ -29579,7 +29333,7 @@
         <v>439</v>
       </c>
       <c r="E476" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F476" s="3" t="s">
         <v>204</v>
@@ -29598,9 +29352,6 @@
       <c r="A477" s="2">
         <v>101800123</v>
       </c>
-      <c r="B477" s="3">
-        <v>101800</v>
-      </c>
       <c r="C477" s="3">
         <v>16</v>
       </c>
@@ -29608,7 +29359,7 @@
         <v>439</v>
       </c>
       <c r="E477" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F477" s="3" t="s">
         <v>205</v>
@@ -29627,9 +29378,6 @@
       <c r="A478" s="2">
         <v>101800124</v>
       </c>
-      <c r="B478" s="3">
-        <v>101800</v>
-      </c>
       <c r="C478" s="3">
         <v>17</v>
       </c>
@@ -29637,7 +29385,7 @@
         <v>439</v>
       </c>
       <c r="E478" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F478" s="3" t="s">
         <v>206</v>
@@ -29656,9 +29404,6 @@
       <c r="A479" s="2">
         <v>101800125</v>
       </c>
-      <c r="B479" s="3">
-        <v>101800</v>
-      </c>
       <c r="C479" s="3">
         <v>18</v>
       </c>
@@ -29666,7 +29411,7 @@
         <v>439</v>
       </c>
       <c r="E479" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F479" s="3" t="s">
         <v>207</v>
@@ -29685,9 +29430,6 @@
       <c r="A480" s="2">
         <v>101800126</v>
       </c>
-      <c r="B480" s="3">
-        <v>101800</v>
-      </c>
       <c r="C480" s="3">
         <v>19</v>
       </c>
@@ -29695,7 +29437,7 @@
         <v>439</v>
       </c>
       <c r="E480" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F480" s="3" t="s">
         <v>208</v>
@@ -29714,9 +29456,6 @@
       <c r="A481" s="2">
         <v>101800127</v>
       </c>
-      <c r="B481" s="3">
-        <v>101800</v>
-      </c>
       <c r="C481" s="3">
         <v>20</v>
       </c>
@@ -29724,7 +29463,7 @@
         <v>439</v>
       </c>
       <c r="E481" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F481" s="3" t="s">
         <v>209</v>
@@ -29743,9 +29482,6 @@
       <c r="A482" s="2">
         <v>101800128</v>
       </c>
-      <c r="B482" s="3">
-        <v>101800</v>
-      </c>
       <c r="C482" s="3">
         <v>21</v>
       </c>
@@ -29753,7 +29489,7 @@
         <v>439</v>
       </c>
       <c r="E482" s="2">
-        <v>10180011</v>
+        <v>10030009</v>
       </c>
       <c r="F482" s="3" t="s">
         <v>210</v>
@@ -29772,9 +29508,6 @@
       <c r="A483" s="2">
         <v>101800129</v>
       </c>
-      <c r="B483" s="3">
-        <v>101800</v>
-      </c>
       <c r="C483" s="3">
         <v>0</v>
       </c>
@@ -29782,7 +29515,7 @@
         <v>439</v>
       </c>
       <c r="E483" s="2">
-        <v>10180012</v>
+        <v>10030010</v>
       </c>
       <c r="F483" s="3" t="s">
         <v>38</v>
@@ -29796,9 +29529,6 @@
       <c r="A484" s="2">
         <v>101800130</v>
       </c>
-      <c r="B484" s="3">
-        <v>101800</v>
-      </c>
       <c r="C484" s="3">
         <v>1</v>
       </c>
@@ -29806,7 +29536,7 @@
         <v>439</v>
       </c>
       <c r="E484" s="2">
-        <v>10180012</v>
+        <v>10030010</v>
       </c>
       <c r="F484" s="3" t="s">
         <v>39</v>
@@ -29825,9 +29555,6 @@
       <c r="A485" s="2">
         <v>101800131</v>
       </c>
-      <c r="B485" s="3">
-        <v>101800</v>
-      </c>
       <c r="C485" s="3">
         <v>2</v>
       </c>
@@ -29835,7 +29562,7 @@
         <v>439</v>
       </c>
       <c r="E485" s="2">
-        <v>10180012</v>
+        <v>10030010</v>
       </c>
       <c r="F485" s="3" t="s">
         <v>41</v>
@@ -29854,9 +29581,6 @@
       <c r="A486" s="2">
         <v>101800132</v>
       </c>
-      <c r="B486" s="3">
-        <v>101800</v>
-      </c>
       <c r="C486" s="3">
         <v>3</v>
       </c>
@@ -29864,7 +29588,7 @@
         <v>439</v>
       </c>
       <c r="E486" s="2">
-        <v>10180012</v>
+        <v>10030010</v>
       </c>
       <c r="F486" s="3" t="s">
         <v>44</v>
@@ -29883,9 +29607,6 @@
       <c r="A487" s="2">
         <v>101800133</v>
       </c>
-      <c r="B487" s="3">
-        <v>101800</v>
-      </c>
       <c r="C487" s="3">
         <v>4</v>
       </c>
@@ -29893,7 +29614,7 @@
         <v>439</v>
       </c>
       <c r="E487" s="2">
-        <v>10180012</v>
+        <v>10030010</v>
       </c>
       <c r="F487" s="3" t="s">
         <v>47</v>
@@ -29912,9 +29633,6 @@
       <c r="A488" s="2">
         <v>101800134</v>
       </c>
-      <c r="B488" s="3">
-        <v>101800</v>
-      </c>
       <c r="C488" s="3">
         <v>5</v>
       </c>
@@ -29922,7 +29640,7 @@
         <v>439</v>
       </c>
       <c r="E488" s="2">
-        <v>10180012</v>
+        <v>10030010</v>
       </c>
       <c r="F488" s="3" t="s">
         <v>50</v>
@@ -29941,9 +29659,6 @@
       <c r="A489" s="2">
         <v>101800135</v>
       </c>
-      <c r="B489" s="3">
-        <v>101800</v>
-      </c>
       <c r="C489" s="3">
         <v>6</v>
       </c>
@@ -29951,7 +29666,7 @@
         <v>439</v>
       </c>
       <c r="E489" s="2">
-        <v>10180012</v>
+        <v>10030010</v>
       </c>
       <c r="F489" s="3" t="s">
         <v>53</v>
@@ -29970,9 +29685,6 @@
       <c r="A490" s="2">
         <v>101800136</v>
       </c>
-      <c r="B490" s="3">
-        <v>101800</v>
-      </c>
       <c r="C490" s="3">
         <v>7</v>
       </c>
@@ -29980,7 +29692,7 @@
         <v>439</v>
       </c>
       <c r="E490" s="2">
-        <v>10180012</v>
+        <v>10030010</v>
       </c>
       <c r="F490" s="3" t="s">
         <v>68</v>
@@ -29999,9 +29711,6 @@
       <c r="A491" s="2">
         <v>101800137</v>
       </c>
-      <c r="B491" s="3">
-        <v>101800</v>
-      </c>
       <c r="C491" s="3">
         <v>8</v>
       </c>
@@ -30009,7 +29718,7 @@
         <v>439</v>
       </c>
       <c r="E491" s="2">
-        <v>10180012</v>
+        <v>10030010</v>
       </c>
       <c r="F491" s="3" t="s">
         <v>71</v>
@@ -30028,9 +29737,6 @@
       <c r="A492" s="2">
         <v>101800138</v>
       </c>
-      <c r="B492" s="3">
-        <v>101800</v>
-      </c>
       <c r="C492" s="3">
         <v>9</v>
       </c>
@@ -30038,7 +29744,7 @@
         <v>439</v>
       </c>
       <c r="E492" s="2">
-        <v>10180012</v>
+        <v>10030010</v>
       </c>
       <c r="F492" s="3" t="s">
         <v>74</v>
@@ -30057,9 +29763,6 @@
       <c r="A493" s="2">
         <v>101800139</v>
       </c>
-      <c r="B493" s="3">
-        <v>101800</v>
-      </c>
       <c r="C493" s="3">
         <v>10</v>
       </c>
@@ -30067,7 +29770,7 @@
         <v>439</v>
       </c>
       <c r="E493" s="2">
-        <v>10180012</v>
+        <v>10030010</v>
       </c>
       <c r="F493" s="3" t="s">
         <v>77</v>
@@ -33584,9 +33287,6 @@
       <c r="A600" s="2">
         <v>102500107</v>
       </c>
-      <c r="B600" s="3">
-        <v>102500</v>
-      </c>
       <c r="C600" s="3">
         <v>0</v>
       </c>
@@ -33594,7 +33294,7 @@
         <v>530</v>
       </c>
       <c r="E600" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F600" s="3" t="s">
         <v>38</v>
@@ -33608,9 +33308,6 @@
       <c r="A601" s="2">
         <v>102500108</v>
       </c>
-      <c r="B601" s="3">
-        <v>102500</v>
-      </c>
       <c r="C601" s="3">
         <v>1</v>
       </c>
@@ -33618,7 +33315,7 @@
         <v>530</v>
       </c>
       <c r="E601" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F601" s="3" t="s">
         <v>39</v>
@@ -33637,9 +33334,6 @@
       <c r="A602" s="2">
         <v>102500109</v>
       </c>
-      <c r="B602" s="3">
-        <v>102500</v>
-      </c>
       <c r="C602" s="3">
         <v>2</v>
       </c>
@@ -33647,7 +33341,7 @@
         <v>530</v>
       </c>
       <c r="E602" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F602" s="3" t="s">
         <v>41</v>
@@ -33666,9 +33360,6 @@
       <c r="A603" s="2">
         <v>102500110</v>
       </c>
-      <c r="B603" s="3">
-        <v>102500</v>
-      </c>
       <c r="C603" s="3">
         <v>3</v>
       </c>
@@ -33676,7 +33367,7 @@
         <v>530</v>
       </c>
       <c r="E603" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F603" s="3" t="s">
         <v>44</v>
@@ -33695,9 +33386,6 @@
       <c r="A604" s="2">
         <v>102500111</v>
       </c>
-      <c r="B604" s="3">
-        <v>102500</v>
-      </c>
       <c r="C604" s="3">
         <v>4</v>
       </c>
@@ -33705,7 +33393,7 @@
         <v>530</v>
       </c>
       <c r="E604" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F604" s="3" t="s">
         <v>47</v>
@@ -33724,9 +33412,6 @@
       <c r="A605" s="2">
         <v>102500112</v>
       </c>
-      <c r="B605" s="3">
-        <v>102500</v>
-      </c>
       <c r="C605" s="3">
         <v>5</v>
       </c>
@@ -33734,7 +33419,7 @@
         <v>530</v>
       </c>
       <c r="E605" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F605" s="3" t="s">
         <v>50</v>
@@ -33753,9 +33438,6 @@
       <c r="A606" s="2">
         <v>102500113</v>
       </c>
-      <c r="B606" s="3">
-        <v>102500</v>
-      </c>
       <c r="C606" s="3">
         <v>6</v>
       </c>
@@ -33763,7 +33445,7 @@
         <v>530</v>
       </c>
       <c r="E606" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F606" s="3" t="s">
         <v>53</v>
@@ -33782,9 +33464,6 @@
       <c r="A607" s="2">
         <v>102500114</v>
       </c>
-      <c r="B607" s="3">
-        <v>102500</v>
-      </c>
       <c r="C607" s="3">
         <v>7</v>
       </c>
@@ -33792,7 +33471,7 @@
         <v>530</v>
       </c>
       <c r="E607" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F607" s="3" t="s">
         <v>68</v>
@@ -33811,9 +33490,6 @@
       <c r="A608" s="2">
         <v>102500115</v>
       </c>
-      <c r="B608" s="3">
-        <v>102500</v>
-      </c>
       <c r="C608" s="3">
         <v>8</v>
       </c>
@@ -33821,7 +33497,7 @@
         <v>530</v>
       </c>
       <c r="E608" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F608" s="3" t="s">
         <v>71</v>
@@ -33840,9 +33516,6 @@
       <c r="A609" s="2">
         <v>102500116</v>
       </c>
-      <c r="B609" s="3">
-        <v>102500</v>
-      </c>
       <c r="C609" s="3">
         <v>9</v>
       </c>
@@ -33850,7 +33523,7 @@
         <v>530</v>
       </c>
       <c r="E609" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F609" s="3" t="s">
         <v>74</v>
@@ -33869,9 +33542,6 @@
       <c r="A610" s="2">
         <v>102500117</v>
       </c>
-      <c r="B610" s="3">
-        <v>102500</v>
-      </c>
       <c r="C610" s="3">
         <v>10</v>
       </c>
@@ -33879,7 +33549,7 @@
         <v>530</v>
       </c>
       <c r="E610" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F610" s="3" t="s">
         <v>77</v>
@@ -33898,9 +33568,6 @@
       <c r="A611" s="2">
         <v>102500118</v>
       </c>
-      <c r="B611" s="3">
-        <v>102500</v>
-      </c>
       <c r="C611" s="3">
         <v>11</v>
       </c>
@@ -33908,7 +33575,7 @@
         <v>530</v>
       </c>
       <c r="E611" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F611" s="3" t="s">
         <v>200</v>
@@ -33927,9 +33594,6 @@
       <c r="A612" s="2">
         <v>102500119</v>
       </c>
-      <c r="B612" s="3">
-        <v>102500</v>
-      </c>
       <c r="C612" s="3">
         <v>12</v>
       </c>
@@ -33937,7 +33601,7 @@
         <v>530</v>
       </c>
       <c r="E612" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F612" s="3" t="s">
         <v>201</v>
@@ -33956,9 +33620,6 @@
       <c r="A613" s="2">
         <v>102500120</v>
       </c>
-      <c r="B613" s="3">
-        <v>102500</v>
-      </c>
       <c r="C613" s="3">
         <v>13</v>
       </c>
@@ -33966,7 +33627,7 @@
         <v>530</v>
       </c>
       <c r="E613" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F613" s="3" t="s">
         <v>202</v>
@@ -33985,9 +33646,6 @@
       <c r="A614" s="2">
         <v>102500121</v>
       </c>
-      <c r="B614" s="3">
-        <v>102500</v>
-      </c>
       <c r="C614" s="3">
         <v>14</v>
       </c>
@@ -33995,7 +33653,7 @@
         <v>530</v>
       </c>
       <c r="E614" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F614" s="3" t="s">
         <v>203</v>
@@ -34014,9 +33672,6 @@
       <c r="A615" s="2">
         <v>102500122</v>
       </c>
-      <c r="B615" s="3">
-        <v>102500</v>
-      </c>
       <c r="C615" s="3">
         <v>15</v>
       </c>
@@ -34024,7 +33679,7 @@
         <v>530</v>
       </c>
       <c r="E615" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F615" s="3" t="s">
         <v>204</v>
@@ -34043,9 +33698,6 @@
       <c r="A616" s="2">
         <v>102500123</v>
       </c>
-      <c r="B616" s="3">
-        <v>102500</v>
-      </c>
       <c r="C616" s="3">
         <v>16</v>
       </c>
@@ -34053,7 +33705,7 @@
         <v>530</v>
       </c>
       <c r="E616" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F616" s="3" t="s">
         <v>205</v>
@@ -34072,9 +33724,6 @@
       <c r="A617" s="2">
         <v>102500124</v>
       </c>
-      <c r="B617" s="3">
-        <v>102500</v>
-      </c>
       <c r="C617" s="3">
         <v>17</v>
       </c>
@@ -34082,7 +33731,7 @@
         <v>530</v>
       </c>
       <c r="E617" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F617" s="3" t="s">
         <v>206</v>
@@ -34101,9 +33750,6 @@
       <c r="A618" s="2">
         <v>102500125</v>
       </c>
-      <c r="B618" s="3">
-        <v>102500</v>
-      </c>
       <c r="C618" s="3">
         <v>18</v>
       </c>
@@ -34111,7 +33757,7 @@
         <v>530</v>
       </c>
       <c r="E618" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F618" s="3" t="s">
         <v>207</v>
@@ -34130,9 +33776,6 @@
       <c r="A619" s="2">
         <v>102500126</v>
       </c>
-      <c r="B619" s="3">
-        <v>102500</v>
-      </c>
       <c r="C619" s="3">
         <v>19</v>
       </c>
@@ -34140,7 +33783,7 @@
         <v>530</v>
       </c>
       <c r="E619" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F619" s="3" t="s">
         <v>208</v>
@@ -34159,9 +33802,6 @@
       <c r="A620" s="2">
         <v>102500127</v>
       </c>
-      <c r="B620" s="3">
-        <v>102500</v>
-      </c>
       <c r="C620" s="3">
         <v>20</v>
       </c>
@@ -34169,7 +33809,7 @@
         <v>530</v>
       </c>
       <c r="E620" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F620" s="3" t="s">
         <v>209</v>
@@ -34188,9 +33828,6 @@
       <c r="A621" s="2">
         <v>102500128</v>
       </c>
-      <c r="B621" s="3">
-        <v>102500</v>
-      </c>
       <c r="C621" s="3">
         <v>21</v>
       </c>
@@ -34198,7 +33835,7 @@
         <v>530</v>
       </c>
       <c r="E621" s="2">
-        <v>10250011</v>
+        <v>10030009</v>
       </c>
       <c r="F621" s="3" t="s">
         <v>210</v>
@@ -34217,9 +33854,6 @@
       <c r="A622" s="2">
         <v>102500129</v>
       </c>
-      <c r="B622" s="3">
-        <v>102500</v>
-      </c>
       <c r="C622" s="3">
         <v>0</v>
       </c>
@@ -34227,7 +33861,7 @@
         <v>530</v>
       </c>
       <c r="E622" s="2">
-        <v>10250012</v>
+        <v>10030010</v>
       </c>
       <c r="F622" s="3" t="s">
         <v>38</v>
@@ -34241,9 +33875,6 @@
       <c r="A623" s="2">
         <v>102500130</v>
       </c>
-      <c r="B623" s="3">
-        <v>102500</v>
-      </c>
       <c r="C623" s="3">
         <v>1</v>
       </c>
@@ -34251,7 +33882,7 @@
         <v>530</v>
       </c>
       <c r="E623" s="2">
-        <v>10250012</v>
+        <v>10030010</v>
       </c>
       <c r="F623" s="3" t="s">
         <v>39</v>
@@ -34270,9 +33901,6 @@
       <c r="A624" s="2">
         <v>102500131</v>
       </c>
-      <c r="B624" s="3">
-        <v>102500</v>
-      </c>
       <c r="C624" s="3">
         <v>2</v>
       </c>
@@ -34280,7 +33908,7 @@
         <v>530</v>
       </c>
       <c r="E624" s="2">
-        <v>10250012</v>
+        <v>10030010</v>
       </c>
       <c r="F624" s="3" t="s">
         <v>41</v>
@@ -34299,9 +33927,6 @@
       <c r="A625" s="2">
         <v>102500132</v>
       </c>
-      <c r="B625" s="3">
-        <v>102500</v>
-      </c>
       <c r="C625" s="3">
         <v>3</v>
       </c>
@@ -34309,7 +33934,7 @@
         <v>530</v>
       </c>
       <c r="E625" s="2">
-        <v>10250012</v>
+        <v>10030010</v>
       </c>
       <c r="F625" s="3" t="s">
         <v>44</v>
@@ -34328,9 +33953,6 @@
       <c r="A626" s="2">
         <v>102500133</v>
       </c>
-      <c r="B626" s="3">
-        <v>102500</v>
-      </c>
       <c r="C626" s="3">
         <v>4</v>
       </c>
@@ -34338,7 +33960,7 @@
         <v>530</v>
       </c>
       <c r="E626" s="2">
-        <v>10250012</v>
+        <v>10030010</v>
       </c>
       <c r="F626" s="3" t="s">
         <v>47</v>
@@ -34357,9 +33979,6 @@
       <c r="A627" s="2">
         <v>102500134</v>
       </c>
-      <c r="B627" s="3">
-        <v>102500</v>
-      </c>
       <c r="C627" s="3">
         <v>5</v>
       </c>
@@ -34367,7 +33986,7 @@
         <v>530</v>
       </c>
       <c r="E627" s="2">
-        <v>10250012</v>
+        <v>10030010</v>
       </c>
       <c r="F627" s="3" t="s">
         <v>50</v>
@@ -34386,9 +34005,6 @@
       <c r="A628" s="2">
         <v>102500135</v>
       </c>
-      <c r="B628" s="3">
-        <v>102500</v>
-      </c>
       <c r="C628" s="3">
         <v>6</v>
       </c>
@@ -34396,7 +34012,7 @@
         <v>530</v>
       </c>
       <c r="E628" s="2">
-        <v>10250012</v>
+        <v>10030010</v>
       </c>
       <c r="F628" s="3" t="s">
         <v>53</v>
@@ -34415,9 +34031,6 @@
       <c r="A629" s="2">
         <v>102500136</v>
       </c>
-      <c r="B629" s="3">
-        <v>102500</v>
-      </c>
       <c r="C629" s="3">
         <v>7</v>
       </c>
@@ -34425,7 +34038,7 @@
         <v>530</v>
       </c>
       <c r="E629" s="2">
-        <v>10250012</v>
+        <v>10030010</v>
       </c>
       <c r="F629" s="3" t="s">
         <v>68</v>
@@ -34444,9 +34057,6 @@
       <c r="A630" s="2">
         <v>102500137</v>
       </c>
-      <c r="B630" s="3">
-        <v>102500</v>
-      </c>
       <c r="C630" s="3">
         <v>8</v>
       </c>
@@ -34454,7 +34064,7 @@
         <v>530</v>
       </c>
       <c r="E630" s="2">
-        <v>10250012</v>
+        <v>10030010</v>
       </c>
       <c r="F630" s="3" t="s">
         <v>71</v>
@@ -34473,9 +34083,6 @@
       <c r="A631" s="2">
         <v>102500138</v>
       </c>
-      <c r="B631" s="3">
-        <v>102500</v>
-      </c>
       <c r="C631" s="3">
         <v>9</v>
       </c>
@@ -34483,7 +34090,7 @@
         <v>530</v>
       </c>
       <c r="E631" s="2">
-        <v>10250012</v>
+        <v>10030010</v>
       </c>
       <c r="F631" s="3" t="s">
         <v>74</v>
@@ -34502,9 +34109,6 @@
       <c r="A632" s="2">
         <v>102500139</v>
       </c>
-      <c r="B632" s="3">
-        <v>102500</v>
-      </c>
       <c r="C632" s="3">
         <v>10</v>
       </c>
@@ -34512,7 +34116,7 @@
         <v>530</v>
       </c>
       <c r="E632" s="2">
-        <v>10250012</v>
+        <v>10030010</v>
       </c>
       <c r="F632" s="3" t="s">
         <v>77</v>
@@ -39121,9 +38725,6 @@
       <c r="A772" s="2">
         <v>103100140</v>
       </c>
-      <c r="B772" s="3">
-        <v>103100</v>
-      </c>
       <c r="C772" s="3">
         <v>0</v>
       </c>
@@ -39131,7 +38732,7 @@
         <v>601</v>
       </c>
       <c r="E772" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F772" s="3" t="s">
         <v>38</v>
@@ -39145,9 +38746,6 @@
       <c r="A773" s="2">
         <v>103100141</v>
       </c>
-      <c r="B773" s="3">
-        <v>103100</v>
-      </c>
       <c r="C773" s="3">
         <v>1</v>
       </c>
@@ -39155,7 +38753,7 @@
         <v>601</v>
       </c>
       <c r="E773" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F773" s="3" t="s">
         <v>39</v>
@@ -39174,9 +38772,6 @@
       <c r="A774" s="2">
         <v>103100142</v>
       </c>
-      <c r="B774" s="3">
-        <v>103100</v>
-      </c>
       <c r="C774" s="3">
         <v>2</v>
       </c>
@@ -39184,7 +38779,7 @@
         <v>601</v>
       </c>
       <c r="E774" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F774" s="3" t="s">
         <v>41</v>
@@ -39203,9 +38798,6 @@
       <c r="A775" s="2">
         <v>103100143</v>
       </c>
-      <c r="B775" s="3">
-        <v>103100</v>
-      </c>
       <c r="C775" s="3">
         <v>3</v>
       </c>
@@ -39213,7 +38805,7 @@
         <v>601</v>
       </c>
       <c r="E775" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F775" s="3" t="s">
         <v>44</v>
@@ -39232,9 +38824,6 @@
       <c r="A776" s="2">
         <v>103100144</v>
       </c>
-      <c r="B776" s="3">
-        <v>103100</v>
-      </c>
       <c r="C776" s="3">
         <v>4</v>
       </c>
@@ -39242,7 +38831,7 @@
         <v>601</v>
       </c>
       <c r="E776" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F776" s="3" t="s">
         <v>47</v>
@@ -39261,9 +38850,6 @@
       <c r="A777" s="2">
         <v>103100145</v>
       </c>
-      <c r="B777" s="3">
-        <v>103100</v>
-      </c>
       <c r="C777" s="3">
         <v>5</v>
       </c>
@@ -39271,7 +38857,7 @@
         <v>601</v>
       </c>
       <c r="E777" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F777" s="3" t="s">
         <v>50</v>
@@ -39290,9 +38876,6 @@
       <c r="A778" s="2">
         <v>103100146</v>
       </c>
-      <c r="B778" s="3">
-        <v>103100</v>
-      </c>
       <c r="C778" s="3">
         <v>6</v>
       </c>
@@ -39300,7 +38883,7 @@
         <v>601</v>
       </c>
       <c r="E778" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F778" s="3" t="s">
         <v>53</v>
@@ -39319,9 +38902,6 @@
       <c r="A779" s="2">
         <v>103100147</v>
       </c>
-      <c r="B779" s="3">
-        <v>103100</v>
-      </c>
       <c r="C779" s="3">
         <v>7</v>
       </c>
@@ -39329,7 +38909,7 @@
         <v>601</v>
       </c>
       <c r="E779" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F779" s="3" t="s">
         <v>68</v>
@@ -39348,9 +38928,6 @@
       <c r="A780" s="2">
         <v>103100148</v>
       </c>
-      <c r="B780" s="3">
-        <v>103100</v>
-      </c>
       <c r="C780" s="3">
         <v>8</v>
       </c>
@@ -39358,7 +38935,7 @@
         <v>601</v>
       </c>
       <c r="E780" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F780" s="3" t="s">
         <v>71</v>
@@ -39377,9 +38954,6 @@
       <c r="A781" s="2">
         <v>103100149</v>
       </c>
-      <c r="B781" s="3">
-        <v>103100</v>
-      </c>
       <c r="C781" s="3">
         <v>9</v>
       </c>
@@ -39387,7 +38961,7 @@
         <v>601</v>
       </c>
       <c r="E781" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F781" s="3" t="s">
         <v>74</v>
@@ -39406,9 +38980,6 @@
       <c r="A782" s="2">
         <v>103100150</v>
       </c>
-      <c r="B782" s="3">
-        <v>103100</v>
-      </c>
       <c r="C782" s="3">
         <v>10</v>
       </c>
@@ -39416,7 +38987,7 @@
         <v>601</v>
       </c>
       <c r="E782" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F782" s="3" t="s">
         <v>77</v>
@@ -39435,9 +39006,6 @@
       <c r="A783" s="2">
         <v>103100151</v>
       </c>
-      <c r="B783" s="3">
-        <v>103100</v>
-      </c>
       <c r="C783" s="3">
         <v>11</v>
       </c>
@@ -39445,7 +39013,7 @@
         <v>601</v>
       </c>
       <c r="E783" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F783" s="3" t="s">
         <v>200</v>
@@ -39464,9 +39032,6 @@
       <c r="A784" s="2">
         <v>103100152</v>
       </c>
-      <c r="B784" s="3">
-        <v>103100</v>
-      </c>
       <c r="C784" s="3">
         <v>12</v>
       </c>
@@ -39474,7 +39039,7 @@
         <v>601</v>
       </c>
       <c r="E784" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F784" s="3" t="s">
         <v>201</v>
@@ -39493,9 +39058,6 @@
       <c r="A785" s="2">
         <v>103100153</v>
       </c>
-      <c r="B785" s="3">
-        <v>103100</v>
-      </c>
       <c r="C785" s="3">
         <v>13</v>
       </c>
@@ -39503,7 +39065,7 @@
         <v>601</v>
       </c>
       <c r="E785" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F785" s="3" t="s">
         <v>202</v>
@@ -39522,9 +39084,6 @@
       <c r="A786" s="2">
         <v>103100154</v>
       </c>
-      <c r="B786" s="3">
-        <v>103100</v>
-      </c>
       <c r="C786" s="3">
         <v>14</v>
       </c>
@@ -39532,7 +39091,7 @@
         <v>601</v>
       </c>
       <c r="E786" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F786" s="3" t="s">
         <v>203</v>
@@ -39551,9 +39110,6 @@
       <c r="A787" s="2">
         <v>103100155</v>
       </c>
-      <c r="B787" s="3">
-        <v>103100</v>
-      </c>
       <c r="C787" s="3">
         <v>15</v>
       </c>
@@ -39561,7 +39117,7 @@
         <v>601</v>
       </c>
       <c r="E787" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F787" s="3" t="s">
         <v>204</v>
@@ -39580,9 +39136,6 @@
       <c r="A788" s="2">
         <v>103100156</v>
       </c>
-      <c r="B788" s="3">
-        <v>103100</v>
-      </c>
       <c r="C788" s="3">
         <v>16</v>
       </c>
@@ -39590,7 +39143,7 @@
         <v>601</v>
       </c>
       <c r="E788" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F788" s="3" t="s">
         <v>205</v>
@@ -39609,9 +39162,6 @@
       <c r="A789" s="2">
         <v>103100157</v>
       </c>
-      <c r="B789" s="3">
-        <v>103100</v>
-      </c>
       <c r="C789" s="3">
         <v>17</v>
       </c>
@@ -39619,7 +39169,7 @@
         <v>601</v>
       </c>
       <c r="E789" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F789" s="3" t="s">
         <v>206</v>
@@ -39638,9 +39188,6 @@
       <c r="A790" s="2">
         <v>103100158</v>
       </c>
-      <c r="B790" s="3">
-        <v>103100</v>
-      </c>
       <c r="C790" s="3">
         <v>18</v>
       </c>
@@ -39648,7 +39195,7 @@
         <v>601</v>
       </c>
       <c r="E790" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F790" s="3" t="s">
         <v>207</v>
@@ -39667,9 +39214,6 @@
       <c r="A791" s="2">
         <v>103100159</v>
       </c>
-      <c r="B791" s="3">
-        <v>103100</v>
-      </c>
       <c r="C791" s="3">
         <v>19</v>
       </c>
@@ -39677,7 +39221,7 @@
         <v>601</v>
       </c>
       <c r="E791" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F791" s="3" t="s">
         <v>208</v>
@@ -39696,9 +39240,6 @@
       <c r="A792" s="2">
         <v>103100160</v>
       </c>
-      <c r="B792" s="3">
-        <v>103100</v>
-      </c>
       <c r="C792" s="3">
         <v>20</v>
       </c>
@@ -39706,7 +39247,7 @@
         <v>601</v>
       </c>
       <c r="E792" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F792" s="3" t="s">
         <v>209</v>
@@ -39725,9 +39266,6 @@
       <c r="A793" s="2">
         <v>103100161</v>
       </c>
-      <c r="B793" s="3">
-        <v>103100</v>
-      </c>
       <c r="C793" s="3">
         <v>21</v>
       </c>
@@ -39735,7 +39273,7 @@
         <v>601</v>
       </c>
       <c r="E793" s="2">
-        <v>10310014</v>
+        <v>10030009</v>
       </c>
       <c r="F793" s="3" t="s">
         <v>210</v>
@@ -39754,9 +39292,6 @@
       <c r="A794" s="2">
         <v>103100162</v>
       </c>
-      <c r="B794" s="3">
-        <v>103100</v>
-      </c>
       <c r="C794" s="3">
         <v>0</v>
       </c>
@@ -39764,7 +39299,7 @@
         <v>601</v>
       </c>
       <c r="E794" s="2">
-        <v>10310015</v>
+        <v>10030010</v>
       </c>
       <c r="F794" s="3" t="s">
         <v>38</v>
@@ -39778,9 +39313,6 @@
       <c r="A795" s="2">
         <v>103100163</v>
       </c>
-      <c r="B795" s="3">
-        <v>103100</v>
-      </c>
       <c r="C795" s="3">
         <v>1</v>
       </c>
@@ -39788,7 +39320,7 @@
         <v>601</v>
       </c>
       <c r="E795" s="2">
-        <v>10310015</v>
+        <v>10030010</v>
       </c>
       <c r="F795" s="3" t="s">
         <v>39</v>
@@ -39807,9 +39339,6 @@
       <c r="A796" s="2">
         <v>103100164</v>
       </c>
-      <c r="B796" s="3">
-        <v>103100</v>
-      </c>
       <c r="C796" s="3">
         <v>2</v>
       </c>
@@ -39817,7 +39346,7 @@
         <v>601</v>
       </c>
       <c r="E796" s="2">
-        <v>10310015</v>
+        <v>10030010</v>
       </c>
       <c r="F796" s="3" t="s">
         <v>41</v>
@@ -39836,9 +39365,6 @@
       <c r="A797" s="2">
         <v>103100165</v>
       </c>
-      <c r="B797" s="3">
-        <v>103100</v>
-      </c>
       <c r="C797" s="3">
         <v>3</v>
       </c>
@@ -39846,7 +39372,7 @@
         <v>601</v>
       </c>
       <c r="E797" s="2">
-        <v>10310015</v>
+        <v>10030010</v>
       </c>
       <c r="F797" s="3" t="s">
         <v>44</v>
@@ -39865,9 +39391,6 @@
       <c r="A798" s="2">
         <v>103100166</v>
       </c>
-      <c r="B798" s="3">
-        <v>103100</v>
-      </c>
       <c r="C798" s="3">
         <v>4</v>
       </c>
@@ -39875,7 +39398,7 @@
         <v>601</v>
       </c>
       <c r="E798" s="2">
-        <v>10310015</v>
+        <v>10030010</v>
       </c>
       <c r="F798" s="3" t="s">
         <v>47</v>
@@ -39894,9 +39417,6 @@
       <c r="A799" s="2">
         <v>103100167</v>
       </c>
-      <c r="B799" s="3">
-        <v>103100</v>
-      </c>
       <c r="C799" s="3">
         <v>5</v>
       </c>
@@ -39904,7 +39424,7 @@
         <v>601</v>
       </c>
       <c r="E799" s="2">
-        <v>10310015</v>
+        <v>10030010</v>
       </c>
       <c r="F799" s="3" t="s">
         <v>50</v>
@@ -39923,9 +39443,6 @@
       <c r="A800" s="2">
         <v>103100168</v>
       </c>
-      <c r="B800" s="3">
-        <v>103100</v>
-      </c>
       <c r="C800" s="3">
         <v>6</v>
       </c>
@@ -39933,7 +39450,7 @@
         <v>601</v>
       </c>
       <c r="E800" s="2">
-        <v>10310015</v>
+        <v>10030010</v>
       </c>
       <c r="F800" s="3" t="s">
         <v>53</v>
@@ -39952,9 +39469,6 @@
       <c r="A801" s="2">
         <v>103100169</v>
       </c>
-      <c r="B801" s="3">
-        <v>103100</v>
-      </c>
       <c r="C801" s="3">
         <v>7</v>
       </c>
@@ -39962,7 +39476,7 @@
         <v>601</v>
       </c>
       <c r="E801" s="2">
-        <v>10310015</v>
+        <v>10030010</v>
       </c>
       <c r="F801" s="3" t="s">
         <v>68</v>
@@ -39981,9 +39495,6 @@
       <c r="A802" s="2">
         <v>103100170</v>
       </c>
-      <c r="B802" s="3">
-        <v>103100</v>
-      </c>
       <c r="C802" s="3">
         <v>8</v>
       </c>
@@ -39991,7 +39502,7 @@
         <v>601</v>
       </c>
       <c r="E802" s="2">
-        <v>10310015</v>
+        <v>10030010</v>
       </c>
       <c r="F802" s="3" t="s">
         <v>71</v>
@@ -40010,9 +39521,6 @@
       <c r="A803" s="2">
         <v>103100171</v>
       </c>
-      <c r="B803" s="3">
-        <v>103100</v>
-      </c>
       <c r="C803" s="3">
         <v>9</v>
       </c>
@@ -40020,7 +39528,7 @@
         <v>601</v>
       </c>
       <c r="E803" s="2">
-        <v>10310015</v>
+        <v>10030010</v>
       </c>
       <c r="F803" s="3" t="s">
         <v>74</v>
@@ -40039,9 +39547,6 @@
       <c r="A804" s="2">
         <v>103100172</v>
       </c>
-      <c r="B804" s="3">
-        <v>103100</v>
-      </c>
       <c r="C804" s="3">
         <v>10</v>
       </c>
@@ -40049,7 +39554,7 @@
         <v>601</v>
       </c>
       <c r="E804" s="2">
-        <v>10310015</v>
+        <v>10030010</v>
       </c>
       <c r="F804" s="3" t="s">
         <v>77</v>
@@ -43190,9 +42695,6 @@
       <c r="A900" s="2">
         <v>102200096</v>
       </c>
-      <c r="B900" s="3">
-        <v>102200</v>
-      </c>
       <c r="C900" s="3">
         <v>0</v>
       </c>
@@ -43200,7 +42702,7 @@
         <v>744</v>
       </c>
       <c r="E900" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F900" s="3" t="s">
         <v>38</v>
@@ -43214,9 +42716,6 @@
       <c r="A901" s="2">
         <v>102200097</v>
       </c>
-      <c r="B901" s="3">
-        <v>102200</v>
-      </c>
       <c r="C901" s="3">
         <v>1</v>
       </c>
@@ -43224,7 +42723,7 @@
         <v>744</v>
       </c>
       <c r="E901" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F901" s="3" t="s">
         <v>39</v>
@@ -43243,9 +42742,6 @@
       <c r="A902" s="2">
         <v>102200098</v>
       </c>
-      <c r="B902" s="3">
-        <v>102200</v>
-      </c>
       <c r="C902" s="3">
         <v>2</v>
       </c>
@@ -43253,7 +42749,7 @@
         <v>744</v>
       </c>
       <c r="E902" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F902" s="3" t="s">
         <v>41</v>
@@ -43272,9 +42768,6 @@
       <c r="A903" s="2">
         <v>102200099</v>
       </c>
-      <c r="B903" s="3">
-        <v>102200</v>
-      </c>
       <c r="C903" s="3">
         <v>3</v>
       </c>
@@ -43282,7 +42775,7 @@
         <v>744</v>
       </c>
       <c r="E903" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F903" s="3" t="s">
         <v>44</v>
@@ -43301,9 +42794,6 @@
       <c r="A904" s="2">
         <v>102200100</v>
       </c>
-      <c r="B904" s="3">
-        <v>102200</v>
-      </c>
       <c r="C904" s="3">
         <v>4</v>
       </c>
@@ -43311,7 +42801,7 @@
         <v>744</v>
       </c>
       <c r="E904" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F904" s="3" t="s">
         <v>47</v>
@@ -43330,9 +42820,6 @@
       <c r="A905" s="2">
         <v>102200101</v>
       </c>
-      <c r="B905" s="3">
-        <v>102200</v>
-      </c>
       <c r="C905" s="3">
         <v>5</v>
       </c>
@@ -43340,7 +42827,7 @@
         <v>744</v>
       </c>
       <c r="E905" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F905" s="3" t="s">
         <v>50</v>
@@ -43359,9 +42846,6 @@
       <c r="A906" s="2">
         <v>102200102</v>
       </c>
-      <c r="B906" s="3">
-        <v>102200</v>
-      </c>
       <c r="C906" s="3">
         <v>6</v>
       </c>
@@ -43369,7 +42853,7 @@
         <v>744</v>
       </c>
       <c r="E906" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F906" s="3" t="s">
         <v>53</v>
@@ -43388,9 +42872,6 @@
       <c r="A907" s="2">
         <v>102200103</v>
       </c>
-      <c r="B907" s="3">
-        <v>102200</v>
-      </c>
       <c r="C907" s="3">
         <v>7</v>
       </c>
@@ -43398,7 +42879,7 @@
         <v>744</v>
       </c>
       <c r="E907" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F907" s="3" t="s">
         <v>68</v>
@@ -43417,9 +42898,6 @@
       <c r="A908" s="2">
         <v>102200104</v>
       </c>
-      <c r="B908" s="3">
-        <v>102200</v>
-      </c>
       <c r="C908" s="3">
         <v>8</v>
       </c>
@@ -43427,7 +42905,7 @@
         <v>744</v>
       </c>
       <c r="E908" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F908" s="3" t="s">
         <v>71</v>
@@ -43446,9 +42924,6 @@
       <c r="A909" s="2">
         <v>102200105</v>
       </c>
-      <c r="B909" s="3">
-        <v>102200</v>
-      </c>
       <c r="C909" s="3">
         <v>9</v>
       </c>
@@ -43456,7 +42931,7 @@
         <v>744</v>
       </c>
       <c r="E909" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F909" s="3" t="s">
         <v>74</v>
@@ -43475,9 +42950,6 @@
       <c r="A910" s="2">
         <v>102200106</v>
       </c>
-      <c r="B910" s="3">
-        <v>102200</v>
-      </c>
       <c r="C910" s="3">
         <v>10</v>
       </c>
@@ -43485,7 +42957,7 @@
         <v>744</v>
       </c>
       <c r="E910" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F910" s="3" t="s">
         <v>77</v>
@@ -43504,9 +42976,6 @@
       <c r="A911" s="2">
         <v>102200107</v>
       </c>
-      <c r="B911" s="3">
-        <v>102200</v>
-      </c>
       <c r="C911" s="3">
         <v>11</v>
       </c>
@@ -43514,7 +42983,7 @@
         <v>744</v>
       </c>
       <c r="E911" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F911" s="3" t="s">
         <v>200</v>
@@ -43533,9 +43002,6 @@
       <c r="A912" s="2">
         <v>102200108</v>
       </c>
-      <c r="B912" s="3">
-        <v>102200</v>
-      </c>
       <c r="C912" s="3">
         <v>12</v>
       </c>
@@ -43543,7 +43009,7 @@
         <v>744</v>
       </c>
       <c r="E912" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F912" s="3" t="s">
         <v>201</v>
@@ -43562,9 +43028,6 @@
       <c r="A913" s="2">
         <v>102200109</v>
       </c>
-      <c r="B913" s="3">
-        <v>102200</v>
-      </c>
       <c r="C913" s="3">
         <v>13</v>
       </c>
@@ -43572,7 +43035,7 @@
         <v>744</v>
       </c>
       <c r="E913" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F913" s="3" t="s">
         <v>202</v>
@@ -43591,9 +43054,6 @@
       <c r="A914" s="2">
         <v>102200110</v>
       </c>
-      <c r="B914" s="3">
-        <v>102200</v>
-      </c>
       <c r="C914" s="3">
         <v>14</v>
       </c>
@@ -43601,7 +43061,7 @@
         <v>744</v>
       </c>
       <c r="E914" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F914" s="3" t="s">
         <v>203</v>
@@ -43620,9 +43080,6 @@
       <c r="A915" s="2">
         <v>102200111</v>
       </c>
-      <c r="B915" s="3">
-        <v>102200</v>
-      </c>
       <c r="C915" s="3">
         <v>15</v>
       </c>
@@ -43630,7 +43087,7 @@
         <v>744</v>
       </c>
       <c r="E915" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F915" s="3" t="s">
         <v>204</v>
@@ -43649,9 +43106,6 @@
       <c r="A916" s="2">
         <v>102200112</v>
       </c>
-      <c r="B916" s="3">
-        <v>102200</v>
-      </c>
       <c r="C916" s="3">
         <v>16</v>
       </c>
@@ -43659,7 +43113,7 @@
         <v>744</v>
       </c>
       <c r="E916" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F916" s="3" t="s">
         <v>205</v>
@@ -43678,9 +43132,6 @@
       <c r="A917" s="2">
         <v>102200113</v>
       </c>
-      <c r="B917" s="3">
-        <v>102200</v>
-      </c>
       <c r="C917" s="3">
         <v>17</v>
       </c>
@@ -43688,7 +43139,7 @@
         <v>744</v>
       </c>
       <c r="E917" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F917" s="3" t="s">
         <v>206</v>
@@ -43707,9 +43158,6 @@
       <c r="A918" s="2">
         <v>102200114</v>
       </c>
-      <c r="B918" s="3">
-        <v>102200</v>
-      </c>
       <c r="C918" s="3">
         <v>18</v>
       </c>
@@ -43717,7 +43165,7 @@
         <v>744</v>
       </c>
       <c r="E918" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F918" s="3" t="s">
         <v>207</v>
@@ -43736,9 +43184,6 @@
       <c r="A919" s="2">
         <v>102200115</v>
       </c>
-      <c r="B919" s="3">
-        <v>102200</v>
-      </c>
       <c r="C919" s="3">
         <v>19</v>
       </c>
@@ -43746,7 +43191,7 @@
         <v>744</v>
       </c>
       <c r="E919" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F919" s="3" t="s">
         <v>208</v>
@@ -43765,9 +43210,6 @@
       <c r="A920" s="2">
         <v>102200116</v>
       </c>
-      <c r="B920" s="3">
-        <v>102200</v>
-      </c>
       <c r="C920" s="3">
         <v>20</v>
       </c>
@@ -43775,7 +43217,7 @@
         <v>744</v>
       </c>
       <c r="E920" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F920" s="3" t="s">
         <v>209</v>
@@ -43794,9 +43236,6 @@
       <c r="A921" s="2">
         <v>102200117</v>
       </c>
-      <c r="B921" s="3">
-        <v>102200</v>
-      </c>
       <c r="C921" s="3">
         <v>21</v>
       </c>
@@ -43804,7 +43243,7 @@
         <v>744</v>
       </c>
       <c r="E921" s="2">
-        <v>10220010</v>
+        <v>10030009</v>
       </c>
       <c r="F921" s="3" t="s">
         <v>210</v>
@@ -43823,9 +43262,6 @@
       <c r="A922" s="2">
         <v>102200118</v>
       </c>
-      <c r="B922" s="3">
-        <v>102200</v>
-      </c>
       <c r="C922" s="3">
         <v>0</v>
       </c>
@@ -43833,7 +43269,7 @@
         <v>744</v>
       </c>
       <c r="E922" s="2">
-        <v>10220013</v>
+        <v>10030010</v>
       </c>
       <c r="F922" s="3" t="s">
         <v>38</v>
@@ -43847,9 +43283,6 @@
       <c r="A923" s="2">
         <v>102200119</v>
       </c>
-      <c r="B923" s="3">
-        <v>102200</v>
-      </c>
       <c r="C923" s="3">
         <v>1</v>
       </c>
@@ -43857,7 +43290,7 @@
         <v>744</v>
       </c>
       <c r="E923" s="2">
-        <v>10220013</v>
+        <v>10030010</v>
       </c>
       <c r="F923" s="3" t="s">
         <v>39</v>
@@ -43876,9 +43309,6 @@
       <c r="A924" s="2">
         <v>102200120</v>
       </c>
-      <c r="B924" s="3">
-        <v>102200</v>
-      </c>
       <c r="C924" s="3">
         <v>2</v>
       </c>
@@ -43886,7 +43316,7 @@
         <v>744</v>
       </c>
       <c r="E924" s="2">
-        <v>10220013</v>
+        <v>10030010</v>
       </c>
       <c r="F924" s="3" t="s">
         <v>41</v>
@@ -43905,9 +43335,6 @@
       <c r="A925" s="2">
         <v>102200121</v>
       </c>
-      <c r="B925" s="3">
-        <v>102200</v>
-      </c>
       <c r="C925" s="3">
         <v>3</v>
       </c>
@@ -43915,7 +43342,7 @@
         <v>744</v>
       </c>
       <c r="E925" s="2">
-        <v>10220013</v>
+        <v>10030010</v>
       </c>
       <c r="F925" s="3" t="s">
         <v>44</v>
@@ -43934,9 +43361,6 @@
       <c r="A926" s="2">
         <v>102200122</v>
       </c>
-      <c r="B926" s="3">
-        <v>102200</v>
-      </c>
       <c r="C926" s="3">
         <v>4</v>
       </c>
@@ -43944,7 +43368,7 @@
         <v>744</v>
       </c>
       <c r="E926" s="2">
-        <v>10220013</v>
+        <v>10030010</v>
       </c>
       <c r="F926" s="3" t="s">
         <v>47</v>
@@ -43963,9 +43387,6 @@
       <c r="A927" s="2">
         <v>102200123</v>
       </c>
-      <c r="B927" s="3">
-        <v>102200</v>
-      </c>
       <c r="C927" s="3">
         <v>5</v>
       </c>
@@ -43973,7 +43394,7 @@
         <v>744</v>
       </c>
       <c r="E927" s="2">
-        <v>10220013</v>
+        <v>10030010</v>
       </c>
       <c r="F927" s="3" t="s">
         <v>50</v>
@@ -43992,9 +43413,6 @@
       <c r="A928" s="2">
         <v>102200124</v>
       </c>
-      <c r="B928" s="3">
-        <v>102200</v>
-      </c>
       <c r="C928" s="3">
         <v>6</v>
       </c>
@@ -44002,7 +43420,7 @@
         <v>744</v>
       </c>
       <c r="E928" s="2">
-        <v>10220013</v>
+        <v>10030010</v>
       </c>
       <c r="F928" s="3" t="s">
         <v>53</v>
@@ -44021,9 +43439,6 @@
       <c r="A929" s="2">
         <v>102200125</v>
       </c>
-      <c r="B929" s="3">
-        <v>102200</v>
-      </c>
       <c r="C929" s="3">
         <v>7</v>
       </c>
@@ -44031,7 +43446,7 @@
         <v>744</v>
       </c>
       <c r="E929" s="2">
-        <v>10220013</v>
+        <v>10030010</v>
       </c>
       <c r="F929" s="3" t="s">
         <v>68</v>
@@ -44050,9 +43465,6 @@
       <c r="A930" s="2">
         <v>102200126</v>
       </c>
-      <c r="B930" s="3">
-        <v>102200</v>
-      </c>
       <c r="C930" s="3">
         <v>8</v>
       </c>
@@ -44060,7 +43472,7 @@
         <v>744</v>
       </c>
       <c r="E930" s="2">
-        <v>10220013</v>
+        <v>10030010</v>
       </c>
       <c r="F930" s="3" t="s">
         <v>71</v>
@@ -44079,9 +43491,6 @@
       <c r="A931" s="2">
         <v>102200127</v>
       </c>
-      <c r="B931" s="3">
-        <v>102200</v>
-      </c>
       <c r="C931" s="3">
         <v>9</v>
       </c>
@@ -44089,7 +43498,7 @@
         <v>744</v>
       </c>
       <c r="E931" s="2">
-        <v>10220013</v>
+        <v>10030010</v>
       </c>
       <c r="F931" s="3" t="s">
         <v>74</v>
@@ -44108,9 +43517,6 @@
       <c r="A932" s="2">
         <v>102200128</v>
       </c>
-      <c r="B932" s="3">
-        <v>102200</v>
-      </c>
       <c r="C932" s="3">
         <v>10</v>
       </c>
@@ -44118,7 +43524,7 @@
         <v>744</v>
       </c>
       <c r="E932" s="2">
-        <v>10220013</v>
+        <v>10030010</v>
       </c>
       <c r="F932" s="3" t="s">
         <v>77</v>
@@ -48715,9 +48121,6 @@
       <c r="A1072" s="2">
         <v>102100140</v>
       </c>
-      <c r="B1072" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1072" s="3">
         <v>0</v>
       </c>
@@ -48725,7 +48128,7 @@
         <v>814</v>
       </c>
       <c r="E1072" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1072" s="3" t="s">
         <v>38</v>
@@ -48739,9 +48142,6 @@
       <c r="A1073" s="2">
         <v>102100141</v>
       </c>
-      <c r="B1073" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1073" s="3">
         <v>1</v>
       </c>
@@ -48749,7 +48149,7 @@
         <v>814</v>
       </c>
       <c r="E1073" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1073" s="3" t="s">
         <v>39</v>
@@ -48768,9 +48168,6 @@
       <c r="A1074" s="2">
         <v>102100142</v>
       </c>
-      <c r="B1074" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1074" s="3">
         <v>2</v>
       </c>
@@ -48778,7 +48175,7 @@
         <v>814</v>
       </c>
       <c r="E1074" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1074" s="3" t="s">
         <v>41</v>
@@ -48797,9 +48194,6 @@
       <c r="A1075" s="2">
         <v>102100143</v>
       </c>
-      <c r="B1075" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1075" s="3">
         <v>3</v>
       </c>
@@ -48807,7 +48201,7 @@
         <v>814</v>
       </c>
       <c r="E1075" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1075" s="3" t="s">
         <v>44</v>
@@ -48826,9 +48220,6 @@
       <c r="A1076" s="2">
         <v>102100144</v>
       </c>
-      <c r="B1076" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1076" s="3">
         <v>4</v>
       </c>
@@ -48836,7 +48227,7 @@
         <v>814</v>
       </c>
       <c r="E1076" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1076" s="3" t="s">
         <v>47</v>
@@ -48855,9 +48246,6 @@
       <c r="A1077" s="2">
         <v>102100145</v>
       </c>
-      <c r="B1077" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1077" s="3">
         <v>5</v>
       </c>
@@ -48865,7 +48253,7 @@
         <v>814</v>
       </c>
       <c r="E1077" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1077" s="3" t="s">
         <v>50</v>
@@ -48884,9 +48272,6 @@
       <c r="A1078" s="2">
         <v>102100146</v>
       </c>
-      <c r="B1078" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1078" s="3">
         <v>6</v>
       </c>
@@ -48894,7 +48279,7 @@
         <v>814</v>
       </c>
       <c r="E1078" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1078" s="3" t="s">
         <v>53</v>
@@ -48913,9 +48298,6 @@
       <c r="A1079" s="2">
         <v>102100147</v>
       </c>
-      <c r="B1079" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1079" s="3">
         <v>7</v>
       </c>
@@ -48923,7 +48305,7 @@
         <v>814</v>
       </c>
       <c r="E1079" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1079" s="3" t="s">
         <v>68</v>
@@ -48942,9 +48324,6 @@
       <c r="A1080" s="2">
         <v>102100148</v>
       </c>
-      <c r="B1080" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1080" s="3">
         <v>8</v>
       </c>
@@ -48952,7 +48331,7 @@
         <v>814</v>
       </c>
       <c r="E1080" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1080" s="3" t="s">
         <v>71</v>
@@ -48971,9 +48350,6 @@
       <c r="A1081" s="2">
         <v>102100149</v>
       </c>
-      <c r="B1081" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1081" s="3">
         <v>9</v>
       </c>
@@ -48981,7 +48357,7 @@
         <v>814</v>
       </c>
       <c r="E1081" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1081" s="3" t="s">
         <v>74</v>
@@ -49000,9 +48376,6 @@
       <c r="A1082" s="2">
         <v>102100150</v>
       </c>
-      <c r="B1082" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1082" s="3">
         <v>10</v>
       </c>
@@ -49010,7 +48383,7 @@
         <v>814</v>
       </c>
       <c r="E1082" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1082" s="3" t="s">
         <v>77</v>
@@ -49029,9 +48402,6 @@
       <c r="A1083" s="2">
         <v>102100151</v>
       </c>
-      <c r="B1083" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1083" s="3">
         <v>11</v>
       </c>
@@ -49039,7 +48409,7 @@
         <v>814</v>
       </c>
       <c r="E1083" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1083" s="3" t="s">
         <v>200</v>
@@ -49058,9 +48428,6 @@
       <c r="A1084" s="2">
         <v>102100152</v>
       </c>
-      <c r="B1084" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1084" s="3">
         <v>12</v>
       </c>
@@ -49068,7 +48435,7 @@
         <v>814</v>
       </c>
       <c r="E1084" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1084" s="3" t="s">
         <v>201</v>
@@ -49087,9 +48454,6 @@
       <c r="A1085" s="2">
         <v>102100153</v>
       </c>
-      <c r="B1085" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1085" s="3">
         <v>13</v>
       </c>
@@ -49097,7 +48461,7 @@
         <v>814</v>
       </c>
       <c r="E1085" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1085" s="3" t="s">
         <v>202</v>
@@ -49116,9 +48480,6 @@
       <c r="A1086" s="2">
         <v>102100154</v>
       </c>
-      <c r="B1086" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1086" s="3">
         <v>14</v>
       </c>
@@ -49126,7 +48487,7 @@
         <v>814</v>
       </c>
       <c r="E1086" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1086" s="3" t="s">
         <v>203</v>
@@ -49145,9 +48506,6 @@
       <c r="A1087" s="2">
         <v>102100155</v>
       </c>
-      <c r="B1087" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1087" s="3">
         <v>15</v>
       </c>
@@ -49155,7 +48513,7 @@
         <v>814</v>
       </c>
       <c r="E1087" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1087" s="3" t="s">
         <v>204</v>
@@ -49174,9 +48532,6 @@
       <c r="A1088" s="2">
         <v>102100156</v>
       </c>
-      <c r="B1088" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1088" s="3">
         <v>16</v>
       </c>
@@ -49184,7 +48539,7 @@
         <v>814</v>
       </c>
       <c r="E1088" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1088" s="3" t="s">
         <v>205</v>
@@ -49203,9 +48558,6 @@
       <c r="A1089" s="2">
         <v>102100157</v>
       </c>
-      <c r="B1089" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1089" s="3">
         <v>17</v>
       </c>
@@ -49213,7 +48565,7 @@
         <v>814</v>
       </c>
       <c r="E1089" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1089" s="3" t="s">
         <v>206</v>
@@ -49232,9 +48584,6 @@
       <c r="A1090" s="2">
         <v>102100158</v>
       </c>
-      <c r="B1090" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1090" s="3">
         <v>18</v>
       </c>
@@ -49242,7 +48591,7 @@
         <v>814</v>
       </c>
       <c r="E1090" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1090" s="3" t="s">
         <v>207</v>
@@ -49261,9 +48610,6 @@
       <c r="A1091" s="2">
         <v>102100159</v>
       </c>
-      <c r="B1091" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1091" s="3">
         <v>19</v>
       </c>
@@ -49271,7 +48617,7 @@
         <v>814</v>
       </c>
       <c r="E1091" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1091" s="3" t="s">
         <v>208</v>
@@ -49290,9 +48636,6 @@
       <c r="A1092" s="2">
         <v>102100160</v>
       </c>
-      <c r="B1092" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1092" s="3">
         <v>20</v>
       </c>
@@ -49300,7 +48643,7 @@
         <v>814</v>
       </c>
       <c r="E1092" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1092" s="3" t="s">
         <v>209</v>
@@ -49319,9 +48662,6 @@
       <c r="A1093" s="2">
         <v>102100161</v>
       </c>
-      <c r="B1093" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1093" s="3">
         <v>21</v>
       </c>
@@ -49329,7 +48669,7 @@
         <v>814</v>
       </c>
       <c r="E1093" s="2">
-        <v>10210014</v>
+        <v>10030009</v>
       </c>
       <c r="F1093" s="3" t="s">
         <v>210</v>
@@ -49348,9 +48688,6 @@
       <c r="A1094" s="2">
         <v>102100162</v>
       </c>
-      <c r="B1094" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1094" s="3">
         <v>0</v>
       </c>
@@ -49358,7 +48695,7 @@
         <v>814</v>
       </c>
       <c r="E1094" s="2">
-        <v>10210015</v>
+        <v>10030010</v>
       </c>
       <c r="F1094" s="3" t="s">
         <v>38</v>
@@ -49372,9 +48709,6 @@
       <c r="A1095" s="2">
         <v>102100163</v>
       </c>
-      <c r="B1095" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1095" s="3">
         <v>1</v>
       </c>
@@ -49382,7 +48716,7 @@
         <v>814</v>
       </c>
       <c r="E1095" s="2">
-        <v>10210015</v>
+        <v>10030010</v>
       </c>
       <c r="F1095" s="3" t="s">
         <v>39</v>
@@ -49401,9 +48735,6 @@
       <c r="A1096" s="2">
         <v>102100164</v>
       </c>
-      <c r="B1096" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1096" s="3">
         <v>2</v>
       </c>
@@ -49411,7 +48742,7 @@
         <v>814</v>
       </c>
       <c r="E1096" s="2">
-        <v>10210015</v>
+        <v>10030010</v>
       </c>
       <c r="F1096" s="3" t="s">
         <v>41</v>
@@ -49430,9 +48761,6 @@
       <c r="A1097" s="2">
         <v>102100165</v>
       </c>
-      <c r="B1097" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1097" s="3">
         <v>3</v>
       </c>
@@ -49440,7 +48768,7 @@
         <v>814</v>
       </c>
       <c r="E1097" s="2">
-        <v>10210015</v>
+        <v>10030010</v>
       </c>
       <c r="F1097" s="3" t="s">
         <v>44</v>
@@ -49459,9 +48787,6 @@
       <c r="A1098" s="2">
         <v>102100166</v>
       </c>
-      <c r="B1098" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1098" s="3">
         <v>4</v>
       </c>
@@ -49469,7 +48794,7 @@
         <v>814</v>
       </c>
       <c r="E1098" s="2">
-        <v>10210015</v>
+        <v>10030010</v>
       </c>
       <c r="F1098" s="3" t="s">
         <v>47</v>
@@ -49488,9 +48813,6 @@
       <c r="A1099" s="2">
         <v>102100167</v>
       </c>
-      <c r="B1099" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1099" s="3">
         <v>5</v>
       </c>
@@ -49498,7 +48820,7 @@
         <v>814</v>
       </c>
       <c r="E1099" s="2">
-        <v>10210015</v>
+        <v>10030010</v>
       </c>
       <c r="F1099" s="3" t="s">
         <v>50</v>
@@ -49517,9 +48839,6 @@
       <c r="A1100" s="2">
         <v>102100168</v>
       </c>
-      <c r="B1100" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1100" s="3">
         <v>6</v>
       </c>
@@ -49527,7 +48846,7 @@
         <v>814</v>
       </c>
       <c r="E1100" s="2">
-        <v>10210015</v>
+        <v>10030010</v>
       </c>
       <c r="F1100" s="3" t="s">
         <v>53</v>
@@ -49546,9 +48865,6 @@
       <c r="A1101" s="2">
         <v>102100169</v>
       </c>
-      <c r="B1101" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1101" s="3">
         <v>7</v>
       </c>
@@ -49556,7 +48872,7 @@
         <v>814</v>
       </c>
       <c r="E1101" s="2">
-        <v>10210015</v>
+        <v>10030010</v>
       </c>
       <c r="F1101" s="3" t="s">
         <v>68</v>
@@ -49575,9 +48891,6 @@
       <c r="A1102" s="2">
         <v>102100170</v>
       </c>
-      <c r="B1102" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1102" s="3">
         <v>8</v>
       </c>
@@ -49585,7 +48898,7 @@
         <v>814</v>
       </c>
       <c r="E1102" s="2">
-        <v>10210015</v>
+        <v>10030010</v>
       </c>
       <c r="F1102" s="3" t="s">
         <v>71</v>
@@ -49604,9 +48917,6 @@
       <c r="A1103" s="2">
         <v>102100171</v>
       </c>
-      <c r="B1103" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1103" s="3">
         <v>9</v>
       </c>
@@ -49614,7 +48924,7 @@
         <v>814</v>
       </c>
       <c r="E1103" s="2">
-        <v>10210015</v>
+        <v>10030010</v>
       </c>
       <c r="F1103" s="3" t="s">
         <v>74</v>
@@ -49633,9 +48943,6 @@
       <c r="A1104" s="2">
         <v>102100172</v>
       </c>
-      <c r="B1104" s="3">
-        <v>102100</v>
-      </c>
       <c r="C1104" s="3">
         <v>10</v>
       </c>
@@ -49643,7 +48950,7 @@
         <v>814</v>
       </c>
       <c r="E1104" s="2">
-        <v>10210015</v>
+        <v>10030010</v>
       </c>
       <c r="F1104" s="3" t="s">
         <v>77</v>
@@ -53061,9 +52368,6 @@
       <c r="A1208" s="2">
         <v>103900104</v>
       </c>
-      <c r="B1208" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1208" s="3">
         <v>0</v>
       </c>
@@ -53071,7 +52375,7 @@
         <v>917</v>
       </c>
       <c r="E1208" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1208" s="3" t="s">
         <v>38</v>
@@ -53085,9 +52389,6 @@
       <c r="A1209" s="2">
         <v>103900105</v>
       </c>
-      <c r="B1209" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1209" s="3">
         <v>1</v>
       </c>
@@ -53095,7 +52396,7 @@
         <v>917</v>
       </c>
       <c r="E1209" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1209" s="3" t="s">
         <v>39</v>
@@ -53114,9 +52415,6 @@
       <c r="A1210" s="2">
         <v>103900106</v>
       </c>
-      <c r="B1210" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1210" s="3">
         <v>2</v>
       </c>
@@ -53124,7 +52422,7 @@
         <v>917</v>
       </c>
       <c r="E1210" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1210" s="3" t="s">
         <v>41</v>
@@ -53143,9 +52441,6 @@
       <c r="A1211" s="2">
         <v>103900107</v>
       </c>
-      <c r="B1211" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1211" s="3">
         <v>3</v>
       </c>
@@ -53153,7 +52448,7 @@
         <v>917</v>
       </c>
       <c r="E1211" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1211" s="3" t="s">
         <v>44</v>
@@ -53172,9 +52467,6 @@
       <c r="A1212" s="2">
         <v>103900108</v>
       </c>
-      <c r="B1212" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1212" s="3">
         <v>4</v>
       </c>
@@ -53182,7 +52474,7 @@
         <v>917</v>
       </c>
       <c r="E1212" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1212" s="3" t="s">
         <v>47</v>
@@ -53201,9 +52493,6 @@
       <c r="A1213" s="2">
         <v>103900109</v>
       </c>
-      <c r="B1213" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1213" s="3">
         <v>5</v>
       </c>
@@ -53211,7 +52500,7 @@
         <v>917</v>
       </c>
       <c r="E1213" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1213" s="3" t="s">
         <v>50</v>
@@ -53230,9 +52519,6 @@
       <c r="A1214" s="2">
         <v>103900110</v>
       </c>
-      <c r="B1214" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1214" s="3">
         <v>6</v>
       </c>
@@ -53240,7 +52526,7 @@
         <v>917</v>
       </c>
       <c r="E1214" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1214" s="3" t="s">
         <v>53</v>
@@ -53259,9 +52545,6 @@
       <c r="A1215" s="2">
         <v>103900111</v>
       </c>
-      <c r="B1215" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1215" s="3">
         <v>7</v>
       </c>
@@ -53269,7 +52552,7 @@
         <v>917</v>
       </c>
       <c r="E1215" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1215" s="3" t="s">
         <v>68</v>
@@ -53288,9 +52571,6 @@
       <c r="A1216" s="2">
         <v>103900112</v>
       </c>
-      <c r="B1216" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1216" s="3">
         <v>8</v>
       </c>
@@ -53298,7 +52578,7 @@
         <v>917</v>
       </c>
       <c r="E1216" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1216" s="3" t="s">
         <v>71</v>
@@ -53317,9 +52597,6 @@
       <c r="A1217" s="2">
         <v>103900113</v>
       </c>
-      <c r="B1217" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1217" s="3">
         <v>9</v>
       </c>
@@ -53327,7 +52604,7 @@
         <v>917</v>
       </c>
       <c r="E1217" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1217" s="3" t="s">
         <v>74</v>
@@ -53346,9 +52623,6 @@
       <c r="A1218" s="2">
         <v>103900114</v>
       </c>
-      <c r="B1218" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1218" s="3">
         <v>10</v>
       </c>
@@ -53356,7 +52630,7 @@
         <v>917</v>
       </c>
       <c r="E1218" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1218" s="3" t="s">
         <v>77</v>
@@ -53375,9 +52649,6 @@
       <c r="A1219" s="2">
         <v>103900115</v>
       </c>
-      <c r="B1219" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1219" s="3">
         <v>11</v>
       </c>
@@ -53385,7 +52656,7 @@
         <v>917</v>
       </c>
       <c r="E1219" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1219" s="3" t="s">
         <v>200</v>
@@ -53404,9 +52675,6 @@
       <c r="A1220" s="2">
         <v>103900116</v>
       </c>
-      <c r="B1220" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1220" s="3">
         <v>12</v>
       </c>
@@ -53414,7 +52682,7 @@
         <v>917</v>
       </c>
       <c r="E1220" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1220" s="3" t="s">
         <v>201</v>
@@ -53433,9 +52701,6 @@
       <c r="A1221" s="2">
         <v>103900117</v>
       </c>
-      <c r="B1221" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1221" s="3">
         <v>13</v>
       </c>
@@ -53443,7 +52708,7 @@
         <v>917</v>
       </c>
       <c r="E1221" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1221" s="3" t="s">
         <v>202</v>
@@ -53462,9 +52727,6 @@
       <c r="A1222" s="2">
         <v>103900118</v>
       </c>
-      <c r="B1222" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1222" s="3">
         <v>14</v>
       </c>
@@ -53472,7 +52734,7 @@
         <v>917</v>
       </c>
       <c r="E1222" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1222" s="3" t="s">
         <v>203</v>
@@ -53491,9 +52753,6 @@
       <c r="A1223" s="2">
         <v>103900119</v>
       </c>
-      <c r="B1223" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1223" s="3">
         <v>15</v>
       </c>
@@ -53501,7 +52760,7 @@
         <v>917</v>
       </c>
       <c r="E1223" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1223" s="3" t="s">
         <v>204</v>
@@ -53520,9 +52779,6 @@
       <c r="A1224" s="2">
         <v>103900120</v>
       </c>
-      <c r="B1224" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1224" s="3">
         <v>16</v>
       </c>
@@ -53530,7 +52786,7 @@
         <v>917</v>
       </c>
       <c r="E1224" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1224" s="3" t="s">
         <v>205</v>
@@ -53549,9 +52805,6 @@
       <c r="A1225" s="2">
         <v>103900121</v>
       </c>
-      <c r="B1225" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1225" s="3">
         <v>17</v>
       </c>
@@ -53559,7 +52812,7 @@
         <v>917</v>
       </c>
       <c r="E1225" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1225" s="3" t="s">
         <v>206</v>
@@ -53578,9 +52831,6 @@
       <c r="A1226" s="2">
         <v>103900122</v>
       </c>
-      <c r="B1226" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1226" s="3">
         <v>18</v>
       </c>
@@ -53588,7 +52838,7 @@
         <v>917</v>
       </c>
       <c r="E1226" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1226" s="3" t="s">
         <v>207</v>
@@ -53607,9 +52857,6 @@
       <c r="A1227" s="2">
         <v>103900123</v>
       </c>
-      <c r="B1227" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1227" s="3">
         <v>19</v>
       </c>
@@ -53617,7 +52864,7 @@
         <v>917</v>
       </c>
       <c r="E1227" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1227" s="3" t="s">
         <v>208</v>
@@ -53636,9 +52883,6 @@
       <c r="A1228" s="2">
         <v>103900124</v>
       </c>
-      <c r="B1228" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1228" s="3">
         <v>20</v>
       </c>
@@ -53646,7 +52890,7 @@
         <v>917</v>
       </c>
       <c r="E1228" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1228" s="3" t="s">
         <v>209</v>
@@ -53665,9 +52909,6 @@
       <c r="A1229" s="2">
         <v>103900125</v>
       </c>
-      <c r="B1229" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1229" s="3">
         <v>21</v>
       </c>
@@ -53675,7 +52916,7 @@
         <v>917</v>
       </c>
       <c r="E1229" s="2">
-        <v>10390011</v>
+        <v>10030009</v>
       </c>
       <c r="F1229" s="3" t="s">
         <v>210</v>
@@ -53694,9 +52935,6 @@
       <c r="A1230" s="2">
         <v>103900126</v>
       </c>
-      <c r="B1230" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1230" s="3">
         <v>0</v>
       </c>
@@ -53704,7 +52942,7 @@
         <v>917</v>
       </c>
       <c r="E1230" s="2">
-        <v>10390012</v>
+        <v>10030010</v>
       </c>
       <c r="F1230" s="3" t="s">
         <v>38</v>
@@ -53718,9 +52956,6 @@
       <c r="A1231" s="2">
         <v>103900127</v>
       </c>
-      <c r="B1231" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1231" s="3">
         <v>1</v>
       </c>
@@ -53728,7 +52963,7 @@
         <v>917</v>
       </c>
       <c r="E1231" s="2">
-        <v>10390012</v>
+        <v>10030010</v>
       </c>
       <c r="F1231" s="3" t="s">
         <v>39</v>
@@ -53747,9 +52982,6 @@
       <c r="A1232" s="2">
         <v>103900128</v>
       </c>
-      <c r="B1232" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1232" s="3">
         <v>2</v>
       </c>
@@ -53757,7 +52989,7 @@
         <v>917</v>
       </c>
       <c r="E1232" s="2">
-        <v>10390012</v>
+        <v>10030010</v>
       </c>
       <c r="F1232" s="3" t="s">
         <v>41</v>
@@ -53776,9 +53008,6 @@
       <c r="A1233" s="2">
         <v>103900129</v>
       </c>
-      <c r="B1233" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1233" s="3">
         <v>3</v>
       </c>
@@ -53786,7 +53015,7 @@
         <v>917</v>
       </c>
       <c r="E1233" s="2">
-        <v>10390012</v>
+        <v>10030010</v>
       </c>
       <c r="F1233" s="3" t="s">
         <v>44</v>
@@ -53805,9 +53034,6 @@
       <c r="A1234" s="2">
         <v>103900130</v>
       </c>
-      <c r="B1234" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1234" s="3">
         <v>4</v>
       </c>
@@ -53815,7 +53041,7 @@
         <v>917</v>
       </c>
       <c r="E1234" s="2">
-        <v>10390012</v>
+        <v>10030010</v>
       </c>
       <c r="F1234" s="3" t="s">
         <v>47</v>
@@ -53834,9 +53060,6 @@
       <c r="A1235" s="2">
         <v>103900131</v>
       </c>
-      <c r="B1235" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1235" s="3">
         <v>5</v>
       </c>
@@ -53844,7 +53067,7 @@
         <v>917</v>
       </c>
       <c r="E1235" s="2">
-        <v>10390012</v>
+        <v>10030010</v>
       </c>
       <c r="F1235" s="3" t="s">
         <v>50</v>
@@ -53863,9 +53086,6 @@
       <c r="A1236" s="2">
         <v>103900132</v>
       </c>
-      <c r="B1236" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1236" s="3">
         <v>6</v>
       </c>
@@ -53873,7 +53093,7 @@
         <v>917</v>
       </c>
       <c r="E1236" s="2">
-        <v>10390012</v>
+        <v>10030010</v>
       </c>
       <c r="F1236" s="3" t="s">
         <v>53</v>
@@ -53892,9 +53112,6 @@
       <c r="A1237" s="2">
         <v>103900133</v>
       </c>
-      <c r="B1237" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1237" s="3">
         <v>7</v>
       </c>
@@ -53902,7 +53119,7 @@
         <v>917</v>
       </c>
       <c r="E1237" s="2">
-        <v>10390012</v>
+        <v>10030010</v>
       </c>
       <c r="F1237" s="3" t="s">
         <v>68</v>
@@ -53921,9 +53138,6 @@
       <c r="A1238" s="2">
         <v>103900134</v>
       </c>
-      <c r="B1238" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1238" s="3">
         <v>8</v>
       </c>
@@ -53931,7 +53145,7 @@
         <v>917</v>
       </c>
       <c r="E1238" s="2">
-        <v>10390012</v>
+        <v>10030010</v>
       </c>
       <c r="F1238" s="3" t="s">
         <v>71</v>
@@ -53950,9 +53164,6 @@
       <c r="A1239" s="2">
         <v>103900135</v>
       </c>
-      <c r="B1239" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1239" s="3">
         <v>9</v>
       </c>
@@ -53960,7 +53171,7 @@
         <v>917</v>
       </c>
       <c r="E1239" s="2">
-        <v>10390012</v>
+        <v>10030010</v>
       </c>
       <c r="F1239" s="3" t="s">
         <v>74</v>
@@ -53979,9 +53190,6 @@
       <c r="A1240" s="2">
         <v>103900136</v>
       </c>
-      <c r="B1240" s="3">
-        <v>103900</v>
-      </c>
       <c r="C1240" s="3">
         <v>10</v>
       </c>
@@ -53989,7 +53197,7 @@
         <v>917</v>
       </c>
       <c r="E1240" s="2">
-        <v>10390012</v>
+        <v>10030010</v>
       </c>
       <c r="F1240" s="3" t="s">
         <v>77</v>
@@ -57506,9 +56714,6 @@
       <c r="A1347" s="2">
         <v>102000107</v>
       </c>
-      <c r="B1347" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1347" s="3">
         <v>0</v>
       </c>
@@ -57516,7 +56721,7 @@
         <v>991</v>
       </c>
       <c r="E1347" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1347" s="3" t="s">
         <v>38</v>
@@ -57530,9 +56735,6 @@
       <c r="A1348" s="2">
         <v>102000108</v>
       </c>
-      <c r="B1348" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1348" s="3">
         <v>1</v>
       </c>
@@ -57540,7 +56742,7 @@
         <v>991</v>
       </c>
       <c r="E1348" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1348" s="3" t="s">
         <v>39</v>
@@ -57559,9 +56761,6 @@
       <c r="A1349" s="2">
         <v>102000109</v>
       </c>
-      <c r="B1349" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1349" s="3">
         <v>2</v>
       </c>
@@ -57569,7 +56768,7 @@
         <v>991</v>
       </c>
       <c r="E1349" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1349" s="3" t="s">
         <v>41</v>
@@ -57588,9 +56787,6 @@
       <c r="A1350" s="2">
         <v>102000110</v>
       </c>
-      <c r="B1350" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1350" s="3">
         <v>3</v>
       </c>
@@ -57598,7 +56794,7 @@
         <v>991</v>
       </c>
       <c r="E1350" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1350" s="3" t="s">
         <v>44</v>
@@ -57617,9 +56813,6 @@
       <c r="A1351" s="2">
         <v>102000111</v>
       </c>
-      <c r="B1351" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1351" s="3">
         <v>4</v>
       </c>
@@ -57627,7 +56820,7 @@
         <v>991</v>
       </c>
       <c r="E1351" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1351" s="3" t="s">
         <v>47</v>
@@ -57646,9 +56839,6 @@
       <c r="A1352" s="2">
         <v>102000112</v>
       </c>
-      <c r="B1352" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1352" s="3">
         <v>5</v>
       </c>
@@ -57656,7 +56846,7 @@
         <v>991</v>
       </c>
       <c r="E1352" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1352" s="3" t="s">
         <v>50</v>
@@ -57675,9 +56865,6 @@
       <c r="A1353" s="2">
         <v>102000113</v>
       </c>
-      <c r="B1353" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1353" s="3">
         <v>6</v>
       </c>
@@ -57685,7 +56872,7 @@
         <v>991</v>
       </c>
       <c r="E1353" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1353" s="3" t="s">
         <v>53</v>
@@ -57704,9 +56891,6 @@
       <c r="A1354" s="2">
         <v>102000114</v>
       </c>
-      <c r="B1354" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1354" s="3">
         <v>7</v>
       </c>
@@ -57714,7 +56898,7 @@
         <v>991</v>
       </c>
       <c r="E1354" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1354" s="3" t="s">
         <v>68</v>
@@ -57733,9 +56917,6 @@
       <c r="A1355" s="2">
         <v>102000115</v>
       </c>
-      <c r="B1355" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1355" s="3">
         <v>8</v>
       </c>
@@ -57743,7 +56924,7 @@
         <v>991</v>
       </c>
       <c r="E1355" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1355" s="3" t="s">
         <v>71</v>
@@ -57762,9 +56943,6 @@
       <c r="A1356" s="2">
         <v>102000116</v>
       </c>
-      <c r="B1356" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1356" s="3">
         <v>9</v>
       </c>
@@ -57772,7 +56950,7 @@
         <v>991</v>
       </c>
       <c r="E1356" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1356" s="3" t="s">
         <v>74</v>
@@ -57791,9 +56969,6 @@
       <c r="A1357" s="2">
         <v>102000117</v>
       </c>
-      <c r="B1357" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1357" s="3">
         <v>10</v>
       </c>
@@ -57801,7 +56976,7 @@
         <v>991</v>
       </c>
       <c r="E1357" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1357" s="3" t="s">
         <v>77</v>
@@ -57820,9 +56995,6 @@
       <c r="A1358" s="2">
         <v>102000118</v>
       </c>
-      <c r="B1358" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1358" s="3">
         <v>11</v>
       </c>
@@ -57830,7 +57002,7 @@
         <v>991</v>
       </c>
       <c r="E1358" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1358" s="3" t="s">
         <v>200</v>
@@ -57849,9 +57021,6 @@
       <c r="A1359" s="2">
         <v>102000119</v>
       </c>
-      <c r="B1359" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1359" s="3">
         <v>12</v>
       </c>
@@ -57859,7 +57028,7 @@
         <v>991</v>
       </c>
       <c r="E1359" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1359" s="3" t="s">
         <v>201</v>
@@ -57878,9 +57047,6 @@
       <c r="A1360" s="2">
         <v>102000120</v>
       </c>
-      <c r="B1360" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1360" s="3">
         <v>13</v>
       </c>
@@ -57888,7 +57054,7 @@
         <v>991</v>
       </c>
       <c r="E1360" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1360" s="3" t="s">
         <v>202</v>
@@ -57907,9 +57073,6 @@
       <c r="A1361" s="2">
         <v>102000121</v>
       </c>
-      <c r="B1361" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1361" s="3">
         <v>14</v>
       </c>
@@ -57917,7 +57080,7 @@
         <v>991</v>
       </c>
       <c r="E1361" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1361" s="3" t="s">
         <v>203</v>
@@ -57936,9 +57099,6 @@
       <c r="A1362" s="2">
         <v>102000122</v>
       </c>
-      <c r="B1362" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1362" s="3">
         <v>15</v>
       </c>
@@ -57946,7 +57106,7 @@
         <v>991</v>
       </c>
       <c r="E1362" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1362" s="3" t="s">
         <v>204</v>
@@ -57965,9 +57125,6 @@
       <c r="A1363" s="2">
         <v>102000123</v>
       </c>
-      <c r="B1363" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1363" s="3">
         <v>16</v>
       </c>
@@ -57975,7 +57132,7 @@
         <v>991</v>
       </c>
       <c r="E1363" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1363" s="3" t="s">
         <v>205</v>
@@ -57994,9 +57151,6 @@
       <c r="A1364" s="2">
         <v>102000124</v>
       </c>
-      <c r="B1364" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1364" s="3">
         <v>17</v>
       </c>
@@ -58004,7 +57158,7 @@
         <v>991</v>
       </c>
       <c r="E1364" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1364" s="3" t="s">
         <v>206</v>
@@ -58023,9 +57177,6 @@
       <c r="A1365" s="2">
         <v>102000125</v>
       </c>
-      <c r="B1365" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1365" s="3">
         <v>18</v>
       </c>
@@ -58033,7 +57184,7 @@
         <v>991</v>
       </c>
       <c r="E1365" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1365" s="3" t="s">
         <v>207</v>
@@ -58052,9 +57203,6 @@
       <c r="A1366" s="2">
         <v>102000126</v>
       </c>
-      <c r="B1366" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1366" s="3">
         <v>19</v>
       </c>
@@ -58062,7 +57210,7 @@
         <v>991</v>
       </c>
       <c r="E1366" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1366" s="3" t="s">
         <v>208</v>
@@ -58081,9 +57229,6 @@
       <c r="A1367" s="2">
         <v>102000127</v>
       </c>
-      <c r="B1367" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1367" s="3">
         <v>20</v>
       </c>
@@ -58091,7 +57236,7 @@
         <v>991</v>
       </c>
       <c r="E1367" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1367" s="3" t="s">
         <v>209</v>
@@ -58110,9 +57255,6 @@
       <c r="A1368" s="2">
         <v>102000128</v>
       </c>
-      <c r="B1368" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1368" s="3">
         <v>21</v>
       </c>
@@ -58120,7 +57262,7 @@
         <v>991</v>
       </c>
       <c r="E1368" s="2">
-        <v>10200011</v>
+        <v>10030009</v>
       </c>
       <c r="F1368" s="3" t="s">
         <v>210</v>
@@ -58139,9 +57281,6 @@
       <c r="A1369" s="2">
         <v>102000129</v>
       </c>
-      <c r="B1369" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1369" s="3">
         <v>0</v>
       </c>
@@ -58149,7 +57288,7 @@
         <v>991</v>
       </c>
       <c r="E1369" s="2">
-        <v>10200012</v>
+        <v>10030010</v>
       </c>
       <c r="F1369" s="3" t="s">
         <v>38</v>
@@ -58163,9 +57302,6 @@
       <c r="A1370" s="2">
         <v>102000130</v>
       </c>
-      <c r="B1370" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1370" s="3">
         <v>1</v>
       </c>
@@ -58173,7 +57309,7 @@
         <v>991</v>
       </c>
       <c r="E1370" s="2">
-        <v>10200012</v>
+        <v>10030010</v>
       </c>
       <c r="F1370" s="3" t="s">
         <v>39</v>
@@ -58192,9 +57328,6 @@
       <c r="A1371" s="2">
         <v>102000131</v>
       </c>
-      <c r="B1371" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1371" s="3">
         <v>2</v>
       </c>
@@ -58202,7 +57335,7 @@
         <v>991</v>
       </c>
       <c r="E1371" s="2">
-        <v>10200012</v>
+        <v>10030010</v>
       </c>
       <c r="F1371" s="3" t="s">
         <v>41</v>
@@ -58221,9 +57354,6 @@
       <c r="A1372" s="2">
         <v>102000132</v>
       </c>
-      <c r="B1372" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1372" s="3">
         <v>3</v>
       </c>
@@ -58231,7 +57361,7 @@
         <v>991</v>
       </c>
       <c r="E1372" s="2">
-        <v>10200012</v>
+        <v>10030010</v>
       </c>
       <c r="F1372" s="3" t="s">
         <v>44</v>
@@ -58250,9 +57380,6 @@
       <c r="A1373" s="2">
         <v>102000133</v>
       </c>
-      <c r="B1373" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1373" s="3">
         <v>4</v>
       </c>
@@ -58260,7 +57387,7 @@
         <v>991</v>
       </c>
       <c r="E1373" s="2">
-        <v>10200012</v>
+        <v>10030010</v>
       </c>
       <c r="F1373" s="3" t="s">
         <v>47</v>
@@ -58279,9 +57406,6 @@
       <c r="A1374" s="2">
         <v>102000134</v>
       </c>
-      <c r="B1374" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1374" s="3">
         <v>5</v>
       </c>
@@ -58289,7 +57413,7 @@
         <v>991</v>
       </c>
       <c r="E1374" s="2">
-        <v>10200012</v>
+        <v>10030010</v>
       </c>
       <c r="F1374" s="3" t="s">
         <v>50</v>
@@ -58308,9 +57432,6 @@
       <c r="A1375" s="2">
         <v>102000135</v>
       </c>
-      <c r="B1375" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1375" s="3">
         <v>6</v>
       </c>
@@ -58318,7 +57439,7 @@
         <v>991</v>
       </c>
       <c r="E1375" s="2">
-        <v>10200012</v>
+        <v>10030010</v>
       </c>
       <c r="F1375" s="3" t="s">
         <v>53</v>
@@ -58337,9 +57458,6 @@
       <c r="A1376" s="2">
         <v>102000136</v>
       </c>
-      <c r="B1376" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1376" s="3">
         <v>7</v>
       </c>
@@ -58347,7 +57465,7 @@
         <v>991</v>
       </c>
       <c r="E1376" s="2">
-        <v>10200012</v>
+        <v>10030010</v>
       </c>
       <c r="F1376" s="3" t="s">
         <v>68</v>
@@ -58366,9 +57484,6 @@
       <c r="A1377" s="2">
         <v>102000137</v>
       </c>
-      <c r="B1377" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1377" s="3">
         <v>8</v>
       </c>
@@ -58376,7 +57491,7 @@
         <v>991</v>
       </c>
       <c r="E1377" s="2">
-        <v>10200012</v>
+        <v>10030010</v>
       </c>
       <c r="F1377" s="3" t="s">
         <v>71</v>
@@ -58395,9 +57510,6 @@
       <c r="A1378" s="2">
         <v>102000138</v>
       </c>
-      <c r="B1378" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1378" s="3">
         <v>9</v>
       </c>
@@ -58405,7 +57517,7 @@
         <v>991</v>
       </c>
       <c r="E1378" s="2">
-        <v>10200012</v>
+        <v>10030010</v>
       </c>
       <c r="F1378" s="3" t="s">
         <v>74</v>
@@ -58424,9 +57536,6 @@
       <c r="A1379" s="2">
         <v>102000139</v>
       </c>
-      <c r="B1379" s="3">
-        <v>102000</v>
-      </c>
       <c r="C1379" s="3">
         <v>10</v>
       </c>
@@ -58434,7 +57543,7 @@
         <v>991</v>
       </c>
       <c r="E1379" s="2">
-        <v>10200012</v>
+        <v>10030010</v>
       </c>
       <c r="F1379" s="3" t="s">
         <v>77</v>
@@ -61521,9 +60630,6 @@
       <c r="A1473" s="2">
         <v>102700094</v>
       </c>
-      <c r="B1473" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1473" s="3">
         <v>0</v>
       </c>
@@ -61531,7 +60637,7 @@
         <v>1069</v>
       </c>
       <c r="E1473" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1473" s="3" t="s">
         <v>38</v>
@@ -61545,9 +60651,6 @@
       <c r="A1474" s="2">
         <v>102700095</v>
       </c>
-      <c r="B1474" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1474" s="3">
         <v>1</v>
       </c>
@@ -61555,7 +60658,7 @@
         <v>1069</v>
       </c>
       <c r="E1474" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1474" s="3" t="s">
         <v>39</v>
@@ -61574,9 +60677,6 @@
       <c r="A1475" s="2">
         <v>102700096</v>
       </c>
-      <c r="B1475" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1475" s="3">
         <v>2</v>
       </c>
@@ -61584,7 +60684,7 @@
         <v>1069</v>
       </c>
       <c r="E1475" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1475" s="3" t="s">
         <v>41</v>
@@ -61603,9 +60703,6 @@
       <c r="A1476" s="2">
         <v>102700097</v>
       </c>
-      <c r="B1476" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1476" s="3">
         <v>3</v>
       </c>
@@ -61613,7 +60710,7 @@
         <v>1069</v>
       </c>
       <c r="E1476" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1476" s="3" t="s">
         <v>44</v>
@@ -61632,9 +60729,6 @@
       <c r="A1477" s="2">
         <v>102700098</v>
       </c>
-      <c r="B1477" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1477" s="3">
         <v>4</v>
       </c>
@@ -61642,7 +60736,7 @@
         <v>1069</v>
       </c>
       <c r="E1477" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1477" s="3" t="s">
         <v>47</v>
@@ -61661,9 +60755,6 @@
       <c r="A1478" s="2">
         <v>102700099</v>
       </c>
-      <c r="B1478" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1478" s="3">
         <v>5</v>
       </c>
@@ -61671,7 +60762,7 @@
         <v>1069</v>
       </c>
       <c r="E1478" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1478" s="3" t="s">
         <v>50</v>
@@ -61690,9 +60781,6 @@
       <c r="A1479" s="2">
         <v>102700100</v>
       </c>
-      <c r="B1479" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1479" s="3">
         <v>6</v>
       </c>
@@ -61700,7 +60788,7 @@
         <v>1069</v>
       </c>
       <c r="E1479" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1479" s="3" t="s">
         <v>53</v>
@@ -61719,9 +60807,6 @@
       <c r="A1480" s="2">
         <v>102700101</v>
       </c>
-      <c r="B1480" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1480" s="3">
         <v>7</v>
       </c>
@@ -61729,7 +60814,7 @@
         <v>1069</v>
       </c>
       <c r="E1480" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1480" s="3" t="s">
         <v>68</v>
@@ -61748,9 +60833,6 @@
       <c r="A1481" s="2">
         <v>102700102</v>
       </c>
-      <c r="B1481" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1481" s="3">
         <v>8</v>
       </c>
@@ -61758,7 +60840,7 @@
         <v>1069</v>
       </c>
       <c r="E1481" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1481" s="3" t="s">
         <v>71</v>
@@ -61777,9 +60859,6 @@
       <c r="A1482" s="2">
         <v>102700103</v>
       </c>
-      <c r="B1482" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1482" s="3">
         <v>9</v>
       </c>
@@ -61787,7 +60866,7 @@
         <v>1069</v>
       </c>
       <c r="E1482" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1482" s="3" t="s">
         <v>74</v>
@@ -61806,9 +60885,6 @@
       <c r="A1483" s="2">
         <v>102700104</v>
       </c>
-      <c r="B1483" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1483" s="3">
         <v>10</v>
       </c>
@@ -61816,7 +60892,7 @@
         <v>1069</v>
       </c>
       <c r="E1483" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1483" s="3" t="s">
         <v>77</v>
@@ -61835,9 +60911,6 @@
       <c r="A1484" s="2">
         <v>102700105</v>
       </c>
-      <c r="B1484" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1484" s="3">
         <v>11</v>
       </c>
@@ -61845,7 +60918,7 @@
         <v>1069</v>
       </c>
       <c r="E1484" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1484" s="3" t="s">
         <v>200</v>
@@ -61864,9 +60937,6 @@
       <c r="A1485" s="2">
         <v>102700106</v>
       </c>
-      <c r="B1485" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1485" s="3">
         <v>12</v>
       </c>
@@ -61874,7 +60944,7 @@
         <v>1069</v>
       </c>
       <c r="E1485" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1485" s="3" t="s">
         <v>201</v>
@@ -61893,9 +60963,6 @@
       <c r="A1486" s="2">
         <v>102700107</v>
       </c>
-      <c r="B1486" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1486" s="3">
         <v>13</v>
       </c>
@@ -61903,7 +60970,7 @@
         <v>1069</v>
       </c>
       <c r="E1486" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1486" s="3" t="s">
         <v>202</v>
@@ -61922,9 +60989,6 @@
       <c r="A1487" s="2">
         <v>102700108</v>
       </c>
-      <c r="B1487" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1487" s="3">
         <v>14</v>
       </c>
@@ -61932,7 +60996,7 @@
         <v>1069</v>
       </c>
       <c r="E1487" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1487" s="3" t="s">
         <v>203</v>
@@ -61951,9 +61015,6 @@
       <c r="A1488" s="2">
         <v>102700109</v>
       </c>
-      <c r="B1488" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1488" s="3">
         <v>15</v>
       </c>
@@ -61961,7 +61022,7 @@
         <v>1069</v>
       </c>
       <c r="E1488" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1488" s="3" t="s">
         <v>204</v>
@@ -61980,9 +61041,6 @@
       <c r="A1489" s="2">
         <v>102700110</v>
       </c>
-      <c r="B1489" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1489" s="3">
         <v>16</v>
       </c>
@@ -61990,7 +61048,7 @@
         <v>1069</v>
       </c>
       <c r="E1489" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1489" s="3" t="s">
         <v>205</v>
@@ -62009,9 +61067,6 @@
       <c r="A1490" s="2">
         <v>102700111</v>
       </c>
-      <c r="B1490" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1490" s="3">
         <v>17</v>
       </c>
@@ -62019,7 +61074,7 @@
         <v>1069</v>
       </c>
       <c r="E1490" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1490" s="3" t="s">
         <v>206</v>
@@ -62038,9 +61093,6 @@
       <c r="A1491" s="2">
         <v>102700112</v>
       </c>
-      <c r="B1491" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1491" s="3">
         <v>18</v>
       </c>
@@ -62048,7 +61100,7 @@
         <v>1069</v>
       </c>
       <c r="E1491" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1491" s="3" t="s">
         <v>207</v>
@@ -62067,9 +61119,6 @@
       <c r="A1492" s="2">
         <v>102700113</v>
       </c>
-      <c r="B1492" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1492" s="3">
         <v>19</v>
       </c>
@@ -62077,7 +61126,7 @@
         <v>1069</v>
       </c>
       <c r="E1492" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1492" s="3" t="s">
         <v>208</v>
@@ -62096,9 +61145,6 @@
       <c r="A1493" s="2">
         <v>102700114</v>
       </c>
-      <c r="B1493" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1493" s="3">
         <v>20</v>
       </c>
@@ -62106,7 +61152,7 @@
         <v>1069</v>
       </c>
       <c r="E1493" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1493" s="3" t="s">
         <v>209</v>
@@ -62125,9 +61171,6 @@
       <c r="A1494" s="2">
         <v>102700115</v>
       </c>
-      <c r="B1494" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1494" s="3">
         <v>21</v>
       </c>
@@ -62135,7 +61178,7 @@
         <v>1069</v>
       </c>
       <c r="E1494" s="2">
-        <v>10270010</v>
+        <v>10030009</v>
       </c>
       <c r="F1494" s="3" t="s">
         <v>210</v>
@@ -62154,9 +61197,6 @@
       <c r="A1495" s="2">
         <v>102700116</v>
       </c>
-      <c r="B1495" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1495" s="3">
         <v>0</v>
       </c>
@@ -62164,7 +61204,7 @@
         <v>1069</v>
       </c>
       <c r="E1495" s="2">
-        <v>10270011</v>
+        <v>10030010</v>
       </c>
       <c r="F1495" s="3" t="s">
         <v>38</v>
@@ -62178,9 +61218,6 @@
       <c r="A1496" s="2">
         <v>102700117</v>
       </c>
-      <c r="B1496" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1496" s="3">
         <v>1</v>
       </c>
@@ -62188,7 +61225,7 @@
         <v>1069</v>
       </c>
       <c r="E1496" s="2">
-        <v>10270011</v>
+        <v>10030010</v>
       </c>
       <c r="F1496" s="3" t="s">
         <v>39</v>
@@ -62207,9 +61244,6 @@
       <c r="A1497" s="2">
         <v>102700118</v>
       </c>
-      <c r="B1497" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1497" s="3">
         <v>2</v>
       </c>
@@ -62217,7 +61251,7 @@
         <v>1069</v>
       </c>
       <c r="E1497" s="2">
-        <v>10270011</v>
+        <v>10030010</v>
       </c>
       <c r="F1497" s="3" t="s">
         <v>41</v>
@@ -62236,9 +61270,6 @@
       <c r="A1498" s="2">
         <v>102700119</v>
       </c>
-      <c r="B1498" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1498" s="3">
         <v>3</v>
       </c>
@@ -62246,7 +61277,7 @@
         <v>1069</v>
       </c>
       <c r="E1498" s="2">
-        <v>10270011</v>
+        <v>10030010</v>
       </c>
       <c r="F1498" s="3" t="s">
         <v>44</v>
@@ -62265,9 +61296,6 @@
       <c r="A1499" s="2">
         <v>102700120</v>
       </c>
-      <c r="B1499" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1499" s="3">
         <v>4</v>
       </c>
@@ -62275,7 +61303,7 @@
         <v>1069</v>
       </c>
       <c r="E1499" s="2">
-        <v>10270011</v>
+        <v>10030010</v>
       </c>
       <c r="F1499" s="3" t="s">
         <v>47</v>
@@ -62294,9 +61322,6 @@
       <c r="A1500" s="2">
         <v>102700121</v>
       </c>
-      <c r="B1500" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1500" s="3">
         <v>5</v>
       </c>
@@ -62304,7 +61329,7 @@
         <v>1069</v>
       </c>
       <c r="E1500" s="2">
-        <v>10270011</v>
+        <v>10030010</v>
       </c>
       <c r="F1500" s="3" t="s">
         <v>50</v>
@@ -62323,9 +61348,6 @@
       <c r="A1501" s="2">
         <v>102700122</v>
       </c>
-      <c r="B1501" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1501" s="3">
         <v>6</v>
       </c>
@@ -62333,7 +61355,7 @@
         <v>1069</v>
       </c>
       <c r="E1501" s="2">
-        <v>10270011</v>
+        <v>10030010</v>
       </c>
       <c r="F1501" s="3" t="s">
         <v>53</v>
@@ -62349,9 +61371,6 @@
       <c r="A1502" s="2">
         <v>102700123</v>
       </c>
-      <c r="B1502" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1502" s="3">
         <v>7</v>
       </c>
@@ -62359,7 +61378,7 @@
         <v>1069</v>
       </c>
       <c r="E1502" s="2">
-        <v>10270011</v>
+        <v>10030010</v>
       </c>
       <c r="F1502" s="3" t="s">
         <v>68</v>
@@ -62375,9 +61394,6 @@
       <c r="A1503" s="2">
         <v>102700124</v>
       </c>
-      <c r="B1503" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1503" s="3">
         <v>8</v>
       </c>
@@ -62385,7 +61401,7 @@
         <v>1069</v>
       </c>
       <c r="E1503" s="2">
-        <v>10270011</v>
+        <v>10030010</v>
       </c>
       <c r="F1503" s="3" t="s">
         <v>71</v>
@@ -62401,9 +61417,6 @@
       <c r="A1504" s="2">
         <v>102700125</v>
       </c>
-      <c r="B1504" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1504" s="3">
         <v>9</v>
       </c>
@@ -62411,7 +61424,7 @@
         <v>1069</v>
       </c>
       <c r="E1504" s="2">
-        <v>10270011</v>
+        <v>10030010</v>
       </c>
       <c r="F1504" s="3" t="s">
         <v>74</v>
@@ -62427,9 +61440,6 @@
       <c r="A1505" s="2">
         <v>102700126</v>
       </c>
-      <c r="B1505" s="3">
-        <v>102700</v>
-      </c>
       <c r="C1505" s="3">
         <v>10</v>
       </c>
@@ -62437,7 +61447,7 @@
         <v>1069</v>
       </c>
       <c r="E1505" s="2">
-        <v>10270011</v>
+        <v>10030010</v>
       </c>
       <c r="F1505" s="3" t="s">
         <v>77</v>
@@ -67767,9 +66777,6 @@
       <c r="A1667" s="2">
         <v>101500162</v>
       </c>
-      <c r="B1667" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1667" s="3">
         <v>0</v>
       </c>
@@ -67777,7 +66784,7 @@
         <v>1137</v>
       </c>
       <c r="E1667" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1667" s="3" t="s">
         <v>38</v>
@@ -67791,9 +66798,6 @@
       <c r="A1668" s="2">
         <v>101500163</v>
       </c>
-      <c r="B1668" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1668" s="3">
         <v>1</v>
       </c>
@@ -67801,7 +66805,7 @@
         <v>1137</v>
       </c>
       <c r="E1668" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1668" s="3" t="s">
         <v>39</v>
@@ -67820,9 +66824,6 @@
       <c r="A1669" s="2">
         <v>101500164</v>
       </c>
-      <c r="B1669" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1669" s="3">
         <v>2</v>
       </c>
@@ -67830,7 +66831,7 @@
         <v>1137</v>
       </c>
       <c r="E1669" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1669" s="3" t="s">
         <v>41</v>
@@ -67849,9 +66850,6 @@
       <c r="A1670" s="2">
         <v>101500165</v>
       </c>
-      <c r="B1670" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1670" s="3">
         <v>3</v>
       </c>
@@ -67859,7 +66857,7 @@
         <v>1137</v>
       </c>
       <c r="E1670" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1670" s="3" t="s">
         <v>44</v>
@@ -67878,9 +66876,6 @@
       <c r="A1671" s="2">
         <v>101500166</v>
       </c>
-      <c r="B1671" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1671" s="3">
         <v>4</v>
       </c>
@@ -67888,7 +66883,7 @@
         <v>1137</v>
       </c>
       <c r="E1671" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1671" s="3" t="s">
         <v>47</v>
@@ -67907,9 +66902,6 @@
       <c r="A1672" s="2">
         <v>101500167</v>
       </c>
-      <c r="B1672" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1672" s="3">
         <v>5</v>
       </c>
@@ -67917,7 +66909,7 @@
         <v>1137</v>
       </c>
       <c r="E1672" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1672" s="3" t="s">
         <v>50</v>
@@ -67936,9 +66928,6 @@
       <c r="A1673" s="2">
         <v>101500168</v>
       </c>
-      <c r="B1673" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1673" s="3">
         <v>6</v>
       </c>
@@ -67946,7 +66935,7 @@
         <v>1137</v>
       </c>
       <c r="E1673" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1673" s="3" t="s">
         <v>53</v>
@@ -67965,9 +66954,6 @@
       <c r="A1674" s="2">
         <v>101500169</v>
       </c>
-      <c r="B1674" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1674" s="3">
         <v>7</v>
       </c>
@@ -67975,7 +66961,7 @@
         <v>1137</v>
       </c>
       <c r="E1674" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1674" s="3" t="s">
         <v>68</v>
@@ -67994,9 +66980,6 @@
       <c r="A1675" s="2">
         <v>101500170</v>
       </c>
-      <c r="B1675" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1675" s="3">
         <v>8</v>
       </c>
@@ -68004,7 +66987,7 @@
         <v>1137</v>
       </c>
       <c r="E1675" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1675" s="3" t="s">
         <v>71</v>
@@ -68023,9 +67006,6 @@
       <c r="A1676" s="2">
         <v>101500171</v>
       </c>
-      <c r="B1676" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1676" s="3">
         <v>9</v>
       </c>
@@ -68033,7 +67013,7 @@
         <v>1137</v>
       </c>
       <c r="E1676" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1676" s="3" t="s">
         <v>74</v>
@@ -68052,9 +67032,6 @@
       <c r="A1677" s="2">
         <v>101500172</v>
       </c>
-      <c r="B1677" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1677" s="3">
         <v>10</v>
       </c>
@@ -68062,7 +67039,7 @@
         <v>1137</v>
       </c>
       <c r="E1677" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1677" s="3" t="s">
         <v>77</v>
@@ -68081,9 +67058,6 @@
       <c r="A1678" s="2">
         <v>101500173</v>
       </c>
-      <c r="B1678" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1678" s="3">
         <v>11</v>
       </c>
@@ -68091,7 +67065,7 @@
         <v>1137</v>
       </c>
       <c r="E1678" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1678" s="3" t="s">
         <v>200</v>
@@ -68110,9 +67084,6 @@
       <c r="A1679" s="2">
         <v>101500174</v>
       </c>
-      <c r="B1679" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1679" s="3">
         <v>12</v>
       </c>
@@ -68120,7 +67091,7 @@
         <v>1137</v>
       </c>
       <c r="E1679" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1679" s="3" t="s">
         <v>201</v>
@@ -68139,9 +67110,6 @@
       <c r="A1680" s="2">
         <v>101500175</v>
       </c>
-      <c r="B1680" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1680" s="3">
         <v>13</v>
       </c>
@@ -68149,7 +67117,7 @@
         <v>1137</v>
       </c>
       <c r="E1680" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1680" s="3" t="s">
         <v>202</v>
@@ -68168,9 +67136,6 @@
       <c r="A1681" s="2">
         <v>101500176</v>
       </c>
-      <c r="B1681" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1681" s="3">
         <v>14</v>
       </c>
@@ -68178,7 +67143,7 @@
         <v>1137</v>
       </c>
       <c r="E1681" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1681" s="3" t="s">
         <v>203</v>
@@ -68197,9 +67162,6 @@
       <c r="A1682" s="2">
         <v>101500177</v>
       </c>
-      <c r="B1682" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1682" s="3">
         <v>15</v>
       </c>
@@ -68207,7 +67169,7 @@
         <v>1137</v>
       </c>
       <c r="E1682" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1682" s="3" t="s">
         <v>204</v>
@@ -68226,9 +67188,6 @@
       <c r="A1683" s="2">
         <v>101500178</v>
       </c>
-      <c r="B1683" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1683" s="3">
         <v>16</v>
       </c>
@@ -68236,7 +67195,7 @@
         <v>1137</v>
       </c>
       <c r="E1683" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1683" s="3" t="s">
         <v>205</v>
@@ -68255,9 +67214,6 @@
       <c r="A1684" s="2">
         <v>101500179</v>
       </c>
-      <c r="B1684" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1684" s="3">
         <v>17</v>
       </c>
@@ -68265,7 +67221,7 @@
         <v>1137</v>
       </c>
       <c r="E1684" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1684" s="3" t="s">
         <v>206</v>
@@ -68284,9 +67240,6 @@
       <c r="A1685" s="2">
         <v>101500180</v>
       </c>
-      <c r="B1685" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1685" s="3">
         <v>18</v>
       </c>
@@ -68294,7 +67247,7 @@
         <v>1137</v>
       </c>
       <c r="E1685" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1685" s="3" t="s">
         <v>207</v>
@@ -68313,9 +67266,6 @@
       <c r="A1686" s="2">
         <v>101500181</v>
       </c>
-      <c r="B1686" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1686" s="3">
         <v>19</v>
       </c>
@@ -68323,7 +67273,7 @@
         <v>1137</v>
       </c>
       <c r="E1686" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1686" s="3" t="s">
         <v>208</v>
@@ -68342,9 +67292,6 @@
       <c r="A1687" s="2">
         <v>101500182</v>
       </c>
-      <c r="B1687" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1687" s="3">
         <v>20</v>
       </c>
@@ -68352,7 +67299,7 @@
         <v>1137</v>
       </c>
       <c r="E1687" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1687" s="3" t="s">
         <v>209</v>
@@ -68371,9 +67318,6 @@
       <c r="A1688" s="2">
         <v>101500183</v>
       </c>
-      <c r="B1688" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1688" s="3">
         <v>21</v>
       </c>
@@ -68381,7 +67325,7 @@
         <v>1137</v>
       </c>
       <c r="E1688" s="2">
-        <v>10150016</v>
+        <v>10030009</v>
       </c>
       <c r="F1688" s="3" t="s">
         <v>210</v>
@@ -68400,9 +67344,6 @@
       <c r="A1689" s="2">
         <v>101500184</v>
       </c>
-      <c r="B1689" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1689" s="3">
         <v>0</v>
       </c>
@@ -68410,7 +67351,7 @@
         <v>1137</v>
       </c>
       <c r="E1689" s="2">
-        <v>10150017</v>
+        <v>10030010</v>
       </c>
       <c r="F1689" s="3" t="s">
         <v>38</v>
@@ -68424,9 +67365,6 @@
       <c r="A1690" s="2">
         <v>101500185</v>
       </c>
-      <c r="B1690" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1690" s="3">
         <v>1</v>
       </c>
@@ -68434,7 +67372,7 @@
         <v>1137</v>
       </c>
       <c r="E1690" s="2">
-        <v>10150017</v>
+        <v>10030010</v>
       </c>
       <c r="F1690" s="3" t="s">
         <v>39</v>
@@ -68453,9 +67391,6 @@
       <c r="A1691" s="2">
         <v>101500186</v>
       </c>
-      <c r="B1691" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1691" s="3">
         <v>2</v>
       </c>
@@ -68463,7 +67398,7 @@
         <v>1137</v>
       </c>
       <c r="E1691" s="2">
-        <v>10150017</v>
+        <v>10030010</v>
       </c>
       <c r="F1691" s="3" t="s">
         <v>41</v>
@@ -68482,9 +67417,6 @@
       <c r="A1692" s="2">
         <v>101500187</v>
       </c>
-      <c r="B1692" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1692" s="3">
         <v>3</v>
       </c>
@@ -68492,7 +67424,7 @@
         <v>1137</v>
       </c>
       <c r="E1692" s="2">
-        <v>10150017</v>
+        <v>10030010</v>
       </c>
       <c r="F1692" s="3" t="s">
         <v>44</v>
@@ -68511,9 +67443,6 @@
       <c r="A1693" s="2">
         <v>101500188</v>
       </c>
-      <c r="B1693" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1693" s="3">
         <v>4</v>
       </c>
@@ -68521,7 +67450,7 @@
         <v>1137</v>
       </c>
       <c r="E1693" s="2">
-        <v>10150017</v>
+        <v>10030010</v>
       </c>
       <c r="F1693" s="3" t="s">
         <v>47</v>
@@ -68540,9 +67469,6 @@
       <c r="A1694" s="2">
         <v>101500189</v>
       </c>
-      <c r="B1694" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1694" s="3">
         <v>5</v>
       </c>
@@ -68550,7 +67476,7 @@
         <v>1137</v>
       </c>
       <c r="E1694" s="2">
-        <v>10150017</v>
+        <v>10030010</v>
       </c>
       <c r="F1694" s="3" t="s">
         <v>50</v>
@@ -68569,9 +67495,6 @@
       <c r="A1695" s="2">
         <v>101500190</v>
       </c>
-      <c r="B1695" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1695" s="3">
         <v>6</v>
       </c>
@@ -68579,7 +67502,7 @@
         <v>1137</v>
       </c>
       <c r="E1695" s="2">
-        <v>10150017</v>
+        <v>10030010</v>
       </c>
       <c r="F1695" s="3" t="s">
         <v>53</v>
@@ -68595,9 +67518,6 @@
       <c r="A1696" s="2">
         <v>101500191</v>
       </c>
-      <c r="B1696" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1696" s="3">
         <v>7</v>
       </c>
@@ -68605,7 +67525,7 @@
         <v>1137</v>
       </c>
       <c r="E1696" s="2">
-        <v>10150017</v>
+        <v>10030010</v>
       </c>
       <c r="F1696" s="3" t="s">
         <v>68</v>
@@ -68621,9 +67541,6 @@
       <c r="A1697" s="2">
         <v>101500192</v>
       </c>
-      <c r="B1697" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1697" s="3">
         <v>8</v>
       </c>
@@ -68631,7 +67548,7 @@
         <v>1137</v>
       </c>
       <c r="E1697" s="2">
-        <v>10150017</v>
+        <v>10030010</v>
       </c>
       <c r="F1697" s="3" t="s">
         <v>71</v>
@@ -68647,9 +67564,6 @@
       <c r="A1698" s="2">
         <v>101500193</v>
       </c>
-      <c r="B1698" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1698" s="3">
         <v>9</v>
       </c>
@@ -68657,7 +67571,7 @@
         <v>1137</v>
       </c>
       <c r="E1698" s="2">
-        <v>10150017</v>
+        <v>10030010</v>
       </c>
       <c r="F1698" s="3" t="s">
         <v>74</v>
@@ -68673,9 +67587,6 @@
       <c r="A1699" s="2">
         <v>101500194</v>
       </c>
-      <c r="B1699" s="3">
-        <v>101500</v>
-      </c>
       <c r="C1699" s="3">
         <v>10</v>
       </c>
@@ -68683,7 +67594,7 @@
         <v>1137</v>
       </c>
       <c r="E1699" s="2">
-        <v>10150017</v>
+        <v>10030010</v>
       </c>
       <c r="F1699" s="3" t="s">
         <v>77</v>

--- a/hall/resources/sample/ResearchSkills.xlsx
+++ b/hall/resources/sample/ResearchSkills.xlsx
@@ -3509,34 +3509,34 @@
     <t>1,6_100|7_100|8_100|9_100|10_100|11_-500|12_-2600|13_-600|14_-300|15_-1200|16_-500|17_-1500|18_-500|19_-200|20_-800|21_-200|22_-600|23_-300|24_-100|25_-300|26_-100|27_-100|28_-200</t>
   </si>
   <si>
-    <t>1,6_400|7_400|8_200|9_200|10_100</t>
-  </si>
-  <si>
-    <t>1,6_800|7_800|8_400|9_400|10_260</t>
-  </si>
-  <si>
-    <t>1,6_1200|7_1200|8_600|9_600|10_450</t>
-  </si>
-  <si>
-    <t>1,6_1600|7_1600|8_800|9_800|10_680</t>
-  </si>
-  <si>
-    <t>1,6_2000|7_2000|8_1000|9_1000|10_950</t>
-  </si>
-  <si>
-    <t>1,6_2400|7_2400|8_1300|9_1200|10_1200</t>
-  </si>
-  <si>
-    <t>1,6_2800|7_2800|8_1600|9_1500|10_1350</t>
-  </si>
-  <si>
-    <t>1,6_3200|7_3200|8_1800|9_1800|10_1650</t>
-  </si>
-  <si>
-    <t>1,6_3600|7_3600|8_2100|9_2100|10_1900</t>
-  </si>
-  <si>
-    <t>1,6_4000|7_4000|8_2500|9_2500|10_2050</t>
+    <t>1,6_300|7_200|8_200|9_200|10_200</t>
+  </si>
+  <si>
+    <t>1,6_800|7_400|8_400|9_400|10_400</t>
+  </si>
+  <si>
+    <t>1,6_1200|7_600|8_600|9_600|10_600</t>
+  </si>
+  <si>
+    <t>1,6_1600|7_900|8_900|9_800|10_800</t>
+  </si>
+  <si>
+    <t>1,6_2000|7_1300|8_1100|9_1000|10_1000</t>
+  </si>
+  <si>
+    <t>1,6_2400|7_1600|8_1300|9_1300|10_1200</t>
+  </si>
+  <si>
+    <t>1,6_2800|7_2000|8_1500|9_1500|10_1400</t>
+  </si>
+  <si>
+    <t>1,6_3200|7_2400|8_1800|9_1800|10_1600</t>
+  </si>
+  <si>
+    <t>1,6_3800|7_2800|8_2000|9_2000|10_1650</t>
+  </si>
+  <si>
+    <t>1,6_4000|7_3000|8_2130|9_2100|10_1800</t>
   </si>
   <si>
     <t>1,11_100|12_50|13_50|14_50|15_50</t>
@@ -3566,10 +3566,10 @@
     <t>1,11_2400|12_1600|13_1600|14_800|15_600</t>
   </si>
   <si>
-    <t>1,11_2700|12_1800|13_1800|14_900|15_700</t>
-  </si>
-  <si>
-    <t>1,11_3000|12_2000|13_2000|14_1000|15_840</t>
+    <t>1,11_2600|12_1700|13_1700|14_900|15_700</t>
+  </si>
+  <si>
+    <t>1,11_2800|12_1800|13_1800|14_1000|15_800</t>
   </si>
   <si>
     <t>1,16_100|17_100|18_50</t>
@@ -57974,7 +57974,7 @@
       <c r="I1389" s="4"/>
       <c r="J1389" s="4"/>
       <c r="L1389" s="13" t="s">
-        <v>58</v>
+        <v>531</v>
       </c>
       <c r="M1389" s="3" t="s">
         <v>59</v>
@@ -58008,7 +58008,7 @@
       <c r="I1390" s="4"/>
       <c r="J1390" s="4"/>
       <c r="L1390" s="13" t="s">
-        <v>61</v>
+        <v>532</v>
       </c>
       <c r="M1390" s="3" t="s">
         <v>62</v>
@@ -58042,7 +58042,7 @@
       <c r="I1391" s="4"/>
       <c r="J1391" s="4"/>
       <c r="L1391" s="13" t="s">
-        <v>64</v>
+        <v>533</v>
       </c>
       <c r="M1391" s="3" t="s">
         <v>65</v>
@@ -58076,7 +58076,7 @@
       <c r="I1392" s="4"/>
       <c r="J1392" s="4"/>
       <c r="L1392" s="13" t="s">
-        <v>67</v>
+        <v>534</v>
       </c>
       <c r="M1392" s="3" t="s">
         <v>68</v>
@@ -58110,7 +58110,7 @@
       <c r="I1393" s="4"/>
       <c r="J1393" s="4"/>
       <c r="L1393" s="13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M1393" s="3" t="s">
         <v>71</v>
@@ -58144,7 +58144,7 @@
       <c r="I1394" s="4"/>
       <c r="J1394" s="4"/>
       <c r="L1394" s="13" t="s">
-        <v>73</v>
+        <v>535</v>
       </c>
       <c r="M1394" s="3" t="s">
         <v>74</v>
@@ -58178,7 +58178,7 @@
       <c r="I1395" s="4"/>
       <c r="J1395" s="4"/>
       <c r="L1395" s="13" t="s">
-        <v>76</v>
+        <v>536</v>
       </c>
       <c r="M1395" s="3" t="s">
         <v>77</v>
@@ -58212,7 +58212,7 @@
       <c r="I1396" s="4"/>
       <c r="J1396" s="4"/>
       <c r="L1396" s="13" t="s">
-        <v>79</v>
+        <v>537</v>
       </c>
       <c r="M1396" s="3" t="s">
         <v>80</v>
@@ -58246,7 +58246,7 @@
       <c r="I1397" s="4"/>
       <c r="J1397" s="4"/>
       <c r="L1397" s="13" t="s">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="M1397" s="3" t="s">
         <v>83</v>
@@ -58280,7 +58280,7 @@
       <c r="I1398" s="4"/>
       <c r="J1398" s="4"/>
       <c r="L1398" s="13" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="M1398" s="3" t="s">
         <v>86</v>
